--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48143,6 +48143,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48166,6 +48166,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="G2079" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="G2080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48212,6 +48212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48235,6 +48235,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2082" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48076,7 +48076,7 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2075" t="n">
         <v>0</v>
@@ -48099,7 +48099,7 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2076" t="n">
         <v>0</v>
@@ -48122,7 +48122,7 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2077" t="n">
         <v>0</v>
@@ -48145,7 +48145,7 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2078" t="n">
         <v>0</v>
@@ -48168,7 +48168,7 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2079" t="n">
         <v>0</v>
@@ -48191,22 +48191,22 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2080" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C2080" t="n">
-        <v>3.35999989509583</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="D2080" t="n">
-        <v>3.3199999332428</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="E2080" t="n">
-        <v>3.35999989509583</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="F2080" t="n">
-        <v>3.3199999332428</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="G2080" t="s">
         <v>7</v>
@@ -48214,22 +48214,22 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2081" t="n">
-        <v>11500</v>
+        <v>4500</v>
       </c>
       <c r="C2081" t="n">
-        <v>3.25999999046326</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="D2081" t="n">
-        <v>3.1800000667572</v>
+        <v>3.3199999332428</v>
       </c>
       <c r="E2081" t="n">
-        <v>3.25999999046326</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="F2081" t="n">
-        <v>3.20000004768372</v>
+        <v>3.3199999332428</v>
       </c>
       <c r="G2081" t="s">
         <v>7</v>
@@ -48237,24 +48237,47 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2082" t="n">
-        <v>7500</v>
+        <v>11500</v>
       </c>
       <c r="C2082" t="n">
-        <v>3.33999991416931</v>
+        <v>3.25999999046326</v>
       </c>
       <c r="D2082" t="n">
-        <v>3.24000000953674</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="E2082" t="n">
         <v>3.25999999046326</v>
       </c>
       <c r="F2082" t="n">
-        <v>3.25999999046326</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="G2082" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2083" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614658355713</v>
+        <v>3.59614706039429</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709558486938</v>
+        <v>3.74709606170654</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589263916016</v>
+        <v>3.62589287757874</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274448394775</v>
+        <v>3.45274472236633</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.83100008964539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40168833732605</v>
+        <v>3.40168857574463</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666011810303</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.65750002861023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24763131141663</v>
+        <v>3.24763107299805</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.57049989700317</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17038035392761</v>
+        <v>3.17038083076477</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657492637634</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657492637634</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416525840759</v>
+        <v>3.16416501998901</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15173387527466</v>
+        <v>3.15173411369324</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18725156784058</v>
+        <v>3.187251329422</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467573165894</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875729560852</v>
+        <v>2.8187575340271</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252024650574</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795203208923</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795203208923</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.88624048233032</v>
+        <v>2.8862407207489</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.09446167945862</v>
+        <v>3.0944619178772</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08558249473572</v>
+        <v>3.0855827331543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G55" t="n">
-        <v>3.13441920280457</v>
+        <v>3.13441896438599</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868769645691</v>
+        <v>3.29868745803833</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678897857666</v>
+        <v>2.99678874015808</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820903778076</v>
+        <v>2.70820927619934</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G74" t="n">
-        <v>2.74816632270813</v>
+        <v>2.74816656112671</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135671615601</v>
+        <v>2.88135695457458</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459030151367</v>
+        <v>2.97459053993225</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122857093811</v>
+        <v>3.00122880935669</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.04118514060974</v>
+        <v>3.04118537902832</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657492637634</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666011810303</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562568664551</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>3.04118514060974</v>
+        <v>3.04118537902832</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670307159424</v>
+        <v>3.0767035484314</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562568664551</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666011810303</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795203208923</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334134101868</v>
+        <v>3.1033411026001</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>3.10778117179871</v>
+        <v>3.10778093338013</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.97015047073364</v>
+        <v>2.97015070915222</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023637771606</v>
+        <v>2.89023661613464</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019318580627</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915875434875</v>
+        <v>2.85915851593018</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928737640381</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>2.71708822250366</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>2.69932961463928</v>
+        <v>2.69932985305786</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713117599487</v>
+        <v>2.67713141441345</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>2.71708822250366</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>2.71708822250366</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G146" t="n">
-        <v>2.74816632270813</v>
+        <v>2.74816656112671</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471844673157</v>
+        <v>2.85471892356873</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928737640381</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76148509979248</v>
+        <v>2.76148557662964</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252024650574</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>2.78368377685547</v>
+        <v>2.78368401527405</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144238471985</v>
+        <v>2.80144262313843</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467573165894</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252024650574</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252024650574</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252024650574</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.6402370929718</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.67603707313538</v>
+        <v>2.67603754997253</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.6402370929718</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818651199341</v>
+        <v>2.82818627357483</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503649711609</v>
+        <v>2.85503673553467</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G256" t="n">
-        <v>2.84608674049377</v>
+        <v>2.8460865020752</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133676528931</v>
+        <v>2.80133700370789</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>2.78343653678894</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448630332947</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078657150269</v>
+        <v>2.72078728675842</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498706817627</v>
+        <v>2.68498730659485</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78343653678894</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763631820679</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.55968761444092</v>
+        <v>2.55968809127808</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.6133873462677</v>
+        <v>2.61338758468628</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G320" t="n">
-        <v>2.55968761444092</v>
+        <v>2.55968809127808</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.6402370929718</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56468677520752</v>
+        <v>2.5646870136261</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>2.51953387260437</v>
+        <v>2.51953411102295</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.3118302822113</v>
+        <v>2.31183052062988</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G343" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147294998169</v>
+        <v>2.50147271156311</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.37504434585571</v>
+        <v>2.37504482269287</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45631957054138</v>
+        <v>2.45631980895996</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341178894043</v>
+        <v>2.48341155052185</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>2.37504434585571</v>
+        <v>2.37504482269287</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698342323303</v>
+        <v>2.35698366165161</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892202377319</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892202377319</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30279970169067</v>
+        <v>2.30279994010925</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.19443297386169</v>
+        <v>2.19443321228027</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.19443297386169</v>
+        <v>2.19443321228027</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>2.20346355438232</v>
+        <v>2.20346331596375</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.1673412322998</v>
+        <v>2.16734147071838</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>2.11315727233887</v>
+        <v>2.11315774917603</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.15831065177917</v>
+        <v>2.1583104133606</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.18540215492249</v>
+        <v>2.18540239334106</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.3118302822113</v>
+        <v>2.31183052062988</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.14927983283997</v>
+        <v>2.14928007125854</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060706138611</v>
+        <v>1.95060694217682</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.85127055644989</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642357826233</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G420" t="n">
-        <v>1.81514823436737</v>
+        <v>1.81514811515808</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G421" t="n">
-        <v>1.77451038360596</v>
+        <v>1.77451062202454</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G423" t="n">
-        <v>1.47198569774628</v>
+        <v>1.47198581695557</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489395618439</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489395618439</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652698993683</v>
+        <v>1.33652710914612</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.21009886264801</v>
+        <v>1.2100989818573</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.2326751947403</v>
+        <v>1.23267531394958</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>1.37264919281006</v>
+        <v>1.37264931201935</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846570968628</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846570968628</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>1.2958892583847</v>
+        <v>1.29588937759399</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G440" t="n">
-        <v>1.36361873149872</v>
+        <v>1.36361885070801</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.36361873149872</v>
+        <v>1.36361885070801</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57132232189178</v>
+        <v>1.5713222026825</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.6029292345047</v>
+        <v>1.60292947292328</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099051475525</v>
+        <v>1.62099039554596</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259766578674</v>
+        <v>1.65259754657745</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.670658826828</v>
+        <v>1.67065894603729</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162812709808</v>
+        <v>1.66162824630737</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193428993225</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193428993225</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611753463745</v>
+        <v>1.80611765384674</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160212516785</v>
+        <v>1.80160236358643</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902579307556</v>
+        <v>1.77902591228485</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642357826233</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G458" t="n">
-        <v>1.88739287853241</v>
+        <v>1.88739275932312</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.85127055644989</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984966754913</v>
+        <v>1.75984978675842</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G477" t="n">
-        <v>1.70956838130951</v>
+        <v>1.70956826210022</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G478" t="n">
-        <v>1.70956838130951</v>
+        <v>1.70956826210022</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412571907043</v>
+        <v>1.87412559986115</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326752185822</v>
+        <v>1.8832676410675</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270494937897</v>
+        <v>1.78270506858826</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G496" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813398838043</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813398838043</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75527858734131</v>
+        <v>1.7552787065506</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G522" t="n">
-        <v>1.59529232978821</v>
+        <v>1.5952924489975</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="n">
-        <v>1.60443449020386</v>
+        <v>1.60443437099457</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G539" t="n">
-        <v>1.60443449020386</v>
+        <v>1.60443437099457</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.60443449020386</v>
+        <v>1.60443437099457</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G541" t="n">
-        <v>1.60443449020386</v>
+        <v>1.60443437099457</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.75</v>
       </c>
       <c r="G547" t="n">
-        <v>1.59986352920532</v>
+        <v>1.59986340999603</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072136878967</v>
+        <v>1.59072124958038</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G557" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67300009727478</v>
+        <v>1.67299997806549</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G566" t="n">
-        <v>1.51758468151093</v>
+        <v>1.51758480072021</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G571" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.79184710979462</v>
+        <v>1.79184699058533</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154529094696</v>
+        <v>1.52154541015625</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G590" t="n">
-        <v>1.53082311153412</v>
+        <v>1.53082299232483</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G591" t="n">
-        <v>1.48443448543549</v>
+        <v>1.48443460464478</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G592" t="n">
-        <v>1.48443448543549</v>
+        <v>1.48443460464478</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>1.44732356071472</v>
+        <v>1.44732367992401</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>1.52618420124054</v>
+        <v>1.52618432044983</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59576714038849</v>
+        <v>1.5957670211792</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>1.66998887062073</v>
+        <v>1.66998875141144</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.80915462970734</v>
+        <v>1.80915451049805</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G606" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G607" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048704624176</v>
+        <v>1.92048716545105</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2</v>
       </c>
       <c r="G615" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2</v>
       </c>
       <c r="G616" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2</v>
       </c>
       <c r="G621" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2</v>
       </c>
       <c r="G622" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>2.05037522315979</v>
+        <v>2.05037546157837</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820820808411</v>
+        <v>2.07820844650269</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615373134613</v>
+        <v>1.97615337371826</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832015037537</v>
+        <v>1.94832026958466</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326441764832</v>
+        <v>2.01326417922974</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748602867126</v>
+        <v>2.08748626708984</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.78331470489502</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.78331470489502</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.6441490650177</v>
+        <v>2.64414882659912</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.6812596321106</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.34726238250732</v>
+        <v>2.34726214408875</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.31015110015869</v>
+        <v>2.31015133857727</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G660" t="n">
-        <v>2.31015110015869</v>
+        <v>2.31015133857727</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>2.39365077018738</v>
+        <v>2.3936505317688</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.34726238250732</v>
+        <v>2.34726214408875</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>2.43076157569885</v>
+        <v>2.43076133728027</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>2.76475930213928</v>
+        <v>2.76475954055786</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764873504639</v>
+        <v>2.72764849662781</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.6812596321106</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G682" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970309257507</v>
+        <v>2.82970333099365</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.83898115158081</v>
+        <v>2.83898091316223</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.78331470489502</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>2.81114792823792</v>
+        <v>2.81114768981934</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G687" t="n">
-        <v>2.89464712142944</v>
+        <v>2.89464735984802</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G694" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>2.89464712142944</v>
+        <v>2.89464735984802</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>2.83898115158081</v>
+        <v>2.83898091316223</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>2.85753631591797</v>
+        <v>2.85753655433655</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>2.96886897087097</v>
+        <v>2.96886920928955</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G716" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G723" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G725" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G729" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G735" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G746" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G789" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>3.61813545227051</v>
+        <v>3.61813569068909</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>3.7877357006073</v>
+        <v>3.78773593902588</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>4.01386976242065</v>
+        <v>4.0138692855835</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G858" t="n">
-        <v>4.01386976242065</v>
+        <v>4.0138692855835</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502420425415</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.97618007659912</v>
+        <v>3.9761803150177</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G876" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G888" t="n">
-        <v>4.50382518768311</v>
+        <v>4.50382566452026</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>5.27644824981689</v>
+        <v>5.27644777297974</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>5.1351146697998</v>
+        <v>5.13511419296265</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>5.27644824981689</v>
+        <v>5.27644777297974</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G906" t="n">
-        <v>5.1351146697998</v>
+        <v>5.13511419296265</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G928" t="n">
-        <v>4.44729137420654</v>
+        <v>4.4472918510437</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5616021156311</v>
+        <v>3.56160235404968</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.93849110603333</v>
+        <v>3.9384913444519</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.88195776939392</v>
+        <v>3.8819580078125</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502420425415</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880266189575</v>
+        <v>4.74880313873291</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G960" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G963" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G964" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404747009277</v>
+        <v>4.17404699325562</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -54582,6 +54582,32 @@
         <v>3.22000002861023</v>
       </c>
       <c r="H2085" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="H2086" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709606170654</v>
+        <v>3.74709582328796</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589240074158</v>
+        <v>3.62589263916016</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.34752440452576</v>
+        <v>3.34752416610718</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274472236633</v>
+        <v>3.45274448394775</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.71050000190735</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29469156265259</v>
+        <v>3.29469203948975</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666011810303</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.65750002861023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24763131141663</v>
+        <v>3.24763107299805</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.19657492637634</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>3.19657492637634</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416549682617</v>
+        <v>3.16416501998901</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15173387527466</v>
+        <v>3.15173411369324</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.187251329422</v>
+        <v>3.18725156784058</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898765563965</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>3.02786660194397</v>
+        <v>3.02786731719971</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875729560852</v>
+        <v>2.8187575340271</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325825691223</v>
+        <v>2.97325873374939</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243505477905</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.91687488555908</v>
+        <v>2.9168746471405</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8862407207489</v>
+        <v>2.88624095916748</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.27900004386902</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9115469455719</v>
+        <v>2.91154670715332</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.30949997901917</v>
       </c>
       <c r="G48" t="n">
-        <v>2.93862891197205</v>
+        <v>2.9386293888092</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.91687488555908</v>
+        <v>2.9168746471405</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.0855827331543</v>
+        <v>3.08558249473572</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08114266395569</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G55" t="n">
-        <v>3.13441920280457</v>
+        <v>3.13441944122314</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760983467102</v>
+        <v>3.26760935783386</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868793487549</v>
+        <v>3.29868769645691</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873017311096</v>
+        <v>3.25873064994812</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02786660194397</v>
+        <v>3.02786731719971</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338381767273</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G66" t="n">
-        <v>3.02786660194397</v>
+        <v>3.02786731719971</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351243972778</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247776985168</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820927619934</v>
+        <v>2.70820903778076</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135719299316</v>
+        <v>2.88135695457458</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027956962585</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459030151367</v>
+        <v>2.97459053993225</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243505477905</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027956962585</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122857093811</v>
+        <v>3.00122904777527</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.04118609428406</v>
+        <v>3.0411856174469</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.19657492637634</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666011810303</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>3.04118609428406</v>
+        <v>3.0411856174469</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670331001282</v>
+        <v>3.07670307159424</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338381767273</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666011810303</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334157943726</v>
+        <v>3.1033411026001</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.08114266395569</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898765563965</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351243972778</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G112" t="n">
-        <v>2.83696007728577</v>
+        <v>2.83696031570435</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023637771606</v>
+        <v>2.89023685455322</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019342422485</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915851593018</v>
+        <v>2.85915875434875</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>2.83696007728577</v>
+        <v>2.83696031570435</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480435371399</v>
+        <v>2.77480411529541</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480435371399</v>
+        <v>2.77480411529541</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>2.69933009147644</v>
+        <v>2.6993293762207</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713165283203</v>
+        <v>2.67713117599487</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.79700255393982</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.79700255393982</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>2.78368353843689</v>
+        <v>2.78368377685547</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.79700255393982</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7259681224823</v>
+        <v>2.72596764564514</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>2.81476140022278</v>
+        <v>2.81476211547852</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247776985168</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027956962585</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.7259681224823</v>
+        <v>2.72596764564514</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77036499977112</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>2.79700255393982</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>2.79700255393982</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027956962585</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027956962585</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>2.81476140022278</v>
+        <v>2.81476211547852</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>2.83713626861572</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868680000305</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G219" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.67603707313538</v>
+        <v>2.67603731155396</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.83713626861572</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.83713626861572</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818675041199</v>
+        <v>2.82818651199341</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503649711609</v>
+        <v>2.85503625869751</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G264" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448725700378</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868680000305</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498754501343</v>
+        <v>2.68498706817627</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763679504395</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.61338782310486</v>
+        <v>2.61338806152344</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178786277771</v>
+        <v>2.54178762435913</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.60443758964539</v>
+        <v>2.60443782806396</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.50598812103271</v>
+        <v>2.50598835945129</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>2.51953411102295</v>
+        <v>2.51953434944153</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.51050353050232</v>
+        <v>2.51050329208374</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G336" t="n">
-        <v>2.43825888633728</v>
+        <v>2.4382586479187</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.51050353050232</v>
+        <v>2.51050329208374</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.47438097000122</v>
+        <v>2.47438144683838</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G363" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>2.32989168167114</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.37504458427429</v>
+        <v>2.37504482269287</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341178894043</v>
+        <v>2.48341131210327</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G374" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.42922806739807</v>
+        <v>2.42922830581665</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>2.37504458427429</v>
+        <v>2.37504482269287</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698366165161</v>
+        <v>2.35698342323303</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30279994010925</v>
+        <v>2.30279970169067</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.2937695980072</v>
+        <v>2.29376935958862</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958563804626</v>
+        <v>2.23958611488342</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861621856689</v>
+        <v>2.24861669540405</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.19443273544312</v>
+        <v>2.19443297386169</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.19443273544312</v>
+        <v>2.19443297386169</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.1583104133606</v>
+        <v>2.15831089019775</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.18540239334106</v>
+        <v>2.18540263175964</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>2.17637157440186</v>
+        <v>2.17637181282043</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26667785644531</v>
+        <v>2.26667737960815</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861621856689</v>
+        <v>2.24861669540405</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G411" t="n">
-        <v>2.17637157440186</v>
+        <v>2.17637181282043</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99575972557068</v>
+        <v>1.99575984477997</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060694217682</v>
+        <v>1.95060706138611</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.85127067565918</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G420" t="n">
-        <v>1.81514811515808</v>
+        <v>1.81514835357666</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G421" t="n">
-        <v>1.77451038360596</v>
+        <v>1.77451050281525</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G422" t="n">
-        <v>1.64356696605682</v>
+        <v>1.64356708526611</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G423" t="n">
-        <v>1.47198593616486</v>
+        <v>1.47198581695557</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652722835541</v>
+        <v>1.33652698993683</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G428" t="n">
-        <v>1.21912944316864</v>
+        <v>1.21912932395935</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.2100989818573</v>
+        <v>1.21009886264801</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364461421967</v>
+        <v>1.22364473342896</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.23267507553101</v>
+        <v>1.23267531394958</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G433" t="n">
-        <v>1.2642822265625</v>
+        <v>1.26428246498108</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>1.37264943122864</v>
+        <v>1.37264919281006</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846606731415</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846606731415</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.60292935371399</v>
+        <v>1.6029292345047</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.67065894603729</v>
+        <v>1.670658826828</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162836551666</v>
+        <v>1.66162800788879</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611753463745</v>
+        <v>1.80611741542816</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160212516785</v>
+        <v>1.80160224437714</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030113697052</v>
+        <v>1.86030089855194</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G458" t="n">
-        <v>1.88739287853241</v>
+        <v>1.88739275932312</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.85127067565918</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G467" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G470" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G471" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897796630859</v>
+        <v>1.92897820472717</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G486" t="n">
-        <v>1.82384431362152</v>
+        <v>1.82384419441223</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412571907043</v>
+        <v>1.87412548065186</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.80098915100098</v>
+        <v>1.80098903179169</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326787948608</v>
+        <v>1.8832676410675</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G493" t="n">
-        <v>1.82384431362152</v>
+        <v>1.82384419441223</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G496" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813410758972</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813410758972</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.7415657043457</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.7415657043457</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.7415657043457</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G509" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G510" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G511" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G522" t="n">
-        <v>1.5952924489975</v>
+        <v>1.59529221057892</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G537" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.75</v>
       </c>
       <c r="G547" t="n">
-        <v>1.59986352920532</v>
+        <v>1.59986340999603</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072148799896</v>
+        <v>1.59072136878967</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014493465424</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014493465424</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G554" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014493465424</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67299997806549</v>
+        <v>1.67300009727478</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G571" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G577" t="n">
-        <v>1.7872759103775</v>
+        <v>1.78727602958679</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242342472076</v>
+        <v>1.73242354393005</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G580" t="n">
-        <v>1.70042634010315</v>
+        <v>1.70042622089386</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154529094696</v>
+        <v>1.52154541015625</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.44268476963043</v>
+        <v>1.44268465042114</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G594" t="n">
-        <v>1.44268476963043</v>
+        <v>1.44268465042114</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>1.44732367992401</v>
+        <v>1.44732356071472</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>1.52618432044983</v>
+        <v>1.52618420124054</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G606" t="n">
-        <v>1.88337635993958</v>
+        <v>1.88337624073029</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G607" t="n">
-        <v>1.88337635993958</v>
+        <v>1.88337624073029</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048716545105</v>
+        <v>1.92048692703247</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G611" t="n">
-        <v>1.7905992269516</v>
+        <v>1.79059910774231</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>1.81843233108521</v>
+        <v>1.81843221187592</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820868492126</v>
+        <v>2.07820844650269</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832015037537</v>
+        <v>1.94832026958466</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326441764832</v>
+        <v>2.01326417922974</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748602867126</v>
+        <v>2.08748579025269</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.58848261833191</v>
+        <v>2.58848285675049</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61631608009338</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.6812596321106</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G646" t="n">
-        <v>2.65342664718628</v>
+        <v>2.6534264087677</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>2.61631608009338</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G648" t="n">
-        <v>2.61631608009338</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>2.59776020050049</v>
+        <v>2.59776043891907</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.54209423065186</v>
+        <v>2.54209399223328</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>2.38437294960022</v>
+        <v>2.3843731880188</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703778266907</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703778266907</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.69053745269775</v>
+        <v>2.69053769111633</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>2.61631608009338</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764849662781</v>
+        <v>2.72764873504639</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.6812596321106</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970333099365</v>
+        <v>2.82970309257507</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G687" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.82042551040649</v>
+        <v>2.82042574882507</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G705" t="n">
-        <v>3.00598001480103</v>
+        <v>3.00597977638245</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G707" t="n">
-        <v>3.00598001480103</v>
+        <v>3.00597977638245</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>3.00598001480103</v>
+        <v>3.00597977638245</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>3.02453517913818</v>
+        <v>3.02453541755676</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G749" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>3.33546876907349</v>
+        <v>3.33546900749207</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>3.37315773963928</v>
+        <v>3.3731575012207</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>3.33546876907349</v>
+        <v>3.33546900749207</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>3.33546876907349</v>
+        <v>3.33546900749207</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>3.37315773963928</v>
+        <v>3.3731575012207</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>3.26009082794189</v>
+        <v>3.26009106636047</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G861" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08800315856934</v>
+        <v>5.08800363540649</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56160235404968</v>
+        <v>3.5616021156311</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>3.63698029518127</v>
+        <v>3.6369800567627</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.88195824623108</v>
+        <v>3.8819580078125</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G938" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880266189575</v>
+        <v>4.74880313873291</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>4.24942493438721</v>
+        <v>4.24942541122437</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G967" t="n">
-        <v>4.24942493438721</v>
+        <v>4.24942541122437</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>4.43786954879761</v>
+        <v>4.43787002563477</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>4.43786954879761</v>
+        <v>4.43787002563477</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>4.55093669891357</v>
+        <v>4.55093622207642</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G974" t="n">
-        <v>4.24942493438721</v>
+        <v>4.24942541122437</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -54660,6 +54660,32 @@
         <v>3.1800000667572</v>
       </c>
       <c r="H2088" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="H2089" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48435,7 +48435,9 @@
       <c r="E2090" t="n">
         <v>3.14000010490417</v>
       </c>
-      <c r="F2090"/>
+      <c r="F2090" t="n">
+        <v>3.11999988555908</v>
+      </c>
       <c r="G2090" t="s">
         <v>7</v>
       </c>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48550,7 +48550,9 @@
       <c r="E2095" t="n">
         <v>3.09999990463257</v>
       </c>
-      <c r="F2095"/>
+      <c r="F2095" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G2095" t="s">
         <v>7</v>
       </c>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48557,6 +48557,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2096">
+      <c r="A2096" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2096" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2097"/>
+      <c r="G2097" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48596,7 +48596,9 @@
       <c r="E2097" t="n">
         <v>3.20000004768372</v>
       </c>
-      <c r="F2097"/>
+      <c r="F2097" t="n">
+        <v>3.20000004768372</v>
+      </c>
       <c r="G2097" t="s">
         <v>7</v>
       </c>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48603,6 +48603,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2098" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48649,6 +48649,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G2100" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48672,6 +48672,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2101" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48695,6 +48695,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2102" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -48718,6 +48718,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2103" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709582328796</v>
+        <v>3.74709630012512</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -543,7 +543,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42743825912476</v>
+        <v>3.42743849754333</v>
       </c>
       <c r="H6" t="n">
         <v>110500</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3475239276886</v>
+        <v>3.34752416610718</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274472236633</v>
+        <v>3.45274496078491</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -630,7 +630,7 @@
         <v>3.83100008964539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40168881416321</v>
+        <v>3.40168833732605</v>
       </c>
       <c r="H9" t="n">
         <v>35000</v>
@@ -688,7 +688,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H11" t="n">
         <v>156500</v>
@@ -775,7 +775,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.22321271896362</v>
+        <v>3.2232129573822</v>
       </c>
       <c r="H14" t="n">
         <v>55000</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881560325623</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -891,7 +891,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416549682617</v>
+        <v>3.16416501998901</v>
       </c>
       <c r="H18" t="n">
         <v>39500</v>
@@ -949,7 +949,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.187251329422</v>
+        <v>3.18725156784058</v>
       </c>
       <c r="H20" t="n">
         <v>214000</v>
@@ -978,7 +978,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898717880249</v>
       </c>
       <c r="H21" t="n">
         <v>50500</v>
@@ -1036,7 +1036,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96571111679077</v>
+        <v>2.96571087837219</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467573165894</v>
+        <v>2.89467597007751</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8187575340271</v>
+        <v>2.81875729560852</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1239,7 +1239,7 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88579702377319</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H30" t="n">
         <v>45000</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1326,7 +1326,7 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>2.88579702377319</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325873374939</v>
+        <v>2.97325849533081</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1500,7 +1500,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683193206787</v>
       </c>
       <c r="H39" t="n">
         <v>20500</v>
@@ -1529,7 +1529,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243457794189</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H40" t="n">
         <v>9500</v>
@@ -1674,7 +1674,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.88624048233032</v>
+        <v>2.8862407207489</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.27900004386902</v>
       </c>
       <c r="G46" t="n">
-        <v>2.91154718399048</v>
+        <v>2.9115469455719</v>
       </c>
       <c r="H46" t="n">
         <v>10000</v>
@@ -1732,7 +1732,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683193206787</v>
       </c>
       <c r="H47" t="n">
         <v>58000</v>
@@ -1761,7 +1761,7 @@
         <v>3.30949997901917</v>
       </c>
       <c r="G48" t="n">
-        <v>2.93862915039062</v>
+        <v>2.93862891197205</v>
       </c>
       <c r="H48" t="n">
         <v>19000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.09446167945862</v>
+        <v>3.0944619178772</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08558225631714</v>
+        <v>3.08558249473572</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1935,7 +1935,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08114290237427</v>
+        <v>3.08114337921143</v>
       </c>
       <c r="H54" t="n">
         <v>61000</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769550323486</v>
+        <v>3.18769526481628</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769550323486</v>
+        <v>3.18769526481628</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868769645691</v>
+        <v>3.29868745803833</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881560325623</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678874015808</v>
+        <v>2.99678897857666</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2312,7 +2312,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351291656494</v>
       </c>
       <c r="H67" t="n">
         <v>40000</v>
@@ -2370,7 +2370,7 @@
         <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88579702377319</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H69" t="n">
         <v>15500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2457,7 +2457,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820879936218</v>
+        <v>2.70820903778076</v>
       </c>
       <c r="H72" t="n">
         <v>15500</v>
@@ -2573,7 +2573,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683193206787</v>
       </c>
       <c r="H76" t="n">
         <v>17000</v>
@@ -2602,7 +2602,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.92131423950195</v>
+        <v>2.92131400108337</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2631,7 +2631,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2718,7 +2718,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243457794189</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2776,7 +2776,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122880935669</v>
+        <v>3.00122857093811</v>
       </c>
       <c r="H83" t="n">
         <v>15000</v>
@@ -2921,7 +2921,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H88" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562544822693</v>
+        <v>3.04562520980835</v>
       </c>
       <c r="H89" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.0767035484314</v>
+        <v>3.07670307159424</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3037,7 +3037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.17437624931335</v>
+        <v>3.17437648773193</v>
       </c>
       <c r="H92" t="n">
         <v>19000</v>
@@ -3066,7 +3066,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H93" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562544822693</v>
+        <v>3.04562520980835</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3182,7 +3182,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H97" t="n">
         <v>9500</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.032306432724</v>
+        <v>3.03230667114258</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3269,7 +3269,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334086418152</v>
+        <v>3.10334134101868</v>
       </c>
       <c r="H100" t="n">
         <v>4500</v>
@@ -3327,7 +3327,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G102" t="n">
-        <v>3.2320921421051</v>
+        <v>3.23209238052368</v>
       </c>
       <c r="H102" t="n">
         <v>28000</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881560325623</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545434951782</v>
+        <v>3.20545411109924</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3414,7 +3414,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.08114290237427</v>
+        <v>3.08114337921143</v>
       </c>
       <c r="H105" t="n">
         <v>22500</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674626350403</v>
+        <v>3.03674650192261</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3501,7 +3501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898717880249</v>
       </c>
       <c r="H108" t="n">
         <v>6000</v>
@@ -3530,7 +3530,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351291656494</v>
       </c>
       <c r="H109" t="n">
         <v>24500</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.97015047073364</v>
+        <v>2.97015070915222</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023661613464</v>
+        <v>2.89023637771606</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.25</v>
       </c>
       <c r="G116" t="n">
-        <v>2.88579702377319</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.84583950042725</v>
+        <v>2.84583926200867</v>
       </c>
       <c r="H117" t="n">
         <v>11500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915875434875</v>
+        <v>2.85915851593018</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3936,7 +3936,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480483055115</v>
+        <v>2.77480459213257</v>
       </c>
       <c r="H123" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480483055115</v>
+        <v>2.77480459213257</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7437264919281</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H127" t="n">
         <v>13000</v>
@@ -4081,7 +4081,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G128" t="n">
-        <v>2.7437264919281</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H128" t="n">
         <v>2500</v>
@@ -4110,7 +4110,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808113098145</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H129" t="n">
         <v>39500</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.67269158363342</v>
+        <v>2.672691822052</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4371,7 +4371,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>2.69932961463928</v>
+        <v>2.69932985305786</v>
       </c>
       <c r="H138" t="n">
         <v>5000</v>
@@ -4458,7 +4458,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H141" t="n">
         <v>4500</v>
@@ -4487,7 +4487,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G142" t="n">
-        <v>2.7437264919281</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H142" t="n">
         <v>8500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700326919556</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4922,7 +4922,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700326919556</v>
       </c>
       <c r="H157" t="n">
         <v>7500</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76148509979248</v>
+        <v>2.76148557662964</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5241,7 +5241,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700326919556</v>
       </c>
       <c r="H168" t="n">
         <v>12500</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144262313843</v>
+        <v>2.80144286155701</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5473,7 +5473,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5531,7 +5531,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808113098145</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H178" t="n">
         <v>9500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5647,7 +5647,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>2.84583950042725</v>
+        <v>2.84583926200867</v>
       </c>
       <c r="H182" t="n">
         <v>18500</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467573165894</v>
+        <v>2.89467597007751</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5763,7 +5763,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H186" t="n">
         <v>66000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6024,7 +6024,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700326919556</v>
       </c>
       <c r="H195" t="n">
         <v>500</v>
@@ -6053,7 +6053,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700326919556</v>
       </c>
       <c r="H196" t="n">
         <v>3000</v>
@@ -6082,7 +6082,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H197" t="n">
         <v>10500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H203" t="n">
         <v>26000</v>
@@ -6343,7 +6343,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H213" t="n">
         <v>37000</v>
@@ -6604,7 +6604,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H215" t="n">
         <v>4000</v>
@@ -6633,7 +6633,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6691,7 +6691,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H218" t="n">
         <v>27500</v>
@@ -6720,7 +6720,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G219" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553654670715</v>
       </c>
       <c r="H219" t="n">
         <v>9000</v>
@@ -6749,7 +6749,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H220" t="n">
         <v>7000</v>
@@ -6778,7 +6778,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H221" t="n">
         <v>31000</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H227" t="n">
         <v>27000</v>
@@ -7010,7 +7010,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.5238881111145</v>
+        <v>2.52388787269592</v>
       </c>
       <c r="H229" t="n">
         <v>28000</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708755493164</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708755493164</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708755493164</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7590,7 +7590,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H249" t="n">
         <v>21000</v>
@@ -7619,7 +7619,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H250" t="n">
         <v>17500</v>
@@ -7706,7 +7706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818675041199</v>
+        <v>2.82818651199341</v>
       </c>
       <c r="H253" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503673553467</v>
+        <v>2.85503625869751</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7822,7 +7822,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553654670715</v>
       </c>
       <c r="H257" t="n">
         <v>19000</v>
@@ -7880,7 +7880,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H259" t="n">
         <v>10000</v>
@@ -7909,7 +7909,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H260" t="n">
         <v>9500</v>
@@ -7938,7 +7938,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H261" t="n">
         <v>7000</v>
@@ -7967,7 +7967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -7996,7 +7996,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H263" t="n">
         <v>6500</v>
@@ -8025,7 +8025,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G264" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553654670715</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H266" t="n">
         <v>18500</v>
@@ -8112,7 +8112,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8199,7 +8199,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H270" t="n">
         <v>8500</v>
@@ -8257,7 +8257,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H272" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8315,7 +8315,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553654670715</v>
       </c>
       <c r="H275" t="n">
         <v>5500</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H276" t="n">
         <v>5000</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8460,7 +8460,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8721,7 +8721,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8779,7 +8779,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498706817627</v>
+        <v>2.68498730659485</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H297" t="n">
         <v>1000</v>
@@ -9011,7 +9011,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H298" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>2.75658702850342</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H306" t="n">
         <v>500</v>
@@ -9272,7 +9272,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H307" t="n">
         <v>3000</v>
@@ -9359,7 +9359,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763703346252</v>
       </c>
       <c r="H310" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653807640076</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9591,7 +9591,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.61338758468628</v>
+        <v>2.6133873462677</v>
       </c>
       <c r="H318" t="n">
         <v>18500</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758760452271</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9678,7 +9678,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178738594055</v>
+        <v>2.54178786277771</v>
       </c>
       <c r="H321" t="n">
         <v>7000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758760452271</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758760452271</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653807640076</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708755493164</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758760452271</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -9997,7 +9997,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.50598788261414</v>
+        <v>2.50598812103271</v>
       </c>
       <c r="H332" t="n">
         <v>30000</v>
@@ -10055,7 +10055,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>2.51953387260437</v>
+        <v>2.51953411102295</v>
       </c>
       <c r="H334" t="n">
         <v>1500</v>
@@ -10084,7 +10084,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.51050329208374</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H335" t="n">
         <v>37500</v>
@@ -10113,7 +10113,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G336" t="n">
-        <v>2.43825888633728</v>
+        <v>2.4382586479187</v>
       </c>
       <c r="H336" t="n">
         <v>29000</v>
@@ -10142,7 +10142,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H337" t="n">
         <v>69000</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H338" t="n">
         <v>33500</v>
@@ -10200,7 +10200,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H339" t="n">
         <v>66500</v>
@@ -10229,7 +10229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>2.41116690635681</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H340" t="n">
         <v>4000</v>
@@ -10345,7 +10345,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H344" t="n">
         <v>11500</v>
@@ -10403,7 +10403,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H346" t="n">
         <v>18500</v>
@@ -10461,7 +10461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49244260787964</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H348" t="n">
         <v>11000</v>
@@ -10490,7 +10490,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.51050329208374</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H349" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>2.49244260787964</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147271156311</v>
+        <v>2.50147294998169</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.47438144683838</v>
+        <v>2.4743812084198</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310574531555</v>
+        <v>2.39310598373413</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310574531555</v>
+        <v>2.39310598373413</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H358" t="n">
         <v>7000</v>
@@ -10780,7 +10780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10809,7 +10809,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H361" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H362" t="n">
         <v>500</v>
@@ -10896,7 +10896,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G363" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -10954,7 +10954,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H366" t="n">
         <v>2500</v>
@@ -11012,7 +11012,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989144325256</v>
       </c>
       <c r="H368" t="n">
         <v>1000</v>
@@ -11128,7 +11128,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49244260787964</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45632004737854</v>
+        <v>2.45631980895996</v>
       </c>
       <c r="H372" t="n">
         <v>2000</v>
@@ -11215,7 +11215,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G374" t="n">
-        <v>2.41116690635681</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H374" t="n">
         <v>9500</v>
@@ -11244,7 +11244,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>2.41116690635681</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H378" t="n">
         <v>1500</v>
@@ -11389,7 +11389,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>2.34795308113098</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H380" t="n">
         <v>5000</v>
@@ -11476,7 +11476,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30280017852783</v>
+        <v>2.30279994010925</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.29376935958862</v>
+        <v>2.29376912117004</v>
       </c>
       <c r="H384" t="n">
         <v>11500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11679,7 +11679,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11853,7 +11853,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.1673412322998</v>
+        <v>2.16734099388123</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11882,7 +11882,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>2.11315774917603</v>
+        <v>2.11315751075745</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.15831065177917</v>
+        <v>2.1583104133606</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H403" t="n">
         <v>8500</v>
@@ -12085,7 +12085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12143,7 +12143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H406" t="n">
         <v>1500</v>
@@ -12172,7 +12172,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H407" t="n">
         <v>7500</v>
@@ -12201,7 +12201,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H408" t="n">
         <v>12000</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12346,7 +12346,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800436973572</v>
       </c>
       <c r="H413" t="n">
         <v>15500</v>
@@ -12404,7 +12404,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800436973572</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060706138611</v>
+        <v>1.95060694217682</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12491,7 +12491,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.8512704372406</v>
+        <v>1.85127055644989</v>
       </c>
       <c r="H418" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12549,7 +12549,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G420" t="n">
-        <v>1.81514811515808</v>
+        <v>1.81514823436737</v>
       </c>
       <c r="H420" t="n">
         <v>9000</v>
@@ -12723,7 +12723,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652698993683</v>
+        <v>1.33652710914612</v>
       </c>
       <c r="H426" t="n">
         <v>7000</v>
@@ -12781,7 +12781,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G428" t="n">
-        <v>1.21912944316864</v>
+        <v>1.21912932395935</v>
       </c>
       <c r="H428" t="n">
         <v>7500</v>
@@ -12810,7 +12810,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G429" t="n">
-        <v>1.18300700187683</v>
+        <v>1.18300712108612</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364473342896</v>
+        <v>1.22364485263824</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12897,7 +12897,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.2326751947403</v>
+        <v>1.23267531394958</v>
       </c>
       <c r="H432" t="n">
         <v>2500</v>
@@ -12926,7 +12926,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G433" t="n">
-        <v>1.2642822265625</v>
+        <v>1.26428234577179</v>
       </c>
       <c r="H433" t="n">
         <v>6000</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846582889557</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846582889557</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13187,7 +13187,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49004709720612</v>
+        <v>1.49004697799683</v>
       </c>
       <c r="H442" t="n">
         <v>13000</v>
@@ -13274,7 +13274,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099027633667</v>
+        <v>1.62099051475525</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G446" t="n">
-        <v>1.62550580501556</v>
+        <v>1.62550592422485</v>
       </c>
       <c r="H446" t="n">
         <v>8500</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259754657745</v>
+        <v>1.65259766578674</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162824630737</v>
+        <v>1.66162836551666</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290335178375</v>
+        <v>1.74290359020233</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13506,7 +13506,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611765384674</v>
+        <v>1.80611753463745</v>
       </c>
       <c r="H453" t="n">
         <v>9500</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160224437714</v>
+        <v>1.80160236358643</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13564,7 +13564,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902579307556</v>
+        <v>1.77902591228485</v>
       </c>
       <c r="H455" t="n">
         <v>4500</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>
@@ -13622,7 +13622,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030113697052</v>
+        <v>1.86030089855194</v>
       </c>
       <c r="H457" t="n">
         <v>7500</v>
@@ -13680,7 +13680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8512704372406</v>
+        <v>1.85127055644989</v>
       </c>
       <c r="H459" t="n">
         <v>6500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984966754913</v>
+        <v>1.75984978675842</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13738,7 +13738,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67757093906403</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H461" t="n">
         <v>31000</v>
@@ -13767,7 +13767,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157908916473</v>
       </c>
       <c r="H462" t="n">
         <v>23000</v>
@@ -13796,7 +13796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>1.57243728637695</v>
+        <v>1.57243716716766</v>
       </c>
       <c r="H463" t="n">
         <v>9500</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13883,7 +13883,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H466" t="n">
         <v>7500</v>
@@ -13941,7 +13941,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H468" t="n">
         <v>1000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H473" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.67757093906403</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H475" t="n">
         <v>12000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14202,7 +14202,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G477" t="n">
-        <v>1.70956826210022</v>
+        <v>1.70956838130951</v>
       </c>
       <c r="H477" t="n">
         <v>2000</v>
@@ -14231,7 +14231,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G478" t="n">
-        <v>1.70956826210022</v>
+        <v>1.70956838130951</v>
       </c>
       <c r="H478" t="n">
         <v>1000</v>
@@ -14260,7 +14260,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871042251587</v>
+        <v>1.71871030330658</v>
       </c>
       <c r="H479" t="n">
         <v>1000</v>
@@ -14289,7 +14289,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H480" t="n">
         <v>4000</v>
@@ -14318,7 +14318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G481" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897796630859</v>
+        <v>1.92897808551788</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14463,7 +14463,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G486" t="n">
-        <v>1.82384419441223</v>
+        <v>1.82384431362152</v>
       </c>
       <c r="H486" t="n">
         <v>9500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412559986115</v>
+        <v>1.87412571907043</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14521,7 +14521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.80098903179169</v>
+        <v>1.80098915100098</v>
       </c>
       <c r="H488" t="n">
         <v>7500</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326776027679</v>
+        <v>1.88326752185822</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14579,7 +14579,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841539382935</v>
+        <v>1.82841527462006</v>
       </c>
       <c r="H490" t="n">
         <v>500</v>
@@ -14608,7 +14608,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83755731582642</v>
+        <v>1.83755743503571</v>
       </c>
       <c r="H491" t="n">
         <v>2000</v>
@@ -14637,7 +14637,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.83755731582642</v>
+        <v>1.83755743503571</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G493" t="n">
-        <v>1.82384419441223</v>
+        <v>1.82384431362152</v>
       </c>
       <c r="H493" t="n">
         <v>1500</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841539382935</v>
+        <v>1.82841527462006</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270494937897</v>
+        <v>1.78270506858826</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G498" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H498" t="n">
         <v>2000</v>
@@ -14840,7 +14840,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G499" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -14869,7 +14869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H500" t="n">
         <v>2000</v>
@@ -14898,7 +14898,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613642692566</v>
       </c>
       <c r="H502" t="n">
         <v>5000</v>
@@ -14956,7 +14956,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H503" t="n">
         <v>500</v>
@@ -14985,7 +14985,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H507" t="n">
         <v>500</v>
@@ -15101,7 +15101,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G509" t="n">
-        <v>1.76442062854767</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H509" t="n">
         <v>3500</v>
@@ -15159,7 +15159,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G510" t="n">
-        <v>1.76442062854767</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G511" t="n">
-        <v>1.76442062854767</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H511" t="n">
         <v>500</v>
@@ -15304,7 +15304,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871042251587</v>
+        <v>1.71871030330658</v>
       </c>
       <c r="H515" t="n">
         <v>1000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.7552787065506</v>
+        <v>1.75527882575989</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15507,7 +15507,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G522" t="n">
-        <v>1.5952924489975</v>
+        <v>1.59529232978821</v>
       </c>
       <c r="H522" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15710,7 +15710,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.64100253582001</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64100253582001</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.64100253582001</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.64100253582001</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157908916473</v>
       </c>
       <c r="H546" t="n">
         <v>2500</v>
@@ -16377,7 +16377,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16406,7 +16406,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G554" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H554" t="n">
         <v>2000</v>
@@ -16464,7 +16464,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H556" t="n">
         <v>1000</v>
@@ -16522,7 +16522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G557" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643157482147</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643157482147</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643157482147</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16696,7 +16696,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67299997806549</v>
+        <v>1.67300009727478</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16725,7 +16725,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157908916473</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G566" t="n">
-        <v>1.51758468151093</v>
+        <v>1.51758480072021</v>
       </c>
       <c r="H566" t="n">
         <v>10000</v>
@@ -16812,7 +16812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157908916473</v>
       </c>
       <c r="H567" t="n">
         <v>4000</v>
@@ -16841,7 +16841,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157908916473</v>
       </c>
       <c r="H568" t="n">
         <v>3500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -17044,7 +17044,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H575" t="n">
         <v>16500</v>
@@ -17102,7 +17102,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G577" t="n">
-        <v>1.7872759103775</v>
+        <v>1.78727602958679</v>
       </c>
       <c r="H577" t="n">
         <v>17500</v>
@@ -17131,7 +17131,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242342472076</v>
+        <v>1.73242354393005</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17334,7 +17334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.63287806510925</v>
+        <v>1.63287794589996</v>
       </c>
       <c r="H585" t="n">
         <v>1500</v>
@@ -17392,7 +17392,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154541015625</v>
+        <v>1.52154529094696</v>
       </c>
       <c r="H587" t="n">
         <v>6500</v>
@@ -17421,7 +17421,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H588" t="n">
         <v>11500</v>
@@ -17450,7 +17450,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H589" t="n">
         <v>500</v>
@@ -17508,7 +17508,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G591" t="n">
-        <v>1.48443448543549</v>
+        <v>1.48443460464478</v>
       </c>
       <c r="H591" t="n">
         <v>9500</v>
@@ -17537,7 +17537,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G592" t="n">
-        <v>1.48443448543549</v>
+        <v>1.48443460464478</v>
       </c>
       <c r="H592" t="n">
         <v>5000</v>
@@ -17624,7 +17624,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>1.44732356071472</v>
+        <v>1.44732367992401</v>
       </c>
       <c r="H595" t="n">
         <v>10500</v>
@@ -17653,7 +17653,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G596" t="n">
-        <v>1.45660150051117</v>
+        <v>1.45660138130188</v>
       </c>
       <c r="H596" t="n">
         <v>5000</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.45660150051117</v>
+        <v>1.45660138130188</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.57721173763275</v>
+        <v>1.57721161842346</v>
       </c>
       <c r="H599" t="n">
         <v>3500</v>
@@ -17798,7 +17798,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>1.57721173763275</v>
+        <v>1.57721161842346</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>1.66998875141144</v>
+        <v>1.66998887062073</v>
       </c>
       <c r="H603" t="n">
         <v>14500</v>
@@ -17914,7 +17914,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.80915462970734</v>
+        <v>1.80915451049805</v>
       </c>
       <c r="H605" t="n">
         <v>13000</v>
@@ -18001,7 +18001,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048716545105</v>
+        <v>1.92048704624176</v>
       </c>
       <c r="H608" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.91120946407318</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18059,7 +18059,7 @@
         <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H610" t="n">
         <v>9500</v>
@@ -18117,7 +18117,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78596019744873</v>
+        <v>1.78596031665802</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78596019744873</v>
+        <v>1.78596031665802</v>
       </c>
       <c r="H613" t="n">
         <v>2000</v>
@@ -18204,7 +18204,7 @@
         <v>2</v>
       </c>
       <c r="G615" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H615" t="n">
         <v>4000</v>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="G616" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H616" t="n">
         <v>2000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.91120946407318</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.91120946407318</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.91120946407318</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2</v>
       </c>
       <c r="G621" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H621" t="n">
         <v>3500</v>
@@ -18407,7 +18407,7 @@
         <v>2</v>
       </c>
       <c r="G622" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H622" t="n">
         <v>500</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820844650269</v>
+        <v>2.07820820808411</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.91120946407318</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18552,7 +18552,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832015037537</v>
+        <v>1.94832026958466</v>
       </c>
       <c r="H627" t="n">
         <v>8500</v>
@@ -18581,7 +18581,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326417922974</v>
+        <v>2.01326441764832</v>
       </c>
       <c r="H628" t="n">
         <v>10500</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748602867126</v>
+        <v>2.08748626708984</v>
       </c>
       <c r="H629" t="n">
         <v>42500</v>
@@ -18697,7 +18697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>2.91320300102234</v>
+        <v>2.91320276260376</v>
       </c>
       <c r="H632" t="n">
         <v>262000</v>
@@ -18755,7 +18755,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H634" t="n">
         <v>177500</v>
@@ -18784,7 +18784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H635" t="n">
         <v>49500</v>
@@ -18813,7 +18813,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G636" t="n">
-        <v>2.84825873374939</v>
+        <v>2.84825849533081</v>
       </c>
       <c r="H636" t="n">
         <v>10500</v>
@@ -18842,7 +18842,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G637" t="n">
-        <v>2.84825873374939</v>
+        <v>2.84825849533081</v>
       </c>
       <c r="H637" t="n">
         <v>39500</v>
@@ -18929,7 +18929,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H640" t="n">
         <v>8500</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.52353882789612</v>
+        <v>2.52353858947754</v>
       </c>
       <c r="H641" t="n">
         <v>36000</v>
@@ -19074,7 +19074,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H645" t="n">
         <v>22000</v>
@@ -19103,7 +19103,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G646" t="n">
-        <v>2.6534264087677</v>
+        <v>2.65342664718628</v>
       </c>
       <c r="H646" t="n">
         <v>31000</v>
@@ -19190,7 +19190,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>2.59776020050049</v>
+        <v>2.59776067733765</v>
       </c>
       <c r="H649" t="n">
         <v>14500</v>
@@ -19422,7 +19422,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H657" t="n">
         <v>9000</v>
@@ -19451,7 +19451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H658" t="n">
         <v>16500</v>
@@ -19915,7 +19915,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57920479774475</v>
+        <v>2.57920503616333</v>
       </c>
       <c r="H674" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57920479774475</v>
+        <v>2.57920503616333</v>
       </c>
       <c r="H675" t="n">
         <v>12000</v>
@@ -20002,7 +20002,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.69053745269775</v>
+        <v>2.69053769111633</v>
       </c>
       <c r="H677" t="n">
         <v>14000</v>
@@ -20118,7 +20118,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H681" t="n">
         <v>13000</v>
@@ -20147,7 +20147,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G682" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H682" t="n">
         <v>23000</v>
@@ -20292,7 +20292,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G687" t="n">
-        <v>2.89464712142944</v>
+        <v>2.89464735984802</v>
       </c>
       <c r="H687" t="n">
         <v>18500</v>
@@ -20408,7 +20408,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H691" t="n">
         <v>110000</v>
@@ -20553,7 +20553,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>2.89464712142944</v>
+        <v>2.89464735984802</v>
       </c>
       <c r="H696" t="n">
         <v>8000</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -20901,7 +20901,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.0430908203125</v>
+        <v>3.04309058189392</v>
       </c>
       <c r="H708" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>2.96886897087097</v>
+        <v>2.96886920928955</v>
       </c>
       <c r="H710" t="n">
         <v>2000</v>
@@ -20988,7 +20988,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.0430908203125</v>
+        <v>3.04309058189392</v>
       </c>
       <c r="H711" t="n">
         <v>6000</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H748" t="n">
         <v>24500</v>
@@ -22264,7 +22264,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H755" t="n">
         <v>1000</v>
@@ -22351,7 +22351,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H758" t="n">
         <v>11500</v>
@@ -22380,7 +22380,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G759" t="n">
-        <v>3.44853568077087</v>
+        <v>3.44853544235229</v>
       </c>
       <c r="H759" t="n">
         <v>35500</v>
@@ -22438,7 +22438,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H761" t="n">
         <v>24000</v>
@@ -22496,7 +22496,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H763" t="n">
         <v>3500</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H766" t="n">
         <v>11000</v>
@@ -22641,7 +22641,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H768" t="n">
         <v>7000</v>
@@ -23221,7 +23221,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H788" t="n">
         <v>5000</v>
@@ -23279,7 +23279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23685,7 +23685,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H804" t="n">
         <v>29000</v>
@@ -23743,7 +23743,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H806" t="n">
         <v>15000</v>
@@ -23801,7 +23801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H808" t="n">
         <v>6500</v>
@@ -23859,7 +23859,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H810" t="n">
         <v>3500</v>
@@ -24033,7 +24033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H816" t="n">
         <v>44000</v>
@@ -24149,7 +24149,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.90080237388611</v>
+        <v>3.90080213546753</v>
       </c>
       <c r="H820" t="n">
         <v>408000</v>
@@ -24236,7 +24236,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H823" t="n">
         <v>29000</v>
@@ -24265,7 +24265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H824" t="n">
         <v>23500</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25396,7 +25396,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.97618007659912</v>
+        <v>3.9761803150177</v>
       </c>
       <c r="H863" t="n">
         <v>58000</v>
@@ -25425,7 +25425,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H864" t="n">
         <v>12000</v>
@@ -25541,7 +25541,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H868" t="n">
         <v>16000</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -26498,7 +26498,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G901" t="n">
-        <v>5.37066984176636</v>
+        <v>5.37067031860352</v>
       </c>
       <c r="H901" t="n">
         <v>172500</v>
@@ -26672,7 +26672,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H907" t="n">
         <v>170500</v>
@@ -26904,7 +26904,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H915" t="n">
         <v>16000</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H916" t="n">
         <v>26000</v>
@@ -27281,7 +27281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G928" t="n">
-        <v>4.44729137420654</v>
+        <v>4.4472918510437</v>
       </c>
       <c r="H928" t="n">
         <v>9000</v>
@@ -27368,7 +27368,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5616021156311</v>
+        <v>3.56160235404968</v>
       </c>
       <c r="H931" t="n">
         <v>72500</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.9384913444519</v>
+        <v>3.93849086761475</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.8819580078125</v>
+        <v>3.88195776939392</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27542,7 +27542,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H937" t="n">
         <v>12000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -28093,7 +28093,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G956" t="n">
-        <v>4.56978034973145</v>
+        <v>4.5697808265686</v>
       </c>
       <c r="H956" t="n">
         <v>1500</v>
@@ -28151,7 +28151,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H958" t="n">
         <v>36500</v>
@@ -28180,7 +28180,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G959" t="n">
-        <v>4.1928915977478</v>
+        <v>4.19289112091064</v>
       </c>
       <c r="H959" t="n">
         <v>3000</v>
@@ -28209,7 +28209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G960" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H960" t="n">
         <v>42500</v>
@@ -28267,7 +28267,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G962" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635778427124</v>
       </c>
       <c r="H962" t="n">
         <v>2500</v>
@@ -28325,7 +28325,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G964" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H964" t="n">
         <v>7000</v>
@@ -28383,7 +28383,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404699325562</v>
+        <v>4.17404747009277</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28412,7 +28412,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G967" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H967" t="n">
         <v>4000</v>
@@ -28441,7 +28441,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>4.43787002563477</v>
+        <v>4.43786954879761</v>
       </c>
       <c r="H968" t="n">
         <v>7500</v>
@@ -28499,7 +28499,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>4.43787002563477</v>
+        <v>4.43786954879761</v>
       </c>
       <c r="H970" t="n">
         <v>14000</v>
@@ -28615,7 +28615,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G974" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H974" t="n">
         <v>4500</v>
@@ -28673,7 +28673,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G976" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H976" t="n">
         <v>20000</v>
@@ -28702,7 +28702,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G977" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H977" t="n">
         <v>5500</v>
@@ -28760,7 +28760,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G979" t="n">
-        <v>3.96998429298401</v>
+        <v>3.96998381614685</v>
       </c>
       <c r="H979" t="n">
         <v>6500</v>
@@ -28847,7 +28847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H982" t="n">
         <v>5500</v>
@@ -28876,7 +28876,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H985" t="n">
         <v>2500</v>
@@ -29021,7 +29021,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H988" t="n">
         <v>2500</v>
@@ -29050,7 +29050,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G989" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H989" t="n">
         <v>4000</v>
@@ -29137,7 +29137,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G992" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H992" t="n">
         <v>2500</v>
@@ -29166,7 +29166,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G993" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H993" t="n">
         <v>500</v>
@@ -29253,7 +29253,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G996" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H996" t="n">
         <v>2500</v>
@@ -29340,7 +29340,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G999" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1000" t="n">
         <v>12000</v>
@@ -29398,7 +29398,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1001" t="n">
         <v>16000</v>
@@ -29601,7 +29601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29688,7 +29688,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.29760408401489</v>
+        <v>4.29760456085205</v>
       </c>
       <c r="H1011" t="n">
         <v>8500</v>
@@ -29804,7 +29804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1015" t="n">
         <v>2500</v>
@@ -29862,7 +29862,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1017" t="n">
         <v>2000</v>
@@ -30065,7 +30065,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1024" t="n">
         <v>6500</v>
@@ -30326,7 +30326,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1033" t="n">
         <v>19500</v>
@@ -30355,7 +30355,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1034" t="n">
         <v>2000</v>
@@ -30442,7 +30442,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.37469148635864</v>
+        <v>4.37469100952148</v>
       </c>
       <c r="H1037" t="n">
         <v>1500</v>
@@ -30500,7 +30500,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1039" t="n">
         <v>6500</v>
@@ -30819,7 +30819,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1050" t="n">
         <v>1000</v>
@@ -30848,7 +30848,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1051" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1059" t="n">
         <v>1500</v>
@@ -31254,7 +31254,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1065" t="n">
         <v>20000</v>
@@ -31312,7 +31312,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1067" t="n">
         <v>9000</v>
@@ -31370,7 +31370,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1069" t="n">
         <v>2000</v>
@@ -31399,7 +31399,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1070" t="n">
         <v>8000</v>
@@ -31486,7 +31486,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1073" t="n">
         <v>35000</v>
@@ -31573,7 +31573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1076" t="n">
         <v>27000</v>
@@ -31602,7 +31602,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.44001054763794</v>
+        <v>3.44001078605652</v>
       </c>
       <c r="H1077" t="n">
         <v>17000</v>
@@ -31805,7 +31805,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1084" t="n">
         <v>6000</v>
@@ -31834,7 +31834,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1085" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1092" t="n">
         <v>13500</v>
@@ -32095,7 +32095,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1094" t="n">
         <v>15500</v>
@@ -32124,7 +32124,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1095" t="n">
         <v>19500</v>
@@ -32240,7 +32240,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1099" t="n">
         <v>3000</v>
@@ -32269,7 +32269,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1100" t="n">
         <v>4000</v>
@@ -32298,7 +32298,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1101" t="n">
         <v>7500</v>
@@ -32327,7 +32327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1102" t="n">
         <v>12000</v>
@@ -32356,7 +32356,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1103" t="n">
         <v>10000</v>
@@ -32443,7 +32443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1106" t="n">
         <v>17000</v>
@@ -32472,7 +32472,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1107" t="n">
         <v>5500</v>
@@ -32530,7 +32530,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1109" t="n">
         <v>6000</v>
@@ -32559,7 +32559,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.07597923278809</v>
+        <v>4.07597875595093</v>
       </c>
       <c r="H1110" t="n">
         <v>8500</v>
@@ -32588,7 +32588,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1111" t="n">
         <v>9000</v>
@@ -32617,7 +32617,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1112" t="n">
         <v>6500</v>
@@ -32762,7 +32762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1117" t="n">
         <v>2000</v>
@@ -32849,7 +32849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.95071268081665</v>
+        <v>3.95071244239807</v>
       </c>
       <c r="H1120" t="n">
         <v>4500</v>
@@ -33226,7 +33226,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1133" t="n">
         <v>1000</v>
@@ -33458,7 +33458,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1141" t="n">
         <v>4500</v>
@@ -33487,7 +33487,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1143" t="n">
         <v>2500</v>
@@ -33545,7 +33545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1144" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1144" t="n">
         <v>6500</v>
@@ -33574,7 +33574,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1145" t="n">
         <v>11500</v>
@@ -33632,7 +33632,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1147" t="n">
         <v>1000</v>
@@ -33748,7 +33748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1151" t="n">
         <v>2500</v>
@@ -33806,7 +33806,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1153" t="n">
         <v>109500</v>
@@ -33922,7 +33922,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.58668088912964</v>
+        <v>4.5866813659668</v>
       </c>
       <c r="H1157" t="n">
         <v>17000</v>
@@ -33951,7 +33951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1158" t="n">
         <v>41000</v>
@@ -34067,7 +34067,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1162" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1164" t="n">
         <v>18000</v>
@@ -34154,7 +34154,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.73121881484985</v>
+        <v>4.73121929168701</v>
       </c>
       <c r="H1165" t="n">
         <v>25000</v>
@@ -34299,7 +34299,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1170" t="n">
         <v>4500</v>
@@ -34328,7 +34328,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1171" t="n">
         <v>9000</v>
@@ -34386,7 +34386,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.63486051559448</v>
+        <v>4.63486003875732</v>
       </c>
       <c r="H1173" t="n">
         <v>7500</v>
@@ -34502,7 +34502,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1177" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1177" t="n">
         <v>3500</v>
@@ -34618,7 +34618,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1181" t="n">
         <v>4500</v>
@@ -34966,7 +34966,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1193" t="n">
         <v>7000</v>
@@ -34995,7 +34995,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1194" t="n">
         <v>2000</v>
@@ -35053,7 +35053,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1196" t="n">
         <v>3000</v>
@@ -35140,7 +35140,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1199" t="n">
         <v>4500</v>
@@ -35169,7 +35169,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1200" t="n">
         <v>2000</v>
@@ -35198,7 +35198,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H1201" t="n">
         <v>4000</v>
@@ -35227,7 +35227,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1202" t="n">
         <v>1000</v>
@@ -35285,7 +35285,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1204" t="n">
         <v>17500</v>
@@ -35517,7 +35517,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1212" t="n">
         <v>13000</v>
@@ -35546,7 +35546,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1213" t="n">
         <v>7000</v>
@@ -35604,7 +35604,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1215" t="n">
         <v>6500</v>
@@ -35633,7 +35633,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1216" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1217" t="n">
         <v>6000</v>
@@ -35691,7 +35691,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.27833223342896</v>
+        <v>4.27833271026611</v>
       </c>
       <c r="H1218" t="n">
         <v>11500</v>
@@ -35720,7 +35720,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1219" t="n">
         <v>36500</v>
@@ -35749,7 +35749,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1220" t="n">
         <v>5000</v>
@@ -35865,7 +35865,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1224" t="n">
         <v>6000</v>
@@ -35894,7 +35894,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1225" t="n">
         <v>8000</v>
@@ -35952,7 +35952,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1227" t="n">
         <v>15500</v>
@@ -61391,6 +61391,64 @@
         <v>0</v>
       </c>
       <c r="I2104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2105" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2106" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614658355713</v>
+        <v>3.59614682197571</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709630012512</v>
+        <v>3.74709606170654</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244806289673</v>
+        <v>3.52244782447815</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -543,7 +543,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42743849754333</v>
+        <v>3.42743825912476</v>
       </c>
       <c r="H6" t="n">
         <v>110500</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.34752416610718</v>
+        <v>3.3475239276886</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274496078491</v>
+        <v>3.45274448394775</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -630,7 +630,7 @@
         <v>3.83100008964539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40168833732605</v>
+        <v>3.40168857574463</v>
       </c>
       <c r="H9" t="n">
         <v>35000</v>
@@ -659,7 +659,7 @@
         <v>3.71050000190735</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29469180107117</v>
+        <v>3.29469203948975</v>
       </c>
       <c r="H10" t="n">
         <v>88500</v>
@@ -746,7 +746,7 @@
         <v>3.57049989700317</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17038083076477</v>
+        <v>3.17038059234619</v>
       </c>
       <c r="H13" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881560325623</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -891,7 +891,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416501998901</v>
+        <v>3.16416525840759</v>
       </c>
       <c r="H18" t="n">
         <v>39500</v>
@@ -949,7 +949,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18725156784058</v>
+        <v>3.187251329422</v>
       </c>
       <c r="H20" t="n">
         <v>214000</v>
@@ -978,7 +978,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898717880249</v>
+        <v>3.01898741722107</v>
       </c>
       <c r="H21" t="n">
         <v>50500</v>
@@ -1007,7 +1007,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H22" t="n">
         <v>26500</v>
@@ -1094,7 +1094,7 @@
         <v>3.3289999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.9559440612793</v>
+        <v>2.95594382286072</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875729560852</v>
+        <v>2.81875777244568</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1239,7 +1239,7 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H30" t="n">
         <v>45000</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1326,7 +1326,7 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1384,7 +1384,7 @@
         <v>3.37450003623962</v>
       </c>
       <c r="G35" t="n">
-        <v>2.99634480476379</v>
+        <v>2.99634504318237</v>
       </c>
       <c r="H35" t="n">
         <v>78000</v>
@@ -1413,7 +1413,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325849533081</v>
+        <v>2.97325897216797</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1616,7 +1616,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.91687488555908</v>
+        <v>2.91687440872192</v>
       </c>
       <c r="H43" t="n">
         <v>3000</v>
@@ -1674,7 +1674,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8862407207489</v>
+        <v>2.88624095916748</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1790,7 +1790,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H49" t="n">
         <v>4000</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.91687488555908</v>
+        <v>2.91687440872192</v>
       </c>
       <c r="H50" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.0944619178772</v>
+        <v>3.09446167945862</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1935,7 +1935,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08114337921143</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H54" t="n">
         <v>61000</v>
@@ -1964,7 +1964,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G55" t="n">
-        <v>3.13441896438599</v>
+        <v>3.13441920280457</v>
       </c>
       <c r="H55" t="n">
         <v>45500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868745803833</v>
+        <v>3.29868769645691</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2109,7 +2109,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873041152954</v>
+        <v>3.25873064994812</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881560325623</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2167,7 +2167,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H62" t="n">
         <v>25500</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678897857666</v>
+        <v>2.99678874015808</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2283,7 +2283,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G66" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H66" t="n">
         <v>20500</v>
@@ -2312,7 +2312,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94351291656494</v>
+        <v>2.94351243972778</v>
       </c>
       <c r="H67" t="n">
         <v>40000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247776985168</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H68" t="n">
         <v>23500</v>
@@ -2370,7 +2370,7 @@
         <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H69" t="n">
         <v>15500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7348473072052</v>
+        <v>2.73484754562378</v>
       </c>
       <c r="H71" t="n">
         <v>17500</v>
@@ -2457,7 +2457,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820903778076</v>
+        <v>2.70820927619934</v>
       </c>
       <c r="H72" t="n">
         <v>15500</v>
@@ -2486,7 +2486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.7348473072052</v>
+        <v>2.73484754562378</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2602,7 +2602,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.92131400108337</v>
+        <v>2.92131376266479</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459030151367</v>
+        <v>2.97459053993225</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H89" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670307159424</v>
+        <v>3.07670331001282</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3037,7 +3037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.17437648773193</v>
+        <v>3.17437624931335</v>
       </c>
       <c r="H92" t="n">
         <v>19000</v>
@@ -3124,7 +3124,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.03230667114258</v>
+        <v>3.03230619430542</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881560325623</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545411109924</v>
+        <v>3.20545434951782</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3414,7 +3414,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.08114337921143</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H105" t="n">
         <v>22500</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674650192261</v>
+        <v>3.03674602508545</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3501,7 +3501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898717880249</v>
+        <v>3.01898741722107</v>
       </c>
       <c r="H108" t="n">
         <v>6000</v>
@@ -3530,7 +3530,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>2.94351291656494</v>
+        <v>2.94351243972778</v>
       </c>
       <c r="H109" t="n">
         <v>24500</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.97015070915222</v>
+        <v>2.9701509475708</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3617,7 +3617,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G112" t="n">
-        <v>2.83696031570435</v>
+        <v>2.83696007728577</v>
       </c>
       <c r="H112" t="n">
         <v>8500</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023637771606</v>
+        <v>2.89023685455322</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.25</v>
       </c>
       <c r="G116" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.84583926200867</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H117" t="n">
         <v>11500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915851593018</v>
+        <v>2.85915875434875</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3907,7 +3907,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>2.83696031570435</v>
+        <v>2.83696007728577</v>
       </c>
       <c r="H122" t="n">
         <v>2000</v>
@@ -3936,7 +3936,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H123" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.672691822052</v>
+        <v>2.67269158363342</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4342,7 +4342,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G137" t="n">
-        <v>2.71264886856079</v>
+        <v>2.71264910697937</v>
       </c>
       <c r="H137" t="n">
         <v>7500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471892356873</v>
+        <v>2.85471868515015</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.79700326919556</v>
+        <v>2.7970027923584</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4922,7 +4922,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.79700326919556</v>
+        <v>2.7970027923584</v>
       </c>
       <c r="H157" t="n">
         <v>7500</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76148557662964</v>
+        <v>2.76148533821106</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5241,7 +5241,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.79700326919556</v>
+        <v>2.7970027923584</v>
       </c>
       <c r="H168" t="n">
         <v>12500</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144286155701</v>
+        <v>2.80144262313843</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596764564514</v>
+        <v>2.7259681224823</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5589,7 +5589,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H180" t="n">
         <v>5000</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5647,7 +5647,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>2.84583926200867</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H182" t="n">
         <v>18500</v>
@@ -5705,7 +5705,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247776985168</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H184" t="n">
         <v>28000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596764564514</v>
+        <v>2.7259681224823</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260591506958</v>
+        <v>2.752605676651</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6024,7 +6024,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>2.79700326919556</v>
+        <v>2.7970027923584</v>
       </c>
       <c r="H195" t="n">
         <v>500</v>
@@ -6053,7 +6053,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>2.79700326919556</v>
+        <v>2.7970027923584</v>
       </c>
       <c r="H196" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588245391846</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6285,7 +6285,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H204" t="n">
         <v>3500</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6488,7 +6488,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H211" t="n">
         <v>5000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6546,7 +6546,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H213" t="n">
         <v>37000</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H215" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G219" t="n">
-        <v>2.76553654670715</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H219" t="n">
         <v>9000</v>
@@ -6807,7 +6807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H222" t="n">
         <v>11500</v>
@@ -6836,7 +6836,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H223" t="n">
         <v>2500</v>
@@ -6865,7 +6865,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H224" t="n">
         <v>13000</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -6981,7 +6981,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H228" t="n">
         <v>36000</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.59548783302307</v>
+        <v>2.59548807144165</v>
       </c>
       <c r="H230" t="n">
         <v>18500</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7097,7 +7097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H232" t="n">
         <v>32000</v>
@@ -7155,7 +7155,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H234" t="n">
         <v>21000</v>
@@ -7184,7 +7184,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H235" t="n">
         <v>8000</v>
@@ -7213,7 +7213,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H236" t="n">
         <v>3500</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813708305359</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813708305359</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7416,7 +7416,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H243" t="n">
         <v>17500</v>
@@ -7445,7 +7445,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7503,7 +7503,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H246" t="n">
         <v>6000</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7619,7 +7619,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H250" t="n">
         <v>17500</v>
@@ -7706,7 +7706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818651199341</v>
+        <v>2.82818698883057</v>
       </c>
       <c r="H253" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503625869751</v>
+        <v>2.85503649711609</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7793,7 +7793,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G256" t="n">
-        <v>2.8460865020752</v>
+        <v>2.84608674049377</v>
       </c>
       <c r="H256" t="n">
         <v>7000</v>
@@ -7822,7 +7822,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76553654670715</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H257" t="n">
         <v>19000</v>
@@ -7851,7 +7851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133676528931</v>
+        <v>2.80133700370789</v>
       </c>
       <c r="H258" t="n">
         <v>14000</v>
@@ -7880,7 +7880,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H259" t="n">
         <v>10000</v>
@@ -7909,7 +7909,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H260" t="n">
         <v>9500</v>
@@ -7967,7 +7967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8025,7 +8025,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G264" t="n">
-        <v>2.76553654670715</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8257,7 +8257,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H272" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8315,7 +8315,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76553654670715</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H275" t="n">
         <v>5500</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448678016663</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H276" t="n">
         <v>5000</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H282" t="n">
         <v>1500</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8779,7 +8779,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498730659485</v>
+        <v>2.68498706817627</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8837,7 +8837,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H292" t="n">
         <v>1500</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8895,7 +8895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G294" t="n">
-        <v>2.70288705825806</v>
+        <v>2.70288729667664</v>
       </c>
       <c r="H294" t="n">
         <v>500</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -9156,7 +9156,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H303" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H308" t="n">
         <v>3500</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9388,7 +9388,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.58653807640076</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9533,7 +9533,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.59548783302307</v>
+        <v>2.59548807144165</v>
       </c>
       <c r="H316" t="n">
         <v>2500</v>
@@ -9562,7 +9562,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.5596878528595</v>
+        <v>2.55968761444092</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9591,7 +9591,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.6133873462677</v>
+        <v>2.61338806152344</v>
       </c>
       <c r="H318" t="n">
         <v>18500</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758760452271</v>
+        <v>2.57758831977844</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G320" t="n">
-        <v>2.5596878528595</v>
+        <v>2.55968761444092</v>
       </c>
       <c r="H320" t="n">
         <v>61000</v>
@@ -9678,7 +9678,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178786277771</v>
+        <v>2.54178762435913</v>
       </c>
       <c r="H321" t="n">
         <v>7000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758760452271</v>
+        <v>2.57758831977844</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G323" t="n">
-        <v>2.55073761940002</v>
+        <v>2.5507378578186</v>
       </c>
       <c r="H323" t="n">
         <v>1500</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758760452271</v>
+        <v>2.57758831977844</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.58653807640076</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.59548783302307</v>
+        <v>2.59548807144165</v>
       </c>
       <c r="H327" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.59548783302307</v>
+        <v>2.59548807144165</v>
       </c>
       <c r="H328" t="n">
         <v>6500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9939,7 +9939,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H330" t="n">
         <v>6000</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758760452271</v>
+        <v>2.57758831977844</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -9997,7 +9997,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.50598812103271</v>
+        <v>2.50598788261414</v>
       </c>
       <c r="H332" t="n">
         <v>30000</v>
@@ -10026,7 +10026,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.5646870136261</v>
+        <v>2.56468653678894</v>
       </c>
       <c r="H333" t="n">
         <v>8500</v>
@@ -10142,7 +10142,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601400375366</v>
       </c>
       <c r="H337" t="n">
         <v>69000</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.3118302822113</v>
+        <v>2.31183052062988</v>
       </c>
       <c r="H338" t="n">
         <v>33500</v>
@@ -10229,7 +10229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116666793823</v>
       </c>
       <c r="H340" t="n">
         <v>4000</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.3840754032135</v>
+        <v>2.38407564163208</v>
       </c>
       <c r="H342" t="n">
         <v>3000</v>
@@ -10316,7 +10316,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G343" t="n">
-        <v>2.3840754032135</v>
+        <v>2.38407564163208</v>
       </c>
       <c r="H343" t="n">
         <v>26500</v>
@@ -10345,7 +10345,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601400375366</v>
       </c>
       <c r="H344" t="n">
         <v>11500</v>
@@ -10374,7 +10374,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.3840754032135</v>
+        <v>2.38407564163208</v>
       </c>
       <c r="H345" t="n">
         <v>3500</v>
@@ -10403,7 +10403,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H346" t="n">
         <v>18500</v>
@@ -10432,7 +10432,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G347" t="n">
-        <v>2.3840754032135</v>
+        <v>2.38407564163208</v>
       </c>
       <c r="H347" t="n">
         <v>13000</v>
@@ -10548,7 +10548,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147294998169</v>
+        <v>2.50147271156311</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.4743812084198</v>
+        <v>2.47438097000122</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -10780,7 +10780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10809,7 +10809,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H361" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H362" t="n">
         <v>500</v>
@@ -10896,7 +10896,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G363" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601400375366</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -10954,7 +10954,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601400375366</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>2.32989144325256</v>
+        <v>2.32989192008972</v>
       </c>
       <c r="H368" t="n">
         <v>1000</v>
@@ -11070,7 +11070,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.3840754032135</v>
+        <v>2.38407564163208</v>
       </c>
       <c r="H369" t="n">
         <v>16500</v>
@@ -11215,7 +11215,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G374" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116666793823</v>
       </c>
       <c r="H374" t="n">
         <v>9500</v>
@@ -11244,7 +11244,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116666793823</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.42922830581665</v>
+        <v>2.42922806739807</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601400375366</v>
       </c>
       <c r="H378" t="n">
         <v>1500</v>
@@ -11418,7 +11418,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H381" t="n">
         <v>6000</v>
@@ -11447,7 +11447,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H382" t="n">
         <v>2500</v>
@@ -11476,7 +11476,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30279994010925</v>
+        <v>2.30279970169067</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.29376912117004</v>
+        <v>2.29376935958862</v>
       </c>
       <c r="H384" t="n">
         <v>11500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11621,7 +11621,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H388" t="n">
         <v>5000</v>
@@ -11679,7 +11679,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861621856689</v>
+        <v>2.24861669540405</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11853,7 +11853,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.16734099388123</v>
+        <v>2.1673412322998</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11882,7 +11882,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>2.11315751075745</v>
+        <v>2.11315774917603</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.1583104133606</v>
+        <v>2.15831065177917</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11940,7 +11940,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.18540263175964</v>
+        <v>2.18540239334106</v>
       </c>
       <c r="H399" t="n">
         <v>18500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H403" t="n">
         <v>8500</v>
@@ -12085,7 +12085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12143,7 +12143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H406" t="n">
         <v>1500</v>
@@ -12172,7 +12172,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861621856689</v>
+        <v>2.24861669540405</v>
       </c>
       <c r="H407" t="n">
         <v>7500</v>
@@ -12201,7 +12201,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.3118302822113</v>
+        <v>2.31183052062988</v>
       </c>
       <c r="H408" t="n">
         <v>12000</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764679908752</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12259,7 +12259,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12346,7 +12346,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.06800436973572</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H413" t="n">
         <v>15500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703518867493</v>
+        <v>2.07703542709351</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12404,7 +12404,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.06800436973572</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99575984477997</v>
+        <v>1.99576008319855</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060694217682</v>
+        <v>1.95060706138611</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12491,7 +12491,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.85127055644989</v>
+        <v>1.85127031803131</v>
       </c>
       <c r="H418" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642333984375</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12578,7 +12578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G421" t="n">
-        <v>1.77451050281525</v>
+        <v>1.77451062202454</v>
       </c>
       <c r="H421" t="n">
         <v>12000</v>
@@ -12607,7 +12607,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G422" t="n">
-        <v>1.64356696605682</v>
+        <v>1.64356708526611</v>
       </c>
       <c r="H422" t="n">
         <v>46500</v>
@@ -12636,7 +12636,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G423" t="n">
-        <v>1.47198593616486</v>
+        <v>1.47198581695557</v>
       </c>
       <c r="H423" t="n">
         <v>9500</v>
@@ -12665,7 +12665,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H424" t="n">
         <v>3000</v>
@@ -12694,7 +12694,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H425" t="n">
         <v>5000</v>
@@ -12723,7 +12723,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652710914612</v>
+        <v>1.33652698993683</v>
       </c>
       <c r="H426" t="n">
         <v>7000</v>
@@ -12752,7 +12752,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12810,7 +12810,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G429" t="n">
-        <v>1.18300712108612</v>
+        <v>1.18300700187683</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.2100989818573</v>
+        <v>1.21009886264801</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364485263824</v>
+        <v>1.22364473342896</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12926,7 +12926,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G433" t="n">
-        <v>1.26428234577179</v>
+        <v>1.2642822265625</v>
       </c>
       <c r="H433" t="n">
         <v>6000</v>
@@ -12955,7 +12955,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H434" t="n">
         <v>11500</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846582889557</v>
+        <v>1.31846606731415</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846582889557</v>
+        <v>1.31846606731415</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13071,7 +13071,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>1.2958892583847</v>
+        <v>1.29588937759399</v>
       </c>
       <c r="H438" t="n">
         <v>7000</v>
@@ -13100,7 +13100,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H439" t="n">
         <v>5000</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.60292935371399</v>
+        <v>1.6029292345047</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13303,7 +13303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G446" t="n">
-        <v>1.62550592422485</v>
+        <v>1.62550580501556</v>
       </c>
       <c r="H446" t="n">
         <v>8500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162836551666</v>
+        <v>1.66162812709808</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13419,7 +13419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H450" t="n">
         <v>30500</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290359020233</v>
+        <v>1.74290335178375</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13477,7 +13477,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H452" t="n">
         <v>5000</v>
@@ -13506,7 +13506,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611753463745</v>
+        <v>1.80611765384674</v>
       </c>
       <c r="H453" t="n">
         <v>9500</v>
@@ -13564,7 +13564,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902591228485</v>
+        <v>1.77902579307556</v>
       </c>
       <c r="H455" t="n">
         <v>4500</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642333984375</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>
@@ -13622,7 +13622,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030089855194</v>
+        <v>1.86030101776123</v>
       </c>
       <c r="H457" t="n">
         <v>7500</v>
@@ -13680,7 +13680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.85127055644989</v>
+        <v>1.85127031803131</v>
       </c>
       <c r="H459" t="n">
         <v>6500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984978675842</v>
+        <v>1.75984966754913</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13738,7 +13738,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H461" t="n">
         <v>31000</v>
@@ -13767,7 +13767,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157908916473</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H462" t="n">
         <v>23000</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13883,7 +13883,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H466" t="n">
         <v>7500</v>
@@ -13941,7 +13941,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H468" t="n">
         <v>1000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H473" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H475" t="n">
         <v>12000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14260,7 +14260,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871054172516</v>
       </c>
       <c r="H479" t="n">
         <v>1000</v>
@@ -14289,7 +14289,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H480" t="n">
         <v>4000</v>
@@ -14318,7 +14318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G481" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897808551788</v>
+        <v>1.92897820472717</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412571907043</v>
+        <v>1.87412548065186</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14521,7 +14521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.80098915100098</v>
+        <v>1.80098903179169</v>
       </c>
       <c r="H488" t="n">
         <v>7500</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326752185822</v>
+        <v>1.88326776027679</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14579,7 +14579,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H490" t="n">
         <v>500</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270506858826</v>
+        <v>1.78270494937897</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14753,7 +14753,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G496" t="n">
-        <v>1.77813398838043</v>
+        <v>1.77813386917114</v>
       </c>
       <c r="H496" t="n">
         <v>7500</v>
@@ -14782,7 +14782,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.77813398838043</v>
+        <v>1.77813386917114</v>
       </c>
       <c r="H497" t="n">
         <v>2000</v>
@@ -14811,7 +14811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G498" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H498" t="n">
         <v>2000</v>
@@ -14840,7 +14840,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G499" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -14869,7 +14869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H500" t="n">
         <v>2000</v>
@@ -14898,7 +14898,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74613642692566</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H502" t="n">
         <v>5000</v>
@@ -14956,7 +14956,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070762634277</v>
+        <v>1.75070750713348</v>
       </c>
       <c r="H503" t="n">
         <v>500</v>
@@ -14985,7 +14985,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070762634277</v>
+        <v>1.75070750713348</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.74156546592712</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.74156546592712</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H507" t="n">
         <v>500</v>
@@ -15101,7 +15101,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.74156546592712</v>
+        <v>1.74156558513641</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G509" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H509" t="n">
         <v>3500</v>
@@ -15159,7 +15159,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G510" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G511" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H511" t="n">
         <v>500</v>
@@ -15304,7 +15304,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871054172516</v>
       </c>
       <c r="H515" t="n">
         <v>1000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75527882575989</v>
+        <v>1.75527858734131</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15710,7 +15710,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157908916473</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H546" t="n">
         <v>2500</v>
@@ -16261,7 +16261,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072136878967</v>
+        <v>1.59072148799896</v>
       </c>
       <c r="H548" t="n">
         <v>9500</v>
@@ -16522,7 +16522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G557" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16725,7 +16725,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157908916473</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G566" t="n">
-        <v>1.51758480072021</v>
+        <v>1.51758468151093</v>
       </c>
       <c r="H566" t="n">
         <v>10000</v>
@@ -16812,7 +16812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157908916473</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H567" t="n">
         <v>4000</v>
@@ -16841,7 +16841,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157908916473</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H568" t="n">
         <v>3500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -17015,7 +17015,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H574" t="n">
         <v>500</v>
@@ -17044,7 +17044,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.64557385444641</v>
+        <v>1.64557373523712</v>
       </c>
       <c r="H575" t="n">
         <v>16500</v>
@@ -17131,7 +17131,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242354393005</v>
+        <v>1.73242330551147</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214201927185</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17247,7 +17247,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H582" t="n">
         <v>5500</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17363,7 +17363,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360024452209</v>
+        <v>1.62360036373138</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17421,7 +17421,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937839508057</v>
+        <v>1.54937851428986</v>
       </c>
       <c r="H588" t="n">
         <v>11500</v>
@@ -17450,7 +17450,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937839508057</v>
+        <v>1.54937851428986</v>
       </c>
       <c r="H589" t="n">
         <v>500</v>
@@ -17740,7 +17740,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H599" t="n">
         <v>3500</v>
@@ -17798,7 +17798,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360024452209</v>
+        <v>1.62360036373138</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18059,7 +18059,7 @@
         <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>1.85554325580597</v>
+        <v>1.85554313659668</v>
       </c>
       <c r="H610" t="n">
         <v>9500</v>
@@ -18117,7 +18117,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78596031665802</v>
+        <v>1.78596019744873</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78596031665802</v>
+        <v>1.78596019744873</v>
       </c>
       <c r="H613" t="n">
         <v>2000</v>
@@ -18175,7 +18175,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>1.81843233108521</v>
+        <v>1.81843221187592</v>
       </c>
       <c r="H614" t="n">
         <v>4000</v>
@@ -18204,7 +18204,7 @@
         <v>2</v>
       </c>
       <c r="G615" t="n">
-        <v>1.85554325580597</v>
+        <v>1.85554313659668</v>
       </c>
       <c r="H615" t="n">
         <v>4000</v>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="G616" t="n">
-        <v>1.85554325580597</v>
+        <v>1.85554313659668</v>
       </c>
       <c r="H616" t="n">
         <v>2000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2</v>
       </c>
       <c r="G621" t="n">
-        <v>1.85554325580597</v>
+        <v>1.85554313659668</v>
       </c>
       <c r="H621" t="n">
         <v>3500</v>
@@ -18407,7 +18407,7 @@
         <v>2</v>
       </c>
       <c r="G622" t="n">
-        <v>1.85554325580597</v>
+        <v>1.85554313659668</v>
       </c>
       <c r="H622" t="n">
         <v>500</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820820808411</v>
+        <v>2.07820844650269</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615337371826</v>
+        <v>1.97615349292755</v>
       </c>
       <c r="H625" t="n">
         <v>14000</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18552,7 +18552,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832026958466</v>
+        <v>1.94832015037537</v>
       </c>
       <c r="H627" t="n">
         <v>8500</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748626708984</v>
+        <v>2.08748602867126</v>
       </c>
       <c r="H629" t="n">
         <v>42500</v>
@@ -18668,7 +18668,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>2.45859479904175</v>
+        <v>2.45859503746033</v>
       </c>
       <c r="H631" t="n">
         <v>119500</v>
@@ -18726,7 +18726,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H633" t="n">
         <v>86500</v>
@@ -18755,7 +18755,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H634" t="n">
         <v>177500</v>
@@ -18784,7 +18784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H635" t="n">
         <v>49500</v>
@@ -18871,7 +18871,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H638" t="n">
         <v>15500</v>
@@ -18900,7 +18900,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H639" t="n">
         <v>1000</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.52353858947754</v>
+        <v>2.5235390663147</v>
       </c>
       <c r="H641" t="n">
         <v>36000</v>
@@ -19074,7 +19074,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68126010894775</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H645" t="n">
         <v>22000</v>
@@ -19190,7 +19190,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>2.59776067733765</v>
+        <v>2.59776043891907</v>
       </c>
       <c r="H649" t="n">
         <v>14500</v>
@@ -19219,7 +19219,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.54209423065186</v>
+        <v>2.54209399223328</v>
       </c>
       <c r="H650" t="n">
         <v>4500</v>
@@ -19306,7 +19306,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H653" t="n">
         <v>19500</v>
@@ -19335,7 +19335,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H654" t="n">
         <v>24000</v>
@@ -19364,7 +19364,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H655" t="n">
         <v>36500</v>
@@ -19393,7 +19393,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G656" t="n">
-        <v>2.32870674133301</v>
+        <v>2.32870650291443</v>
       </c>
       <c r="H656" t="n">
         <v>47500</v>
@@ -19422,7 +19422,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>2.30087327957153</v>
+        <v>2.30087351799011</v>
       </c>
       <c r="H657" t="n">
         <v>9000</v>
@@ -19451,7 +19451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.30087327957153</v>
+        <v>2.30087351799011</v>
       </c>
       <c r="H658" t="n">
         <v>16500</v>
@@ -19538,7 +19538,7 @@
         <v>2.5</v>
       </c>
       <c r="G661" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H661" t="n">
         <v>210500</v>
@@ -19567,7 +19567,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>2.40292835235596</v>
+        <v>2.40292811393738</v>
       </c>
       <c r="H662" t="n">
         <v>38500</v>
@@ -19596,7 +19596,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220569610596</v>
       </c>
       <c r="H663" t="n">
         <v>11500</v>
@@ -19683,7 +19683,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>2.32870674133301</v>
+        <v>2.32870650291443</v>
       </c>
       <c r="H666" t="n">
         <v>5000</v>
@@ -19712,7 +19712,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G667" t="n">
-        <v>2.40292835235596</v>
+        <v>2.40292811393738</v>
       </c>
       <c r="H667" t="n">
         <v>9500</v>
@@ -19741,7 +19741,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220569610596</v>
       </c>
       <c r="H668" t="n">
         <v>14000</v>
@@ -19799,7 +19799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H670" t="n">
         <v>4500</v>
@@ -19828,7 +19828,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H671" t="n">
         <v>8000</v>
@@ -19857,7 +19857,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.60703802108765</v>
+        <v>2.60703825950623</v>
       </c>
       <c r="H673" t="n">
         <v>48500</v>
@@ -19973,7 +19973,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>2.60703802108765</v>
+        <v>2.60703825950623</v>
       </c>
       <c r="H676" t="n">
         <v>27000</v>
@@ -20002,7 +20002,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.69053769111633</v>
+        <v>2.69053745269775</v>
       </c>
       <c r="H677" t="n">
         <v>14000</v>
@@ -20060,7 +20060,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>2.76475930213928</v>
+        <v>2.7647590637207</v>
       </c>
       <c r="H679" t="n">
         <v>15500</v>
@@ -20089,7 +20089,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764849662781</v>
+        <v>2.72764873504639</v>
       </c>
       <c r="H680" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.68126010894775</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H681" t="n">
         <v>13000</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970333099365</v>
+        <v>2.82970309257507</v>
       </c>
       <c r="H683" t="n">
         <v>121000</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20263,7 +20263,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>2.81114768981934</v>
+        <v>2.81114792823792</v>
       </c>
       <c r="H686" t="n">
         <v>1000</v>
@@ -20321,7 +20321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G688" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G690" t="n">
-        <v>2.9317581653595</v>
+        <v>2.93175840377808</v>
       </c>
       <c r="H690" t="n">
         <v>16000</v>
@@ -20408,7 +20408,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H691" t="n">
         <v>110000</v>
@@ -20437,7 +20437,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H692" t="n">
         <v>52500</v>
@@ -20466,7 +20466,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H693" t="n">
         <v>128500</v>
@@ -20495,7 +20495,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G694" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H694" t="n">
         <v>12500</v>
@@ -20785,7 +20785,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.08020162582397</v>
+        <v>3.0802013874054</v>
       </c>
       <c r="H704" t="n">
         <v>200500</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -21046,7 +21046,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>3.02453541755676</v>
+        <v>3.02453517913818</v>
       </c>
       <c r="H713" t="n">
         <v>6500</v>
@@ -21104,7 +21104,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H715" t="n">
         <v>6000</v>
@@ -21133,7 +21133,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G716" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H716" t="n">
         <v>4000</v>
@@ -21191,7 +21191,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G718" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H718" t="n">
         <v>500</v>
@@ -21220,7 +21220,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H719" t="n">
         <v>500</v>
@@ -21336,7 +21336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G723" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H723" t="n">
         <v>2000</v>
@@ -21394,7 +21394,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G725" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H725" t="n">
         <v>11500</v>
@@ -21423,7 +21423,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H726" t="n">
         <v>5500</v>
@@ -21452,7 +21452,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G727" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H727" t="n">
         <v>8500</v>
@@ -21597,7 +21597,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G732" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H732" t="n">
         <v>4000</v>
@@ -21655,7 +21655,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>3.03395748138428</v>
+        <v>3.03395771980286</v>
       </c>
       <c r="H734" t="n">
         <v>5500</v>
@@ -21742,7 +21742,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H737" t="n">
         <v>1000</v>
@@ -21800,7 +21800,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G739" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H739" t="n">
         <v>21500</v>
@@ -21945,7 +21945,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H744" t="n">
         <v>4000</v>
@@ -22061,7 +22061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H748" t="n">
         <v>24500</v>
@@ -22148,7 +22148,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H751" t="n">
         <v>37000</v>
@@ -22177,7 +22177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H752" t="n">
         <v>5500</v>
@@ -22206,7 +22206,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>3.22240233421326</v>
+        <v>3.22240209579468</v>
       </c>
       <c r="H753" t="n">
         <v>11000</v>
@@ -22235,7 +22235,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G754" t="n">
-        <v>3.22240233421326</v>
+        <v>3.22240209579468</v>
       </c>
       <c r="H754" t="n">
         <v>4000</v>
@@ -22322,7 +22322,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H757" t="n">
         <v>24500</v>
@@ -22380,7 +22380,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G759" t="n">
-        <v>3.44853544235229</v>
+        <v>3.44853568077087</v>
       </c>
       <c r="H759" t="n">
         <v>35500</v>
@@ -22409,7 +22409,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>3.3731575012207</v>
+        <v>3.37315773963928</v>
       </c>
       <c r="H760" t="n">
         <v>17000</v>
@@ -22467,7 +22467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H762" t="n">
         <v>12000</v>
@@ -22525,7 +22525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>3.3731575012207</v>
+        <v>3.37315773963928</v>
       </c>
       <c r="H764" t="n">
         <v>6000</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H766" t="n">
         <v>11000</v>
@@ -22815,7 +22815,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G774" t="n">
-        <v>3.03395748138428</v>
+        <v>3.03395771980286</v>
       </c>
       <c r="H774" t="n">
         <v>192500</v>
@@ -22844,7 +22844,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>3.07164645195007</v>
+        <v>3.07164621353149</v>
       </c>
       <c r="H775" t="n">
         <v>84000</v>
@@ -22873,7 +22873,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G776" t="n">
-        <v>3.07164645195007</v>
+        <v>3.07164621353149</v>
       </c>
       <c r="H776" t="n">
         <v>8500</v>
@@ -22902,7 +22902,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H777" t="n">
         <v>10000</v>
@@ -22931,7 +22931,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>3.07164645195007</v>
+        <v>3.07164621353149</v>
       </c>
       <c r="H778" t="n">
         <v>7500</v>
@@ -22989,7 +22989,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H780" t="n">
         <v>4000</v>
@@ -23163,7 +23163,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H786" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H787" t="n">
         <v>7000</v>
@@ -23308,7 +23308,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23453,7 +23453,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G796" t="n">
-        <v>3.03395748138428</v>
+        <v>3.03395771980286</v>
       </c>
       <c r="H796" t="n">
         <v>7500</v>
@@ -23482,7 +23482,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G797" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H797" t="n">
         <v>16500</v>
@@ -23540,7 +23540,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>3.03395748138428</v>
+        <v>3.03395771980286</v>
       </c>
       <c r="H799" t="n">
         <v>5000</v>
@@ -23685,7 +23685,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H804" t="n">
         <v>29000</v>
@@ -23743,7 +23743,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H806" t="n">
         <v>15000</v>
@@ -23801,7 +23801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H808" t="n">
         <v>6500</v>
@@ -23830,7 +23830,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H809" t="n">
         <v>14500</v>
@@ -23859,7 +23859,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H810" t="n">
         <v>3500</v>
@@ -23975,7 +23975,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G814" t="n">
-        <v>2.97742414474487</v>
+        <v>2.97742438316345</v>
       </c>
       <c r="H814" t="n">
         <v>6000</v>
@@ -24033,7 +24033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H816" t="n">
         <v>44000</v>
@@ -24091,7 +24091,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H818" t="n">
         <v>30500</v>
@@ -24120,7 +24120,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H819" t="n">
         <v>13000</v>
@@ -24149,7 +24149,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G820" t="n">
-        <v>3.90080213546753</v>
+        <v>3.90080237388611</v>
       </c>
       <c r="H820" t="n">
         <v>408000</v>
@@ -24178,7 +24178,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>3.69351363182068</v>
+        <v>3.6935133934021</v>
       </c>
       <c r="H821" t="n">
         <v>295500</v>
@@ -24236,7 +24236,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H823" t="n">
         <v>29000</v>
@@ -24265,7 +24265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H824" t="n">
         <v>23500</v>
@@ -24816,7 +24816,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H843" t="n">
         <v>32000</v>
@@ -24903,7 +24903,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>4.29653596878052</v>
+        <v>4.29653644561768</v>
       </c>
       <c r="H846" t="n">
         <v>21500</v>
@@ -24961,7 +24961,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H848" t="n">
         <v>22000</v>
@@ -25019,7 +25019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>4.29653596878052</v>
+        <v>4.29653644561768</v>
       </c>
       <c r="H850" t="n">
         <v>12000</v>
@@ -25106,7 +25106,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H856" t="n">
         <v>4500</v>
@@ -25280,7 +25280,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H859" t="n">
         <v>13000</v>
@@ -25309,7 +25309,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502444267273</v>
+        <v>3.99502468109131</v>
       </c>
       <c r="H860" t="n">
         <v>49000</v>
@@ -25396,7 +25396,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.9761803150177</v>
+        <v>3.97618007659912</v>
       </c>
       <c r="H863" t="n">
         <v>58000</v>
@@ -25425,7 +25425,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H864" t="n">
         <v>12000</v>
@@ -25483,7 +25483,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H866" t="n">
         <v>18000</v>
@@ -25512,7 +25512,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H867" t="n">
         <v>13500</v>
@@ -25541,7 +25541,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H868" t="n">
         <v>16000</v>
@@ -25599,7 +25599,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.16462469100952</v>
+        <v>4.16462516784668</v>
       </c>
       <c r="H870" t="n">
         <v>19500</v>
@@ -25628,7 +25628,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>4.16462469100952</v>
+        <v>4.16462516784668</v>
       </c>
       <c r="H871" t="n">
         <v>14500</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H875" t="n">
         <v>6500</v>
@@ -25802,7 +25802,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>4.27769136428833</v>
+        <v>4.27769184112549</v>
       </c>
       <c r="H877" t="n">
         <v>60000</v>
@@ -25860,7 +25860,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37191390991211</v>
+        <v>4.37191343307495</v>
       </c>
       <c r="H879" t="n">
         <v>147000</v>
@@ -25889,7 +25889,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G880" t="n">
-        <v>4.40960264205933</v>
+        <v>4.40960311889648</v>
       </c>
       <c r="H880" t="n">
         <v>51000</v>
@@ -25976,7 +25976,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G883" t="n">
-        <v>4.29653596878052</v>
+        <v>4.29653644561768</v>
       </c>
       <c r="H883" t="n">
         <v>17500</v>
@@ -26005,7 +26005,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G884" t="n">
-        <v>4.29653596878052</v>
+        <v>4.29653644561768</v>
       </c>
       <c r="H884" t="n">
         <v>13000</v>
@@ -26063,7 +26063,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>4.40960264205933</v>
+        <v>4.40960311889648</v>
       </c>
       <c r="H886" t="n">
         <v>17000</v>
@@ -26179,7 +26179,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G890" t="n">
-        <v>4.5792031288147</v>
+        <v>4.57920360565186</v>
       </c>
       <c r="H890" t="n">
         <v>18500</v>
@@ -26208,7 +26208,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>4.5792031288147</v>
+        <v>4.57920360565186</v>
       </c>
       <c r="H891" t="n">
         <v>18000</v>
@@ -26266,7 +26266,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>4.5792031288147</v>
+        <v>4.57920360565186</v>
       </c>
       <c r="H893" t="n">
         <v>19500</v>
@@ -26295,7 +26295,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>4.48498106002808</v>
+        <v>4.48498058319092</v>
       </c>
       <c r="H894" t="n">
         <v>6500</v>
@@ -26382,7 +26382,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G897" t="n">
-        <v>4.37191390991211</v>
+        <v>4.37191343307495</v>
       </c>
       <c r="H897" t="n">
         <v>7500</v>
@@ -26411,7 +26411,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G898" t="n">
-        <v>4.48498106002808</v>
+        <v>4.48498058319092</v>
       </c>
       <c r="H898" t="n">
         <v>11500</v>
@@ -26498,7 +26498,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G901" t="n">
-        <v>5.37067031860352</v>
+        <v>5.37066984176636</v>
       </c>
       <c r="H901" t="n">
         <v>172500</v>
@@ -26556,7 +26556,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H903" t="n">
         <v>32500</v>
@@ -26672,7 +26672,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H907" t="n">
         <v>170500</v>
@@ -26817,7 +26817,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H912" t="n">
         <v>14000</v>
@@ -26904,7 +26904,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H915" t="n">
         <v>16000</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H916" t="n">
         <v>26000</v>
@@ -26962,7 +26962,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H917" t="n">
         <v>61000</v>
@@ -26991,7 +26991,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H918" t="n">
         <v>13000</v>
@@ -27020,7 +27020,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08800363540649</v>
+        <v>5.08800315856934</v>
       </c>
       <c r="H919" t="n">
         <v>26500</v>
@@ -27049,7 +27049,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H920" t="n">
         <v>12500</v>
@@ -27107,7 +27107,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H922" t="n">
         <v>5000</v>
@@ -27426,7 +27426,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>3.65582466125488</v>
+        <v>3.65582489967346</v>
       </c>
       <c r="H933" t="n">
         <v>9000</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.93849086761475</v>
+        <v>3.93849158287048</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.88195776939392</v>
+        <v>3.8819580078125</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502444267273</v>
+        <v>3.99502468109131</v>
       </c>
       <c r="H936" t="n">
         <v>4500</v>
@@ -27542,7 +27542,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H937" t="n">
         <v>12000</v>
@@ -27600,7 +27600,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H939" t="n">
         <v>8000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27658,7 +27658,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H941" t="n">
         <v>3500</v>
@@ -27687,7 +27687,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>4.27769136428833</v>
+        <v>4.27769184112549</v>
       </c>
       <c r="H942" t="n">
         <v>6500</v>
@@ -27716,7 +27716,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>4.27769136428833</v>
+        <v>4.27769184112549</v>
       </c>
       <c r="H943" t="n">
         <v>2000</v>
@@ -27745,7 +27745,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H944" t="n">
         <v>3500</v>
@@ -27774,7 +27774,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G945" t="n">
-        <v>4.40960264205933</v>
+        <v>4.40960311889648</v>
       </c>
       <c r="H945" t="n">
         <v>6500</v>
@@ -27890,7 +27890,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H949" t="n">
         <v>30500</v>
@@ -27977,7 +27977,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880313873291</v>
+        <v>4.74880266189575</v>
       </c>
       <c r="H952" t="n">
         <v>8000</v>
@@ -28267,7 +28267,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G962" t="n">
-        <v>4.13635778427124</v>
+        <v>4.1363582611084</v>
       </c>
       <c r="H962" t="n">
         <v>2500</v>
@@ -28557,7 +28557,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G972" t="n">
-        <v>4.54151439666748</v>
+        <v>4.54151391983032</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28673,7 +28673,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G976" t="n">
-        <v>4.02779912948608</v>
+        <v>4.02779960632324</v>
       </c>
       <c r="H976" t="n">
         <v>20000</v>
@@ -28702,7 +28702,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G977" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H977" t="n">
         <v>5500</v>
@@ -28760,7 +28760,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G979" t="n">
-        <v>3.96998381614685</v>
+        <v>3.96998429298401</v>
       </c>
       <c r="H979" t="n">
         <v>6500</v>
@@ -28847,7 +28847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.03743553161621</v>
+        <v>4.03743505477905</v>
       </c>
       <c r="H982" t="n">
         <v>5500</v>
@@ -28876,7 +28876,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.03743553161621</v>
+        <v>4.03743505477905</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H985" t="n">
         <v>2500</v>
@@ -29021,7 +29021,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H988" t="n">
         <v>2500</v>
@@ -29050,7 +29050,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G989" t="n">
-        <v>4.02779912948608</v>
+        <v>4.02779960632324</v>
       </c>
       <c r="H989" t="n">
         <v>4000</v>
@@ -29137,7 +29137,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G992" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H992" t="n">
         <v>2500</v>
@@ -29166,7 +29166,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G993" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H993" t="n">
         <v>500</v>
@@ -29253,7 +29253,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G996" t="n">
-        <v>4.23015260696411</v>
+        <v>4.23015308380127</v>
       </c>
       <c r="H996" t="n">
         <v>2500</v>
@@ -29340,7 +29340,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G999" t="n">
-        <v>4.12415885925293</v>
+        <v>4.12415838241577</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.9121687412262</v>
+        <v>3.91216897964478</v>
       </c>
       <c r="H1000" t="n">
         <v>12000</v>
@@ -29398,7 +29398,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.23015260696411</v>
+        <v>4.23015308380127</v>
       </c>
       <c r="H1001" t="n">
         <v>16000</v>
@@ -29601,7 +29601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29688,7 +29688,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.29760456085205</v>
+        <v>4.29760408401489</v>
       </c>
       <c r="H1011" t="n">
         <v>8500</v>
@@ -29804,7 +29804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H1015" t="n">
         <v>2500</v>
@@ -29862,7 +29862,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.05670690536499</v>
+        <v>4.05670738220215</v>
       </c>
       <c r="H1017" t="n">
         <v>2000</v>
@@ -30065,7 +30065,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.20124530792236</v>
+        <v>4.20124578475952</v>
       </c>
       <c r="H1024" t="n">
         <v>6500</v>
@@ -30326,7 +30326,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.47105026245117</v>
+        <v>4.47104978561401</v>
       </c>
       <c r="H1033" t="n">
         <v>19500</v>
@@ -30355,7 +30355,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.39396286010742</v>
+        <v>4.39396333694458</v>
       </c>
       <c r="H1034" t="n">
         <v>2000</v>
@@ -30442,7 +30442,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.37469100952148</v>
+        <v>4.37469148635864</v>
       </c>
       <c r="H1037" t="n">
         <v>1500</v>
@@ -30500,7 +30500,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.41323518753052</v>
+        <v>4.41323471069336</v>
       </c>
       <c r="H1039" t="n">
         <v>6500</v>
@@ -30819,7 +30819,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.47105026245117</v>
+        <v>4.47104978561401</v>
       </c>
       <c r="H1050" t="n">
         <v>1000</v>
@@ -30848,7 +30848,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.50959348678589</v>
+        <v>4.50959396362305</v>
       </c>
       <c r="H1051" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.41323518753052</v>
+        <v>4.41323471069336</v>
       </c>
       <c r="H1059" t="n">
         <v>1500</v>
@@ -31254,7 +31254,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.41323518753052</v>
+        <v>4.41323471069336</v>
       </c>
       <c r="H1065" t="n">
         <v>20000</v>
@@ -31312,7 +31312,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.12415885925293</v>
+        <v>4.12415838241577</v>
       </c>
       <c r="H1067" t="n">
         <v>9000</v>
@@ -31370,7 +31370,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.9410765171051</v>
+        <v>3.94107675552368</v>
       </c>
       <c r="H1069" t="n">
         <v>2000</v>
@@ -31399,7 +31399,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.9121687412262</v>
+        <v>3.91216897964478</v>
       </c>
       <c r="H1070" t="n">
         <v>8000</v>
@@ -31486,7 +31486,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.49782586097717</v>
+        <v>3.49782609939575</v>
       </c>
       <c r="H1073" t="n">
         <v>35000</v>
@@ -31573,7 +31573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.27620053291321</v>
+        <v>3.27620077133179</v>
       </c>
       <c r="H1076" t="n">
         <v>27000</v>
@@ -31602,7 +31602,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.44001078605652</v>
+        <v>3.44001054763794</v>
       </c>
       <c r="H1077" t="n">
         <v>17000</v>
@@ -31805,7 +31805,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.27620053291321</v>
+        <v>3.27620077133179</v>
       </c>
       <c r="H1084" t="n">
         <v>6000</v>
@@ -31834,7 +31834,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.49782586097717</v>
+        <v>3.49782609939575</v>
       </c>
       <c r="H1085" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H1092" t="n">
         <v>13500</v>
@@ -32095,7 +32095,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H1094" t="n">
         <v>15500</v>
@@ -32124,7 +32124,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1095" t="n">
         <v>19500</v>
@@ -32240,7 +32240,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1099" t="n">
         <v>3000</v>
@@ -32269,7 +32269,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.12415885925293</v>
+        <v>4.12415838241577</v>
       </c>
       <c r="H1100" t="n">
         <v>4000</v>
@@ -32298,7 +32298,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1101" t="n">
         <v>7500</v>
@@ -32327,7 +32327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.08561420440674</v>
+        <v>4.0856146812439</v>
       </c>
       <c r="H1102" t="n">
         <v>12000</v>
@@ -32356,7 +32356,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1103" t="n">
         <v>10000</v>
@@ -32443,7 +32443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1106" t="n">
         <v>17000</v>
@@ -32472,7 +32472,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.12415885925293</v>
+        <v>4.12415838241577</v>
       </c>
       <c r="H1107" t="n">
         <v>5500</v>
@@ -32530,7 +32530,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1109" t="n">
         <v>6000</v>
@@ -32559,7 +32559,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.07597875595093</v>
+        <v>4.07597923278809</v>
       </c>
       <c r="H1110" t="n">
         <v>8500</v>
@@ -32588,7 +32588,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1111" t="n">
         <v>9000</v>
@@ -32617,7 +32617,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1112" t="n">
         <v>6500</v>
@@ -32762,7 +32762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1117" t="n">
         <v>2000</v>
@@ -32849,7 +32849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.95071244239807</v>
+        <v>3.95071268081665</v>
       </c>
       <c r="H1120" t="n">
         <v>4500</v>
@@ -33226,7 +33226,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.9410765171051</v>
+        <v>3.94107675552368</v>
       </c>
       <c r="H1133" t="n">
         <v>1000</v>
@@ -33458,7 +33458,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.02779912948608</v>
+        <v>4.02779960632324</v>
       </c>
       <c r="H1141" t="n">
         <v>4500</v>
@@ -33487,7 +33487,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.02779912948608</v>
+        <v>4.02779960632324</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1143" t="n">
         <v>2500</v>
@@ -33545,7 +33545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1144" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1144" t="n">
         <v>6500</v>
@@ -33574,7 +33574,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05670690536499</v>
+        <v>4.05670738220215</v>
       </c>
       <c r="H1145" t="n">
         <v>11500</v>
@@ -33632,7 +33632,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.05670690536499</v>
+        <v>4.05670738220215</v>
       </c>
       <c r="H1147" t="n">
         <v>1000</v>
@@ -33748,7 +33748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1151" t="n">
         <v>2500</v>
@@ -33806,7 +33806,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.50959348678589</v>
+        <v>4.50959396362305</v>
       </c>
       <c r="H1153" t="n">
         <v>109500</v>
@@ -33922,7 +33922,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.5866813659668</v>
+        <v>4.58668088912964</v>
       </c>
       <c r="H1157" t="n">
         <v>17000</v>
@@ -33951,7 +33951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.64449644088745</v>
+        <v>4.64449596405029</v>
       </c>
       <c r="H1158" t="n">
         <v>41000</v>
@@ -34067,7 +34067,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.76976251602173</v>
+        <v>4.76976203918457</v>
       </c>
       <c r="H1162" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.76976251602173</v>
+        <v>4.76976203918457</v>
       </c>
       <c r="H1164" t="n">
         <v>18000</v>
@@ -34154,7 +34154,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.73121929168701</v>
+        <v>4.73121881484985</v>
       </c>
       <c r="H1165" t="n">
         <v>25000</v>
@@ -34299,7 +34299,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.64449644088745</v>
+        <v>4.64449596405029</v>
       </c>
       <c r="H1170" t="n">
         <v>4500</v>
@@ -34328,7 +34328,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.64449644088745</v>
+        <v>4.64449596405029</v>
       </c>
       <c r="H1171" t="n">
         <v>9000</v>
@@ -34386,7 +34386,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.63486003875732</v>
+        <v>4.63486051559448</v>
       </c>
       <c r="H1173" t="n">
         <v>7500</v>
@@ -34502,7 +34502,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1177" t="n">
-        <v>4.54813671112061</v>
+        <v>4.54813718795776</v>
       </c>
       <c r="H1177" t="n">
         <v>3500</v>
@@ -34618,7 +34618,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.39396286010742</v>
+        <v>4.39396333694458</v>
       </c>
       <c r="H1181" t="n">
         <v>4500</v>
@@ -34966,7 +34966,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.23015260696411</v>
+        <v>4.23015308380127</v>
       </c>
       <c r="H1193" t="n">
         <v>7000</v>
@@ -34995,7 +34995,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.31687593460083</v>
+        <v>4.31687641143799</v>
       </c>
       <c r="H1194" t="n">
         <v>2000</v>
@@ -35053,7 +35053,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.20124530792236</v>
+        <v>4.20124578475952</v>
       </c>
       <c r="H1196" t="n">
         <v>3000</v>
@@ -35140,7 +35140,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1199" t="n">
         <v>4500</v>
@@ -35169,7 +35169,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.12415885925293</v>
+        <v>4.12415838241577</v>
       </c>
       <c r="H1200" t="n">
         <v>2000</v>
@@ -35198,7 +35198,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.03743553161621</v>
+        <v>4.03743505477905</v>
       </c>
       <c r="H1201" t="n">
         <v>4000</v>
@@ -35227,7 +35227,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.05670690536499</v>
+        <v>4.05670738220215</v>
       </c>
       <c r="H1202" t="n">
         <v>1000</v>
@@ -35285,7 +35285,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1204" t="n">
         <v>17500</v>
@@ -35517,7 +35517,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.54813671112061</v>
+        <v>4.54813718795776</v>
       </c>
       <c r="H1212" t="n">
         <v>13000</v>
@@ -35546,7 +35546,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.41323518753052</v>
+        <v>4.41323471069336</v>
       </c>
       <c r="H1213" t="n">
         <v>7000</v>
@@ -35604,7 +35604,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.47105026245117</v>
+        <v>4.47104978561401</v>
       </c>
       <c r="H1215" t="n">
         <v>6500</v>
@@ -35633,7 +35633,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.47105026245117</v>
+        <v>4.47104978561401</v>
       </c>
       <c r="H1216" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.39396286010742</v>
+        <v>4.39396333694458</v>
       </c>
       <c r="H1217" t="n">
         <v>6000</v>
@@ -35691,7 +35691,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.27833271026611</v>
+        <v>4.27833223342896</v>
       </c>
       <c r="H1218" t="n">
         <v>11500</v>
@@ -35720,7 +35720,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.05670690536499</v>
+        <v>4.05670738220215</v>
       </c>
       <c r="H1219" t="n">
         <v>36500</v>
@@ -35749,7 +35749,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1220" t="n">
         <v>5000</v>
@@ -35865,7 +35865,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.14343023300171</v>
+        <v>4.14343070983887</v>
       </c>
       <c r="H1224" t="n">
         <v>6000</v>
@@ -35894,7 +35894,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.31687593460083</v>
+        <v>4.31687641143799</v>
       </c>
       <c r="H1225" t="n">
         <v>8000</v>
@@ -35952,7 +35952,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.10488700866699</v>
+        <v>4.10488653182983</v>
       </c>
       <c r="H1227" t="n">
         <v>15500</v>
@@ -61449,6 +61449,35 @@
         <v>1000</v>
       </c>
       <c r="I2106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2107" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I2107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614682197571</v>
+        <v>3.59614658355713</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709606170654</v>
+        <v>3.74709582328796</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -485,7 +485,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589240074158</v>
+        <v>3.62589263916016</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244782447815</v>
+        <v>3.52244758605957</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274448394775</v>
+        <v>3.45274496078491</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -630,7 +630,7 @@
         <v>3.83100008964539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40168857574463</v>
+        <v>3.40168833732605</v>
       </c>
       <c r="H9" t="n">
         <v>35000</v>
@@ -717,7 +717,7 @@
         <v>3.65750002861023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24763131141663</v>
+        <v>3.24763083457947</v>
       </c>
       <c r="H12" t="n">
         <v>215500</v>
@@ -746,7 +746,7 @@
         <v>3.57049989700317</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17038059234619</v>
+        <v>3.17038083076477</v>
       </c>
       <c r="H13" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -1036,7 +1036,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96571087837219</v>
+        <v>2.96571111679077</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.3289999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.95594382286072</v>
+        <v>2.95594358444214</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875777244568</v>
+        <v>2.8187575340271</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1239,7 +1239,7 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H30" t="n">
         <v>45000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78812336921692</v>
+        <v>2.78812408447266</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1326,7 +1326,7 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1384,7 +1384,7 @@
         <v>3.37450003623962</v>
       </c>
       <c r="G35" t="n">
-        <v>2.99634504318237</v>
+        <v>2.99634480476379</v>
       </c>
       <c r="H35" t="n">
         <v>78000</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325897216797</v>
+        <v>2.97325849533081</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1500,7 +1500,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683193206787</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H39" t="n">
         <v>20500</v>
@@ -1529,7 +1529,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243481636047</v>
+        <v>2.91243457794189</v>
       </c>
       <c r="H40" t="n">
         <v>9500</v>
@@ -1616,7 +1616,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.91687440872192</v>
+        <v>2.9168746471405</v>
       </c>
       <c r="H43" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683193206787</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H47" t="n">
         <v>58000</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.91687440872192</v>
+        <v>2.9168746471405</v>
       </c>
       <c r="H50" t="n">
         <v>18000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.09446167945862</v>
+        <v>3.0944619178772</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08558249473572</v>
+        <v>3.0855827331543</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769502639771</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769502639771</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760983467102</v>
+        <v>3.2676100730896</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868769645691</v>
+        <v>3.29868745803833</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2109,7 +2109,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873064994812</v>
+        <v>3.25873041152954</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678874015808</v>
+        <v>2.99678897857666</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2312,7 +2312,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94351243972778</v>
+        <v>2.94351267814636</v>
       </c>
       <c r="H67" t="n">
         <v>40000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247753143311</v>
+        <v>2.87247729301453</v>
       </c>
       <c r="H68" t="n">
         <v>23500</v>
@@ -2370,7 +2370,7 @@
         <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H69" t="n">
         <v>15500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2515,7 +2515,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G74" t="n">
-        <v>2.74816656112671</v>
+        <v>2.74816632270813</v>
       </c>
       <c r="H74" t="n">
         <v>8500</v>
@@ -2544,7 +2544,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135695457458</v>
+        <v>2.88135671615601</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2573,7 +2573,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683193206787</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H76" t="n">
         <v>17000</v>
@@ -2602,7 +2602,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.92131376266479</v>
+        <v>2.92131423950195</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2631,7 +2631,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459053993225</v>
+        <v>2.97459030151367</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2718,7 +2718,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243481636047</v>
+        <v>2.91243457794189</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H85" t="n">
         <v>19000</v>
@@ -2863,7 +2863,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H86" t="n">
         <v>7000</v>
@@ -2950,7 +2950,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562544822693</v>
+        <v>3.04562568664551</v>
       </c>
       <c r="H89" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670331001282</v>
+        <v>3.07670307159424</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3037,7 +3037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.17437624931335</v>
+        <v>3.17437672615051</v>
       </c>
       <c r="H92" t="n">
         <v>19000</v>
@@ -3066,7 +3066,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213533401489</v>
+        <v>3.19213509559631</v>
       </c>
       <c r="H93" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213533401489</v>
+        <v>3.19213509559631</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562544822693</v>
+        <v>3.04562568664551</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.03230619430542</v>
+        <v>3.03230595588684</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3269,7 +3269,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334134101868</v>
+        <v>3.10334157943726</v>
       </c>
       <c r="H100" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.15217804908752</v>
+        <v>3.1521782875061</v>
       </c>
       <c r="H101" t="n">
         <v>14500</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545434951782</v>
+        <v>3.20545411109924</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674602508545</v>
+        <v>3.03674626350403</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3472,7 +3472,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>3.10778093338013</v>
+        <v>3.10778117179871</v>
       </c>
       <c r="H107" t="n">
         <v>6000</v>
@@ -3530,7 +3530,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>2.94351243972778</v>
+        <v>2.94351267814636</v>
       </c>
       <c r="H109" t="n">
         <v>24500</v>
@@ -3617,7 +3617,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G112" t="n">
-        <v>2.83696007728577</v>
+        <v>2.83696031570435</v>
       </c>
       <c r="H112" t="n">
         <v>8500</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023685455322</v>
+        <v>2.89023637771606</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.25</v>
       </c>
       <c r="G116" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.84583950042725</v>
+        <v>2.84583973884583</v>
       </c>
       <c r="H117" t="n">
         <v>11500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915875434875</v>
+        <v>2.85915851593018</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3907,7 +3907,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>2.83696007728577</v>
+        <v>2.83696031570435</v>
       </c>
       <c r="H122" t="n">
         <v>2000</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588269233704</v>
+        <v>2.8058819770813</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G137" t="n">
-        <v>2.71264910697937</v>
+        <v>2.71264886856079</v>
       </c>
       <c r="H137" t="n">
         <v>7500</v>
@@ -4400,7 +4400,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713141441345</v>
+        <v>2.67713165283203</v>
       </c>
       <c r="H139" t="n">
         <v>2500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4545,7 +4545,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H144" t="n">
         <v>72000</v>
@@ -4603,7 +4603,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G146" t="n">
-        <v>2.74816656112671</v>
+        <v>2.74816632270813</v>
       </c>
       <c r="H146" t="n">
         <v>11500</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592540740967</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471868515015</v>
+        <v>2.8547191619873</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032228469849</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4922,7 +4922,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H157" t="n">
         <v>7500</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928713798523</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5009,7 +5009,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H160" t="n">
         <v>1500</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592516899109</v>
+        <v>2.76592540740967</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5183,7 +5183,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H166" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H168" t="n">
         <v>12500</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144262313843</v>
+        <v>2.80144238471985</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5299,7 +5299,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H170" t="n">
         <v>4500</v>
@@ -5328,7 +5328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H171" t="n">
         <v>7500</v>
@@ -5357,7 +5357,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.7259681224823</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.78812336921692</v>
+        <v>2.78812408447266</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588269233704</v>
+        <v>2.8058819770813</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5647,7 +5647,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>2.84583950042725</v>
+        <v>2.84583973884583</v>
       </c>
       <c r="H182" t="n">
         <v>18500</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5705,7 +5705,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247753143311</v>
+        <v>2.87247729301453</v>
       </c>
       <c r="H184" t="n">
         <v>28000</v>
@@ -5763,7 +5763,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H186" t="n">
         <v>66000</v>
@@ -5792,7 +5792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.7259681224823</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.752605676651</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.78812336921692</v>
+        <v>2.78812408447266</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H191" t="n">
         <v>9500</v>
@@ -5937,7 +5937,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036476135254</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H195" t="n">
         <v>500</v>
@@ -6053,7 +6053,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>2.7970027923584</v>
+        <v>2.79700303077698</v>
       </c>
       <c r="H196" t="n">
         <v>3000</v>
@@ -6082,7 +6082,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H197" t="n">
         <v>10500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588269233704</v>
+        <v>2.8058819770813</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H203" t="n">
         <v>26000</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6546,7 +6546,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H213" t="n">
         <v>37000</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6662,7 +6662,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868680000305</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H217" t="n">
         <v>14000</v>
@@ -6691,7 +6691,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H218" t="n">
         <v>27500</v>
@@ -6749,7 +6749,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H220" t="n">
         <v>7000</v>
@@ -6778,7 +6778,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H221" t="n">
         <v>31000</v>
@@ -6807,7 +6807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H222" t="n">
         <v>11500</v>
@@ -6836,7 +6836,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H223" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H227" t="n">
         <v>27000</v>
@@ -6981,7 +6981,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H228" t="n">
         <v>36000</v>
@@ -7010,7 +7010,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52388787269592</v>
+        <v>2.5238881111145</v>
       </c>
       <c r="H229" t="n">
         <v>28000</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.59548807144165</v>
+        <v>2.59548759460449</v>
       </c>
       <c r="H230" t="n">
         <v>18500</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7097,7 +7097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H232" t="n">
         <v>32000</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813708305359</v>
+        <v>2.65813755989075</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813708305359</v>
+        <v>2.65813755989075</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7416,7 +7416,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H243" t="n">
         <v>17500</v>
@@ -7445,7 +7445,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7503,7 +7503,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H246" t="n">
         <v>6000</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7619,7 +7619,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H250" t="n">
         <v>17500</v>
@@ -7706,7 +7706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818698883057</v>
+        <v>2.82818627357483</v>
       </c>
       <c r="H253" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503649711609</v>
+        <v>2.85503625869751</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7764,7 +7764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>2.8102867603302</v>
+        <v>2.81028699874878</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7851,7 +7851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133700370789</v>
+        <v>2.80133676528931</v>
       </c>
       <c r="H258" t="n">
         <v>14000</v>
@@ -8083,7 +8083,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H266" t="n">
         <v>18500</v>
@@ -8199,7 +8199,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H270" t="n">
         <v>8500</v>
@@ -8228,7 +8228,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>2.78343677520752</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923651695251</v>
+        <v>2.81923675537109</v>
       </c>
       <c r="H272" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8431,7 +8431,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868680000305</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8460,7 +8460,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H282" t="n">
         <v>1500</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393706321716</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H297" t="n">
         <v>1000</v>
@@ -9011,7 +9011,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H298" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78343677520752</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H302" t="n">
         <v>19000</v>
@@ -9156,7 +9156,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H303" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H307" t="n">
         <v>3000</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H308" t="n">
         <v>3500</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763703346252</v>
+        <v>2.74763655662537</v>
       </c>
       <c r="H310" t="n">
         <v>1500</v>
@@ -9388,7 +9388,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128733634949</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9533,7 +9533,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.59548807144165</v>
+        <v>2.59548759460449</v>
       </c>
       <c r="H316" t="n">
         <v>2500</v>
@@ -9591,7 +9591,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.61338806152344</v>
+        <v>2.61338758468628</v>
       </c>
       <c r="H318" t="n">
         <v>18500</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758831977844</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9678,7 +9678,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178762435913</v>
+        <v>2.54178810119629</v>
       </c>
       <c r="H321" t="n">
         <v>7000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758831977844</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G323" t="n">
-        <v>2.5507378578186</v>
+        <v>2.55073809623718</v>
       </c>
       <c r="H323" t="n">
         <v>1500</v>
@@ -9765,7 +9765,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.60443758964539</v>
+        <v>2.60443782806396</v>
       </c>
       <c r="H324" t="n">
         <v>3000</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758831977844</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.59548807144165</v>
+        <v>2.59548759460449</v>
       </c>
       <c r="H327" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.59548807144165</v>
+        <v>2.59548759460449</v>
       </c>
       <c r="H328" t="n">
         <v>6500</v>
@@ -9939,7 +9939,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H330" t="n">
         <v>6000</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758831977844</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -10026,7 +10026,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56468653678894</v>
+        <v>2.5646870136261</v>
       </c>
       <c r="H333" t="n">
         <v>8500</v>
@@ -10084,7 +10084,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.51050353050232</v>
+        <v>2.5105037689209</v>
       </c>
       <c r="H335" t="n">
         <v>37500</v>
@@ -10113,7 +10113,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4382586479187</v>
+        <v>2.43825888633728</v>
       </c>
       <c r="H336" t="n">
         <v>29000</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H338" t="n">
         <v>33500</v>
@@ -10200,7 +10200,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H339" t="n">
         <v>66500</v>
@@ -10229,7 +10229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H340" t="n">
         <v>4000</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.38407564163208</v>
+        <v>2.38407516479492</v>
       </c>
       <c r="H342" t="n">
         <v>3000</v>
@@ -10316,7 +10316,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G343" t="n">
-        <v>2.38407564163208</v>
+        <v>2.38407516479492</v>
       </c>
       <c r="H343" t="n">
         <v>26500</v>
@@ -10374,7 +10374,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.38407564163208</v>
+        <v>2.38407516479492</v>
       </c>
       <c r="H345" t="n">
         <v>3500</v>
@@ -10432,7 +10432,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38407564163208</v>
+        <v>2.38407516479492</v>
       </c>
       <c r="H347" t="n">
         <v>13000</v>
@@ -10461,7 +10461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H348" t="n">
         <v>11000</v>
@@ -10490,7 +10490,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.51050353050232</v>
+        <v>2.5105037689209</v>
       </c>
       <c r="H349" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.47438097000122</v>
+        <v>2.47438073158264</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310574531555</v>
+        <v>2.39310598373413</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.42019772529602</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310574531555</v>
+        <v>2.39310598373413</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H358" t="n">
         <v>7000</v>
@@ -10983,7 +10983,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H366" t="n">
         <v>2500</v>
@@ -11012,7 +11012,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11070,7 +11070,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.38407564163208</v>
+        <v>2.38407516479492</v>
       </c>
       <c r="H369" t="n">
         <v>16500</v>
@@ -11099,7 +11099,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.37504482269287</v>
+        <v>2.37504458427429</v>
       </c>
       <c r="H370" t="n">
         <v>500</v>
@@ -11128,7 +11128,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49244213104248</v>
+        <v>2.49244236946106</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11186,7 +11186,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341155052185</v>
+        <v>2.48341178894043</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G374" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H374" t="n">
         <v>9500</v>
@@ -11244,7 +11244,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>2.41116666793823</v>
+        <v>2.41116714477539</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.42922806739807</v>
+        <v>2.42922830581665</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11302,7 +11302,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>2.37504482269287</v>
+        <v>2.37504458427429</v>
       </c>
       <c r="H377" t="n">
         <v>1000</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698342323303</v>
+        <v>2.35698318481445</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H380" t="n">
         <v>5000</v>
@@ -11418,7 +11418,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.33892250061035</v>
+        <v>2.33892226219177</v>
       </c>
       <c r="H381" t="n">
         <v>6000</v>
@@ -11447,7 +11447,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.33892250061035</v>
+        <v>2.33892226219177</v>
       </c>
       <c r="H382" t="n">
         <v>2500</v>
@@ -11476,7 +11476,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30279970169067</v>
+        <v>2.30280017852783</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.29376935958862</v>
+        <v>2.29376912117004</v>
       </c>
       <c r="H384" t="n">
         <v>11500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25764679908752</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11621,7 +11621,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.221524477005</v>
+        <v>2.22152471542358</v>
       </c>
       <c r="H388" t="n">
         <v>5000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11824,7 +11824,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>2.20346355438232</v>
+        <v>2.20346331596375</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.1673412322998</v>
+        <v>2.16734147071838</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11882,7 +11882,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>2.11315774917603</v>
+        <v>2.11315751075745</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249389648438</v>
+        <v>2.21249413490295</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.25764679908752</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570843696594</v>
       </c>
       <c r="H403" t="n">
         <v>8500</v>
@@ -12085,7 +12085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570843696594</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12114,7 +12114,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26667761802673</v>
+        <v>2.26667737960815</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12143,7 +12143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570819854736</v>
+        <v>2.27570843696594</v>
       </c>
       <c r="H406" t="n">
         <v>1500</v>
@@ -12201,7 +12201,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.31183052062988</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H408" t="n">
         <v>12000</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25764679908752</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12259,7 +12259,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.221524477005</v>
+        <v>2.22152471542358</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12346,7 +12346,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.06800484657288</v>
+        <v>2.0680046081543</v>
       </c>
       <c r="H413" t="n">
         <v>15500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703542709351</v>
+        <v>2.07703495025635</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12404,7 +12404,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.06800484657288</v>
+        <v>2.0680046081543</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99576008319855</v>
+        <v>1.99575984477997</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12491,7 +12491,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.85127031803131</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H418" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12665,7 +12665,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489419460297</v>
+        <v>1.44489407539368</v>
       </c>
       <c r="H424" t="n">
         <v>3000</v>
@@ -12694,7 +12694,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489419460297</v>
+        <v>1.44489407539368</v>
       </c>
       <c r="H425" t="n">
         <v>5000</v>
@@ -12723,7 +12723,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652698993683</v>
+        <v>1.33652710914612</v>
       </c>
       <c r="H426" t="n">
         <v>7000</v>
@@ -12752,7 +12752,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458815097809</v>
+        <v>1.3545880317688</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G428" t="n">
-        <v>1.21912932395935</v>
+        <v>1.21912944316864</v>
       </c>
       <c r="H428" t="n">
         <v>7500</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.21009886264801</v>
+        <v>1.2100989818573</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364473342896</v>
+        <v>1.22364449501038</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12897,7 +12897,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.23267531394958</v>
+        <v>1.2326751947403</v>
       </c>
       <c r="H432" t="n">
         <v>2500</v>
@@ -12955,7 +12955,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458815097809</v>
+        <v>1.3545880317688</v>
       </c>
       <c r="H434" t="n">
         <v>11500</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846606731415</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846606731415</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13071,7 +13071,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>1.29588937759399</v>
+        <v>1.2958892583847</v>
       </c>
       <c r="H438" t="n">
         <v>7000</v>
@@ -13100,7 +13100,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458815097809</v>
+        <v>1.3545880317688</v>
       </c>
       <c r="H439" t="n">
         <v>5000</v>
@@ -13187,7 +13187,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49004697799683</v>
+        <v>1.49004685878754</v>
       </c>
       <c r="H442" t="n">
         <v>13000</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.6029292345047</v>
+        <v>1.60292947292328</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13274,7 +13274,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099051475525</v>
+        <v>1.62099039554596</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G446" t="n">
-        <v>1.62550580501556</v>
+        <v>1.62550568580627</v>
       </c>
       <c r="H446" t="n">
         <v>8500</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259766578674</v>
+        <v>1.65259754657745</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162812709808</v>
+        <v>1.66162824630737</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13419,7 +13419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193417072296</v>
       </c>
       <c r="H450" t="n">
         <v>30500</v>
@@ -13477,7 +13477,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193417072296</v>
       </c>
       <c r="H452" t="n">
         <v>5000</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>
@@ -13651,7 +13651,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G458" t="n">
-        <v>1.88739275932312</v>
+        <v>1.88739287853241</v>
       </c>
       <c r="H458" t="n">
         <v>500</v>
@@ -13680,7 +13680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.85127031803131</v>
+        <v>1.8512704372406</v>
       </c>
       <c r="H459" t="n">
         <v>6500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984966754913</v>
+        <v>1.75984978675842</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13767,7 +13767,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H462" t="n">
         <v>23000</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14202,7 +14202,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G477" t="n">
-        <v>1.70956838130951</v>
+        <v>1.70956826210022</v>
       </c>
       <c r="H477" t="n">
         <v>2000</v>
@@ -14231,7 +14231,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G478" t="n">
-        <v>1.70956838130951</v>
+        <v>1.70956826210022</v>
       </c>
       <c r="H478" t="n">
         <v>1000</v>
@@ -14260,7 +14260,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871054172516</v>
+        <v>1.71871030330658</v>
       </c>
       <c r="H479" t="n">
         <v>1000</v>
@@ -14289,7 +14289,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H480" t="n">
         <v>4000</v>
@@ -14318,7 +14318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G481" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897820472717</v>
+        <v>1.92897808551788</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412548065186</v>
+        <v>1.87412559986115</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14521,7 +14521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.80098903179169</v>
+        <v>1.80098915100098</v>
       </c>
       <c r="H488" t="n">
         <v>7500</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326776027679</v>
+        <v>1.8832676410675</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14724,7 +14724,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270494937897</v>
+        <v>1.78270506858826</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G498" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H498" t="n">
         <v>2000</v>
@@ -14840,7 +14840,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G499" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -14869,7 +14869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H500" t="n">
         <v>2000</v>
@@ -14898,7 +14898,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H502" t="n">
         <v>5000</v>
@@ -14956,7 +14956,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H503" t="n">
         <v>500</v>
@@ -14985,7 +14985,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871054172516</v>
+        <v>1.71871030330658</v>
       </c>
       <c r="H515" t="n">
         <v>1000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75527858734131</v>
+        <v>1.75527882575989</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G523" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H524" t="n">
         <v>3500</v>
@@ -15594,7 +15594,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G525" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G526" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15768,7 +15768,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G531" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G532" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G533" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G534" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H546" t="n">
         <v>2500</v>
@@ -16261,7 +16261,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072148799896</v>
+        <v>1.59072124958038</v>
       </c>
       <c r="H548" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G551" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G554" t="n">
-        <v>1.65471589565277</v>
+        <v>1.65471577644348</v>
       </c>
       <c r="H554" t="n">
         <v>2000</v>
@@ -16464,7 +16464,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65471589565277</v>
+        <v>1.65471577644348</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G561" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16696,7 +16696,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67300009727478</v>
+        <v>1.67299997806549</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16725,7 +16725,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H567" t="n">
         <v>4000</v>
@@ -16841,7 +16841,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157932758331</v>
+        <v>1.58157920837402</v>
       </c>
       <c r="H568" t="n">
         <v>3500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16928,7 +16928,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G571" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H571" t="n">
         <v>6500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -16986,7 +16986,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H573" t="n">
         <v>1000</v>
@@ -17015,7 +17015,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H574" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.79184710979462</v>
+        <v>1.79184699058533</v>
       </c>
       <c r="H576" t="n">
         <v>17500</v>
@@ -17131,7 +17131,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242330551147</v>
+        <v>1.73242342472076</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H579" t="n">
         <v>10000</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17247,7 +17247,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H582" t="n">
         <v>5500</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17363,7 +17363,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154529094696</v>
+        <v>1.52154541015625</v>
       </c>
       <c r="H587" t="n">
         <v>6500</v>
@@ -17421,7 +17421,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H588" t="n">
         <v>11500</v>
@@ -17450,7 +17450,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937839508057</v>
       </c>
       <c r="H589" t="n">
         <v>500</v>
@@ -17479,7 +17479,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G590" t="n">
-        <v>1.53082311153412</v>
+        <v>1.53082299232483</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17653,7 +17653,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G596" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H596" t="n">
         <v>5000</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>1.52618420124054</v>
+        <v>1.52618432044983</v>
       </c>
       <c r="H598" t="n">
         <v>3500</v>
@@ -17769,7 +17769,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59576714038849</v>
+        <v>1.5957670211792</v>
       </c>
       <c r="H600" t="n">
         <v>4500</v>
@@ -17827,7 +17827,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17856,7 +17856,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>1.66998887062073</v>
+        <v>1.66998875141144</v>
       </c>
       <c r="H603" t="n">
         <v>14500</v>
@@ -17943,7 +17943,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G606" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H606" t="n">
         <v>49500</v>
@@ -17972,7 +17972,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G607" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H607" t="n">
         <v>35500</v>
@@ -18001,7 +18001,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048704624176</v>
+        <v>1.92048716545105</v>
       </c>
       <c r="H608" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18059,7 +18059,7 @@
         <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H610" t="n">
         <v>9500</v>
@@ -18117,7 +18117,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78596019744873</v>
+        <v>1.78596031665802</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78596019744873</v>
+        <v>1.78596031665802</v>
       </c>
       <c r="H613" t="n">
         <v>2000</v>
@@ -18175,7 +18175,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>1.81843221187592</v>
+        <v>1.81843233108521</v>
       </c>
       <c r="H614" t="n">
         <v>4000</v>
@@ -18204,7 +18204,7 @@
         <v>2</v>
       </c>
       <c r="G615" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H615" t="n">
         <v>4000</v>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="G616" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H616" t="n">
         <v>2000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2</v>
       </c>
       <c r="G621" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H621" t="n">
         <v>3500</v>
@@ -18407,7 +18407,7 @@
         <v>2</v>
       </c>
       <c r="G622" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H622" t="n">
         <v>500</v>
@@ -18436,7 +18436,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>2.05037522315979</v>
+        <v>2.05037546157837</v>
       </c>
       <c r="H623" t="n">
         <v>67500</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615349292755</v>
+        <v>1.97615337371826</v>
       </c>
       <c r="H625" t="n">
         <v>14000</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120934486389</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18552,7 +18552,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832015037537</v>
+        <v>1.94832026958466</v>
       </c>
       <c r="H627" t="n">
         <v>8500</v>
@@ -18581,7 +18581,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326441764832</v>
+        <v>2.01326417922974</v>
       </c>
       <c r="H628" t="n">
         <v>10500</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748602867126</v>
+        <v>2.08748626708984</v>
       </c>
       <c r="H629" t="n">
         <v>42500</v>
@@ -18668,7 +18668,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>2.45859503746033</v>
+        <v>2.45859479904175</v>
       </c>
       <c r="H631" t="n">
         <v>119500</v>
@@ -18697,7 +18697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>2.91320276260376</v>
+        <v>2.91320300102234</v>
       </c>
       <c r="H632" t="n">
         <v>262000</v>
@@ -18726,7 +18726,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H633" t="n">
         <v>86500</v>
@@ -18871,7 +18871,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>2.80187034606934</v>
+        <v>2.80187010765076</v>
       </c>
       <c r="H638" t="n">
         <v>15500</v>
@@ -18900,7 +18900,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H639" t="n">
         <v>1000</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.5235390663147</v>
+        <v>2.52353858947754</v>
       </c>
       <c r="H641" t="n">
         <v>36000</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H644" t="n">
         <v>12000</v>
@@ -19074,7 +19074,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H645" t="n">
         <v>22000</v>
@@ -19132,7 +19132,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H647" t="n">
         <v>12000</v>
@@ -19161,7 +19161,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G648" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.54209399223328</v>
+        <v>2.54209423065186</v>
       </c>
       <c r="H650" t="n">
         <v>4500</v>
@@ -19248,7 +19248,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>2.38437294960022</v>
+        <v>2.38437271118164</v>
       </c>
       <c r="H651" t="n">
         <v>63000</v>
@@ -19306,7 +19306,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H653" t="n">
         <v>19500</v>
@@ -19335,7 +19335,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H654" t="n">
         <v>24000</v>
@@ -19364,7 +19364,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H655" t="n">
         <v>36500</v>
@@ -19538,7 +19538,7 @@
         <v>2.5</v>
       </c>
       <c r="G661" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H661" t="n">
         <v>210500</v>
@@ -19567,7 +19567,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>2.40292811393738</v>
+        <v>2.40292835235596</v>
       </c>
       <c r="H662" t="n">
         <v>38500</v>
@@ -19596,7 +19596,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220569610596</v>
+        <v>2.41220593452454</v>
       </c>
       <c r="H663" t="n">
         <v>11500</v>
@@ -19625,7 +19625,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>2.39365077018738</v>
+        <v>2.3936505317688</v>
       </c>
       <c r="H664" t="n">
         <v>5500</v>
@@ -19712,7 +19712,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G667" t="n">
-        <v>2.40292811393738</v>
+        <v>2.40292835235596</v>
       </c>
       <c r="H667" t="n">
         <v>9500</v>
@@ -19741,7 +19741,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220569610596</v>
+        <v>2.41220593452454</v>
       </c>
       <c r="H668" t="n">
         <v>14000</v>
@@ -19770,7 +19770,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>2.43076157569885</v>
+        <v>2.43076133728027</v>
       </c>
       <c r="H669" t="n">
         <v>1500</v>
@@ -19799,7 +19799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H670" t="n">
         <v>4500</v>
@@ -19828,7 +19828,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H671" t="n">
         <v>8000</v>
@@ -19857,7 +19857,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703802108765</v>
       </c>
       <c r="H673" t="n">
         <v>48500</v>
@@ -19973,7 +19973,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703802108765</v>
       </c>
       <c r="H676" t="n">
         <v>27000</v>
@@ -20002,7 +20002,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.69053745269775</v>
+        <v>2.69053769111633</v>
       </c>
       <c r="H677" t="n">
         <v>14000</v>
@@ -20031,7 +20031,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H678" t="n">
         <v>18000</v>
@@ -20060,7 +20060,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>2.7647590637207</v>
+        <v>2.76475954055786</v>
       </c>
       <c r="H679" t="n">
         <v>15500</v>
@@ -20089,7 +20089,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764873504639</v>
+        <v>2.72764849662781</v>
       </c>
       <c r="H680" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H681" t="n">
         <v>13000</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970309257507</v>
+        <v>2.82970333099365</v>
       </c>
       <c r="H683" t="n">
         <v>121000</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331446647644</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20263,7 +20263,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>2.81114792823792</v>
+        <v>2.81114768981934</v>
       </c>
       <c r="H686" t="n">
         <v>1000</v>
@@ -20321,7 +20321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G688" t="n">
-        <v>2.80187034606934</v>
+        <v>2.80187010765076</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>2.80187034606934</v>
+        <v>2.80187010765076</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G690" t="n">
-        <v>2.93175840377808</v>
+        <v>2.9317581653595</v>
       </c>
       <c r="H690" t="n">
         <v>16000</v>
@@ -20611,7 +20611,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>2.85753631591797</v>
+        <v>2.85753655433655</v>
       </c>
       <c r="H698" t="n">
         <v>500</v>
@@ -20785,7 +20785,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G704" t="n">
-        <v>3.0802013874054</v>
+        <v>3.08020162582397</v>
       </c>
       <c r="H704" t="n">
         <v>200500</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -20901,7 +20901,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H708" t="n">
         <v>7000</v>
@@ -20988,7 +20988,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H711" t="n">
         <v>6000</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -21046,7 +21046,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>3.02453517913818</v>
+        <v>3.02453541755676</v>
       </c>
       <c r="H713" t="n">
         <v>6500</v>
@@ -21191,7 +21191,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G718" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H718" t="n">
         <v>500</v>
@@ -21365,7 +21365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H724" t="n">
         <v>5000</v>
@@ -21452,7 +21452,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G727" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H727" t="n">
         <v>8500</v>
@@ -21510,7 +21510,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G729" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H729" t="n">
         <v>3500</v>
@@ -21539,7 +21539,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H730" t="n">
         <v>6000</v>
@@ -21597,7 +21597,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G732" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H732" t="n">
         <v>4000</v>
@@ -21655,7 +21655,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>3.03395771980286</v>
+        <v>3.03395748138428</v>
       </c>
       <c r="H734" t="n">
         <v>5500</v>
@@ -21684,7 +21684,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G735" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H735" t="n">
         <v>3500</v>
@@ -21713,7 +21713,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H737" t="n">
         <v>1000</v>
@@ -21771,7 +21771,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21800,7 +21800,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G739" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H739" t="n">
         <v>21500</v>
@@ -21858,7 +21858,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H741" t="n">
         <v>7500</v>
@@ -21887,7 +21887,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H742" t="n">
         <v>2500</v>
@@ -21916,7 +21916,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H743" t="n">
         <v>10000</v>
@@ -21945,7 +21945,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H744" t="n">
         <v>4000</v>
@@ -22003,7 +22003,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G746" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H746" t="n">
         <v>10500</v>
@@ -22032,7 +22032,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H747" t="n">
         <v>72500</v>
@@ -22148,7 +22148,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H751" t="n">
         <v>37000</v>
@@ -22177,7 +22177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H752" t="n">
         <v>5500</v>
@@ -22206,7 +22206,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>3.22240209579468</v>
+        <v>3.22240233421326</v>
       </c>
       <c r="H753" t="n">
         <v>11000</v>
@@ -22235,7 +22235,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G754" t="n">
-        <v>3.22240209579468</v>
+        <v>3.22240233421326</v>
       </c>
       <c r="H754" t="n">
         <v>4000</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H766" t="n">
         <v>11000</v>
@@ -22612,7 +22612,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H767" t="n">
         <v>9500</v>
@@ -22786,7 +22786,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H773" t="n">
         <v>13000</v>
@@ -22815,7 +22815,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G774" t="n">
-        <v>3.03395771980286</v>
+        <v>3.03395748138428</v>
       </c>
       <c r="H774" t="n">
         <v>192500</v>
@@ -22844,7 +22844,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>3.07164621353149</v>
+        <v>3.07164645195007</v>
       </c>
       <c r="H775" t="n">
         <v>84000</v>
@@ -22873,7 +22873,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G776" t="n">
-        <v>3.07164621353149</v>
+        <v>3.07164645195007</v>
       </c>
       <c r="H776" t="n">
         <v>8500</v>
@@ -22902,7 +22902,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H777" t="n">
         <v>10000</v>
@@ -22931,7 +22931,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>3.07164621353149</v>
+        <v>3.07164645195007</v>
       </c>
       <c r="H778" t="n">
         <v>7500</v>
@@ -22960,7 +22960,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H779" t="n">
         <v>5000</v>
@@ -22989,7 +22989,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H780" t="n">
         <v>4000</v>
@@ -23018,7 +23018,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H781" t="n">
         <v>3500</v>
@@ -23047,7 +23047,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H782" t="n">
         <v>1500</v>
@@ -23076,7 +23076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H786" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H787" t="n">
         <v>7000</v>
@@ -23250,7 +23250,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G789" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H789" t="n">
         <v>6000</v>
@@ -23308,7 +23308,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23395,7 +23395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H794" t="n">
         <v>9000</v>
@@ -23453,7 +23453,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G796" t="n">
-        <v>3.03395771980286</v>
+        <v>3.03395748138428</v>
       </c>
       <c r="H796" t="n">
         <v>7500</v>
@@ -23482,7 +23482,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G797" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H797" t="n">
         <v>16500</v>
@@ -23511,7 +23511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H798" t="n">
         <v>7000</v>
@@ -23540,7 +23540,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>3.03395771980286</v>
+        <v>3.03395748138428</v>
       </c>
       <c r="H799" t="n">
         <v>5000</v>
@@ -23685,7 +23685,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H804" t="n">
         <v>29000</v>
@@ -23743,7 +23743,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H806" t="n">
         <v>15000</v>
@@ -23830,7 +23830,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H809" t="n">
         <v>14500</v>
@@ -23946,7 +23946,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H813" t="n">
         <v>7000</v>
@@ -23975,7 +23975,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G814" t="n">
-        <v>2.97742438316345</v>
+        <v>2.97742414474487</v>
       </c>
       <c r="H814" t="n">
         <v>6000</v>
@@ -24004,7 +24004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H815" t="n">
         <v>15000</v>
@@ -24062,7 +24062,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H817" t="n">
         <v>19000</v>
@@ -24178,7 +24178,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>3.6935133934021</v>
+        <v>3.69351363182068</v>
       </c>
       <c r="H821" t="n">
         <v>295500</v>
@@ -24207,7 +24207,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>3.61813545227051</v>
+        <v>3.61813569068909</v>
       </c>
       <c r="H822" t="n">
         <v>59500</v>
@@ -24497,7 +24497,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>3.7877357006073</v>
+        <v>3.78773593902588</v>
       </c>
       <c r="H832" t="n">
         <v>21500</v>
@@ -24903,7 +24903,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>4.29653644561768</v>
+        <v>4.29653596878052</v>
       </c>
       <c r="H846" t="n">
         <v>21500</v>
@@ -25019,7 +25019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>4.29653644561768</v>
+        <v>4.29653596878052</v>
       </c>
       <c r="H850" t="n">
         <v>12000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25280,7 +25280,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H859" t="n">
         <v>13000</v>
@@ -25309,7 +25309,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502468109131</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H860" t="n">
         <v>49000</v>
@@ -25396,7 +25396,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.97618007659912</v>
+        <v>3.9761803150177</v>
       </c>
       <c r="H863" t="n">
         <v>58000</v>
@@ -25483,7 +25483,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H866" t="n">
         <v>18000</v>
@@ -25512,7 +25512,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H867" t="n">
         <v>13500</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25802,7 +25802,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>4.27769184112549</v>
+        <v>4.27769136428833</v>
       </c>
       <c r="H877" t="n">
         <v>60000</v>
@@ -25860,7 +25860,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37191343307495</v>
+        <v>4.37191390991211</v>
       </c>
       <c r="H879" t="n">
         <v>147000</v>
@@ -25889,7 +25889,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G880" t="n">
-        <v>4.40960311889648</v>
+        <v>4.40960264205933</v>
       </c>
       <c r="H880" t="n">
         <v>51000</v>
@@ -25976,7 +25976,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G883" t="n">
-        <v>4.29653644561768</v>
+        <v>4.29653596878052</v>
       </c>
       <c r="H883" t="n">
         <v>17500</v>
@@ -26005,7 +26005,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G884" t="n">
-        <v>4.29653644561768</v>
+        <v>4.29653596878052</v>
       </c>
       <c r="H884" t="n">
         <v>13000</v>
@@ -26063,7 +26063,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G886" t="n">
-        <v>4.40960311889648</v>
+        <v>4.40960264205933</v>
       </c>
       <c r="H886" t="n">
         <v>17000</v>
@@ -26121,7 +26121,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G888" t="n">
-        <v>4.50382518768311</v>
+        <v>4.50382566452026</v>
       </c>
       <c r="H888" t="n">
         <v>46000</v>
@@ -26179,7 +26179,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G890" t="n">
-        <v>4.57920360565186</v>
+        <v>4.5792031288147</v>
       </c>
       <c r="H890" t="n">
         <v>18500</v>
@@ -26208,7 +26208,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G891" t="n">
-        <v>4.57920360565186</v>
+        <v>4.5792031288147</v>
       </c>
       <c r="H891" t="n">
         <v>18000</v>
@@ -26266,7 +26266,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>4.57920360565186</v>
+        <v>4.5792031288147</v>
       </c>
       <c r="H893" t="n">
         <v>19500</v>
@@ -26295,7 +26295,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>4.48498058319092</v>
+        <v>4.48498106002808</v>
       </c>
       <c r="H894" t="n">
         <v>6500</v>
@@ -26382,7 +26382,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G897" t="n">
-        <v>4.37191343307495</v>
+        <v>4.37191390991211</v>
       </c>
       <c r="H897" t="n">
         <v>7500</v>
@@ -26411,7 +26411,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G898" t="n">
-        <v>4.48498058319092</v>
+        <v>4.48498106002808</v>
       </c>
       <c r="H898" t="n">
         <v>11500</v>
@@ -26498,7 +26498,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G901" t="n">
-        <v>5.37066984176636</v>
+        <v>5.37067031860352</v>
       </c>
       <c r="H901" t="n">
         <v>172500</v>
@@ -26556,7 +26556,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H903" t="n">
         <v>32500</v>
@@ -26672,7 +26672,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H907" t="n">
         <v>170500</v>
@@ -26817,7 +26817,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H912" t="n">
         <v>14000</v>
@@ -26904,7 +26904,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H915" t="n">
         <v>16000</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H916" t="n">
         <v>26000</v>
@@ -26962,7 +26962,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H917" t="n">
         <v>61000</v>
@@ -26991,7 +26991,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H918" t="n">
         <v>13000</v>
@@ -27020,7 +27020,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08800315856934</v>
+        <v>5.08800363540649</v>
       </c>
       <c r="H919" t="n">
         <v>26500</v>
@@ -27049,7 +27049,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H920" t="n">
         <v>12500</v>
@@ -27107,7 +27107,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H922" t="n">
         <v>5000</v>
@@ -27426,7 +27426,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>3.65582489967346</v>
+        <v>3.65582466125488</v>
       </c>
       <c r="H933" t="n">
         <v>9000</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.93849158287048</v>
+        <v>3.9384913444519</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27513,7 +27513,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502468109131</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H936" t="n">
         <v>4500</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27687,7 +27687,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>4.27769184112549</v>
+        <v>4.27769136428833</v>
       </c>
       <c r="H942" t="n">
         <v>6500</v>
@@ -27716,7 +27716,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>4.27769184112549</v>
+        <v>4.27769136428833</v>
       </c>
       <c r="H943" t="n">
         <v>2000</v>
@@ -27774,7 +27774,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G945" t="n">
-        <v>4.40960311889648</v>
+        <v>4.40960264205933</v>
       </c>
       <c r="H945" t="n">
         <v>6500</v>
@@ -27890,7 +27890,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H949" t="n">
         <v>30500</v>
@@ -27977,7 +27977,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880266189575</v>
+        <v>4.74880313873291</v>
       </c>
       <c r="H952" t="n">
         <v>8000</v>
@@ -28267,7 +28267,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G962" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635778427124</v>
       </c>
       <c r="H962" t="n">
         <v>2500</v>
@@ -28383,7 +28383,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404747009277</v>
+        <v>4.17404699325562</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28557,7 +28557,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G972" t="n">
-        <v>4.54151391983032</v>
+        <v>4.54151439666748</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28673,7 +28673,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G976" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H976" t="n">
         <v>20000</v>
@@ -28702,7 +28702,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G977" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H977" t="n">
         <v>5500</v>
@@ -28760,7 +28760,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G979" t="n">
-        <v>3.96998429298401</v>
+        <v>3.96998381614685</v>
       </c>
       <c r="H979" t="n">
         <v>6500</v>
@@ -28847,7 +28847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H982" t="n">
         <v>5500</v>
@@ -28876,7 +28876,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H985" t="n">
         <v>2500</v>
@@ -29021,7 +29021,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H988" t="n">
         <v>2500</v>
@@ -29050,7 +29050,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G989" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H989" t="n">
         <v>4000</v>
@@ -29137,7 +29137,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G992" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H992" t="n">
         <v>2500</v>
@@ -29166,7 +29166,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G993" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H993" t="n">
         <v>500</v>
@@ -29253,7 +29253,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G996" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H996" t="n">
         <v>2500</v>
@@ -29340,7 +29340,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G999" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1000" t="n">
         <v>12000</v>
@@ -29398,7 +29398,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1001" t="n">
         <v>16000</v>
@@ -29601,7 +29601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29688,7 +29688,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.29760408401489</v>
+        <v>4.29760456085205</v>
       </c>
       <c r="H1011" t="n">
         <v>8500</v>
@@ -29804,7 +29804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1015" t="n">
         <v>2500</v>
@@ -29862,7 +29862,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1017" t="n">
         <v>2000</v>
@@ -30065,7 +30065,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1024" t="n">
         <v>6500</v>
@@ -30326,7 +30326,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1033" t="n">
         <v>19500</v>
@@ -30355,7 +30355,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1034" t="n">
         <v>2000</v>
@@ -30442,7 +30442,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.37469148635864</v>
+        <v>4.37469100952148</v>
       </c>
       <c r="H1037" t="n">
         <v>1500</v>
@@ -30500,7 +30500,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1039" t="n">
         <v>6500</v>
@@ -30819,7 +30819,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1050" t="n">
         <v>1000</v>
@@ -30848,7 +30848,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1051" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1059" t="n">
         <v>1500</v>
@@ -31254,7 +31254,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1065" t="n">
         <v>20000</v>
@@ -31312,7 +31312,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1067" t="n">
         <v>9000</v>
@@ -31370,7 +31370,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1069" t="n">
         <v>2000</v>
@@ -31399,7 +31399,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1070" t="n">
         <v>8000</v>
@@ -31486,7 +31486,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1073" t="n">
         <v>35000</v>
@@ -31573,7 +31573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1076" t="n">
         <v>27000</v>
@@ -31602,7 +31602,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.44001054763794</v>
+        <v>3.44001078605652</v>
       </c>
       <c r="H1077" t="n">
         <v>17000</v>
@@ -31805,7 +31805,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1084" t="n">
         <v>6000</v>
@@ -31834,7 +31834,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1085" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1092" t="n">
         <v>13500</v>
@@ -32095,7 +32095,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1094" t="n">
         <v>15500</v>
@@ -32124,7 +32124,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1095" t="n">
         <v>19500</v>
@@ -32240,7 +32240,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1099" t="n">
         <v>3000</v>
@@ -32269,7 +32269,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1100" t="n">
         <v>4000</v>
@@ -32298,7 +32298,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1101" t="n">
         <v>7500</v>
@@ -32327,7 +32327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1102" t="n">
         <v>12000</v>
@@ -32356,7 +32356,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1103" t="n">
         <v>10000</v>
@@ -32443,7 +32443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1106" t="n">
         <v>17000</v>
@@ -32472,7 +32472,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1107" t="n">
         <v>5500</v>
@@ -32530,7 +32530,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1109" t="n">
         <v>6000</v>
@@ -32559,7 +32559,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.07597923278809</v>
+        <v>4.07597875595093</v>
       </c>
       <c r="H1110" t="n">
         <v>8500</v>
@@ -32588,7 +32588,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1111" t="n">
         <v>9000</v>
@@ -32617,7 +32617,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1112" t="n">
         <v>6500</v>
@@ -32762,7 +32762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1117" t="n">
         <v>2000</v>
@@ -32849,7 +32849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.95071268081665</v>
+        <v>3.95071244239807</v>
       </c>
       <c r="H1120" t="n">
         <v>4500</v>
@@ -33226,7 +33226,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1133" t="n">
         <v>1000</v>
@@ -33458,7 +33458,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1141" t="n">
         <v>4500</v>
@@ -33487,7 +33487,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1143" t="n">
         <v>2500</v>
@@ -33545,7 +33545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1144" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1144" t="n">
         <v>6500</v>
@@ -33574,7 +33574,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1145" t="n">
         <v>11500</v>
@@ -33632,7 +33632,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1147" t="n">
         <v>1000</v>
@@ -33748,7 +33748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1151" t="n">
         <v>2500</v>
@@ -33806,7 +33806,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1153" t="n">
         <v>109500</v>
@@ -33922,7 +33922,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.58668088912964</v>
+        <v>4.5866813659668</v>
       </c>
       <c r="H1157" t="n">
         <v>17000</v>
@@ -33951,7 +33951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1158" t="n">
         <v>41000</v>
@@ -34067,7 +34067,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1162" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1164" t="n">
         <v>18000</v>
@@ -34154,7 +34154,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.73121881484985</v>
+        <v>4.73121929168701</v>
       </c>
       <c r="H1165" t="n">
         <v>25000</v>
@@ -34299,7 +34299,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1170" t="n">
         <v>4500</v>
@@ -34328,7 +34328,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1171" t="n">
         <v>9000</v>
@@ -34386,7 +34386,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.63486051559448</v>
+        <v>4.63486003875732</v>
       </c>
       <c r="H1173" t="n">
         <v>7500</v>
@@ -34502,7 +34502,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1177" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1177" t="n">
         <v>3500</v>
@@ -34618,7 +34618,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1181" t="n">
         <v>4500</v>
@@ -34966,7 +34966,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1193" t="n">
         <v>7000</v>
@@ -34995,7 +34995,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1194" t="n">
         <v>2000</v>
@@ -35053,7 +35053,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1196" t="n">
         <v>3000</v>
@@ -35140,7 +35140,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1199" t="n">
         <v>4500</v>
@@ -35169,7 +35169,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1200" t="n">
         <v>2000</v>
@@ -35198,7 +35198,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H1201" t="n">
         <v>4000</v>
@@ -35227,7 +35227,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1202" t="n">
         <v>1000</v>
@@ -35285,7 +35285,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1204" t="n">
         <v>17500</v>
@@ -35517,7 +35517,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1212" t="n">
         <v>13000</v>
@@ -35546,7 +35546,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1213" t="n">
         <v>7000</v>
@@ -35604,7 +35604,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1215" t="n">
         <v>6500</v>
@@ -35633,7 +35633,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1216" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1217" t="n">
         <v>6000</v>
@@ -35691,7 +35691,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.27833223342896</v>
+        <v>4.27833271026611</v>
       </c>
       <c r="H1218" t="n">
         <v>11500</v>
@@ -35720,7 +35720,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1219" t="n">
         <v>36500</v>
@@ -35749,7 +35749,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1220" t="n">
         <v>5000</v>
@@ -35865,7 +35865,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1224" t="n">
         <v>6000</v>
@@ -35894,7 +35894,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1225" t="n">
         <v>8000</v>
@@ -35952,7 +35952,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1227" t="n">
         <v>15500</v>
@@ -61478,6 +61478,35 @@
         <v>10000</v>
       </c>
       <c r="I2107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2108" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I2108" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614658355713</v>
+        <v>3.59614682197571</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709582328796</v>
+        <v>3.74709558486938</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3475239276886</v>
+        <v>3.34752416610718</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274496078491</v>
+        <v>3.45274472236633</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -688,7 +688,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H11" t="n">
         <v>156500</v>
@@ -717,7 +717,7 @@
         <v>3.65750002861023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24763083457947</v>
+        <v>3.24763131141663</v>
       </c>
       <c r="H12" t="n">
         <v>215500</v>
@@ -746,7 +746,7 @@
         <v>3.57049989700317</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17038083076477</v>
+        <v>3.17038059234619</v>
       </c>
       <c r="H13" t="n">
         <v>78500</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.19657468795776</v>
+        <v>3.19657444953918</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881631851196</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -862,7 +862,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>3.19657468795776</v>
+        <v>3.19657444953918</v>
       </c>
       <c r="H17" t="n">
         <v>22000</v>
@@ -920,7 +920,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15173411369324</v>
+        <v>3.15173387527466</v>
       </c>
       <c r="H19" t="n">
         <v>13500</v>
@@ -949,7 +949,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.187251329422</v>
+        <v>3.18725156784058</v>
       </c>
       <c r="H20" t="n">
         <v>214000</v>
@@ -978,7 +978,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898765563965</v>
       </c>
       <c r="H21" t="n">
         <v>50500</v>
@@ -1065,7 +1065,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.95860767364502</v>
+        <v>2.95860743522644</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1094,7 +1094,7 @@
         <v>3.3289999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.95594358444214</v>
+        <v>2.95594382286072</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H26" t="n">
         <v>15500</v>
@@ -1152,7 +1152,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H27" t="n">
         <v>57500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467620849609</v>
+        <v>2.89467644691467</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8187575340271</v>
+        <v>2.81875705718994</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78812408447266</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1355,7 +1355,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890198707581</v>
       </c>
       <c r="H34" t="n">
         <v>49500</v>
@@ -1384,7 +1384,7 @@
         <v>3.37450003623962</v>
       </c>
       <c r="G35" t="n">
-        <v>2.99634480476379</v>
+        <v>2.99634504318237</v>
       </c>
       <c r="H35" t="n">
         <v>78000</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325849533081</v>
+        <v>2.97325873374939</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1471,7 +1471,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H38" t="n">
         <v>9000</v>
@@ -1500,7 +1500,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H39" t="n">
         <v>20500</v>
@@ -1529,7 +1529,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243457794189</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H40" t="n">
         <v>9500</v>
@@ -1558,7 +1558,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H41" t="n">
         <v>11000</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H42" t="n">
         <v>3000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H44" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.88624095916748</v>
+        <v>2.8862407207489</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1732,7 +1732,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H47" t="n">
         <v>58000</v>
@@ -1848,7 +1848,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.0944619178772</v>
+        <v>3.09446167945862</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.0855827331543</v>
+        <v>3.08558225631714</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769502639771</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769502639771</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.2676100730896</v>
+        <v>3.26760959625244</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868745803833</v>
+        <v>3.29868721961975</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881631851196</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678897857666</v>
+        <v>2.99678921699524</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2225,7 +2225,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G64" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890198707581</v>
       </c>
       <c r="H64" t="n">
         <v>18500</v>
@@ -2254,7 +2254,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338429450989</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H65" t="n">
         <v>5500</v>
@@ -2341,7 +2341,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H68" t="n">
         <v>23500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>2.73484754562378</v>
+        <v>2.73484706878662</v>
       </c>
       <c r="H71" t="n">
         <v>17500</v>
@@ -2457,7 +2457,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820927619934</v>
+        <v>2.70820879936218</v>
       </c>
       <c r="H72" t="n">
         <v>15500</v>
@@ -2486,7 +2486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.73484754562378</v>
+        <v>2.73484706878662</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2544,7 +2544,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135671615601</v>
+        <v>2.88135695457458</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2573,7 +2573,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683145523071</v>
+        <v>2.95683169364929</v>
       </c>
       <c r="H76" t="n">
         <v>17000</v>
@@ -2602,7 +2602,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.92131423950195</v>
+        <v>2.92131400108337</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2631,7 +2631,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027885437012</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459030151367</v>
+        <v>2.97459053993225</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364153862</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2718,7 +2718,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243457794189</v>
+        <v>2.91243481636047</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027885437012</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.1521782875061</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H85" t="n">
         <v>19000</v>
@@ -2863,7 +2863,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.1521782875061</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H86" t="n">
         <v>7000</v>
@@ -2892,7 +2892,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.19657468795776</v>
+        <v>3.19657444953918</v>
       </c>
       <c r="H87" t="n">
         <v>5500</v>
@@ -2921,7 +2921,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H88" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562568664551</v>
+        <v>3.04562520980835</v>
       </c>
       <c r="H89" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670307159424</v>
+        <v>3.07670331001282</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3037,7 +3037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.17437672615051</v>
+        <v>3.17437648773193</v>
       </c>
       <c r="H92" t="n">
         <v>19000</v>
@@ -3124,7 +3124,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562568664551</v>
+        <v>3.04562520980835</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3153,7 +3153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338429450989</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H96" t="n">
         <v>4500</v>
@@ -3182,7 +3182,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H97" t="n">
         <v>9500</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.03230595588684</v>
+        <v>3.032306432724</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3298,7 +3298,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.1521782875061</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H101" t="n">
         <v>14500</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881631851196</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674626350403</v>
+        <v>3.03674650192261</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3472,7 +3472,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>3.10778117179871</v>
+        <v>3.10778141021729</v>
       </c>
       <c r="H107" t="n">
         <v>6000</v>
@@ -3501,7 +3501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898741722107</v>
+        <v>3.01898765563965</v>
       </c>
       <c r="H108" t="n">
         <v>6000</v>
@@ -3559,7 +3559,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H110" t="n">
         <v>14000</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9701509475708</v>
+        <v>2.97015070915222</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3617,7 +3617,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G112" t="n">
-        <v>2.83696031570435</v>
+        <v>2.83696007728577</v>
       </c>
       <c r="H112" t="n">
         <v>8500</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023637771606</v>
+        <v>2.89023685455322</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H114" t="n">
         <v>4000</v>
@@ -3704,7 +3704,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019342422485</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.84583973884583</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H117" t="n">
         <v>11500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3907,7 +3907,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>2.83696031570435</v>
+        <v>2.83696007728577</v>
       </c>
       <c r="H122" t="n">
         <v>2000</v>
@@ -3936,7 +3936,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480435371399</v>
+        <v>2.77480459213257</v>
       </c>
       <c r="H123" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480435371399</v>
+        <v>2.77480459213257</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.74372673034668</v>
+        <v>2.7437264919281</v>
       </c>
       <c r="H127" t="n">
         <v>13000</v>
@@ -4081,7 +4081,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G128" t="n">
-        <v>2.74372673034668</v>
+        <v>2.7437264919281</v>
       </c>
       <c r="H128" t="n">
         <v>2500</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.8058819770813</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.67269158363342</v>
+        <v>2.672691822052</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4342,7 +4342,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G137" t="n">
-        <v>2.71264886856079</v>
+        <v>2.71264863014221</v>
       </c>
       <c r="H137" t="n">
         <v>7500</v>
@@ -4487,7 +4487,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G142" t="n">
-        <v>2.74372673034668</v>
+        <v>2.7437264919281</v>
       </c>
       <c r="H142" t="n">
         <v>8500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4545,7 +4545,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H144" t="n">
         <v>72000</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592540740967</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.8547191619873</v>
+        <v>2.85471868515015</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032228469849</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -5009,7 +5009,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H160" t="n">
         <v>1500</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592540740967</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5183,7 +5183,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H166" t="n">
         <v>6000</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144238471985</v>
+        <v>2.80144286155701</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5299,7 +5299,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H170" t="n">
         <v>4500</v>
@@ -5328,7 +5328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H171" t="n">
         <v>7500</v>
@@ -5357,7 +5357,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596788406372</v>
+        <v>2.72596740722656</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.78812408447266</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5589,7 +5589,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>2.81476187705994</v>
+        <v>2.81476163864136</v>
       </c>
       <c r="H180" t="n">
         <v>5000</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.8058819770813</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5647,7 +5647,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>2.84583973884583</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H182" t="n">
         <v>18500</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364153862</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5705,7 +5705,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H184" t="n">
         <v>28000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467620849609</v>
+        <v>2.89467644691467</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5763,7 +5763,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027885437012</v>
       </c>
       <c r="H186" t="n">
         <v>66000</v>
@@ -5792,7 +5792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596788406372</v>
+        <v>2.72596740722656</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.78812408447266</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H191" t="n">
         <v>9500</v>
@@ -5937,7 +5937,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6082,7 +6082,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027885437012</v>
       </c>
       <c r="H197" t="n">
         <v>10500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364153862</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84139966964722</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.8058819770813</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364106178284</v>
+        <v>2.82364153862</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.8502790927887</v>
+        <v>2.85027885437012</v>
       </c>
       <c r="H203" t="n">
         <v>26000</v>
@@ -6285,7 +6285,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>2.81476187705994</v>
+        <v>2.81476163864136</v>
       </c>
       <c r="H204" t="n">
         <v>3500</v>
@@ -6314,7 +6314,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H205" t="n">
         <v>2500</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H215" t="n">
         <v>4000</v>
@@ -6662,7 +6662,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868727684021</v>
       </c>
       <c r="H217" t="n">
         <v>14000</v>
@@ -6691,7 +6691,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H218" t="n">
         <v>27500</v>
@@ -6749,7 +6749,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H220" t="n">
         <v>7000</v>
@@ -6778,7 +6778,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H221" t="n">
         <v>31000</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H227" t="n">
         <v>27000</v>
@@ -6981,7 +6981,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H228" t="n">
         <v>36000</v>
@@ -7010,7 +7010,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.5238881111145</v>
+        <v>2.52388787269592</v>
       </c>
       <c r="H229" t="n">
         <v>28000</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813732147217</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813732147217</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708731651306</v>
+        <v>2.6670868396759</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708731651306</v>
+        <v>2.6670868396759</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7416,7 +7416,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H243" t="n">
         <v>17500</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708731651306</v>
+        <v>2.6670868396759</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H251" t="n">
         <v>24500</v>
@@ -7677,7 +7677,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H252" t="n">
         <v>10000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503625869751</v>
+        <v>2.85503649711609</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7764,7 +7764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>2.81028699874878</v>
+        <v>2.8102867603302</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7793,7 +7793,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G256" t="n">
-        <v>2.84608674049377</v>
+        <v>2.8460865020752</v>
       </c>
       <c r="H256" t="n">
         <v>7000</v>
@@ -7880,7 +7880,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H259" t="n">
         <v>10000</v>
@@ -7909,7 +7909,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H260" t="n">
         <v>9500</v>
@@ -7967,7 +7967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -8054,7 +8054,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H266" t="n">
         <v>18500</v>
@@ -8199,7 +8199,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H270" t="n">
         <v>8500</v>
@@ -8228,7 +8228,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>2.7834370136261</v>
+        <v>2.78343677520752</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8315,7 +8315,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448678016663</v>
       </c>
       <c r="H276" t="n">
         <v>5000</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8431,7 +8431,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868727684021</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8460,7 +8460,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973704338074</v>
+        <v>2.72973680496216</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H297" t="n">
         <v>1000</v>
@@ -9011,7 +9011,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H298" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>2.7834370136261</v>
+        <v>2.78343677520752</v>
       </c>
       <c r="H302" t="n">
         <v>19000</v>
@@ -9272,7 +9272,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H307" t="n">
         <v>3000</v>
@@ -9359,7 +9359,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H310" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233757972717</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9678,7 +9678,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178810119629</v>
+        <v>2.54178786277771</v>
       </c>
       <c r="H321" t="n">
         <v>7000</v>
@@ -9736,7 +9736,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G323" t="n">
-        <v>2.55073809623718</v>
+        <v>2.5507378578186</v>
       </c>
       <c r="H323" t="n">
         <v>1500</v>
@@ -9765,7 +9765,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.60443782806396</v>
+        <v>2.60443758964539</v>
       </c>
       <c r="H324" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708731651306</v>
+        <v>2.6670868396759</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9939,7 +9939,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H330" t="n">
         <v>6000</v>
@@ -9997,7 +9997,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.50598788261414</v>
+        <v>2.50598812103271</v>
       </c>
       <c r="H332" t="n">
         <v>30000</v>
@@ -10026,7 +10026,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.5646870136261</v>
+        <v>2.56468677520752</v>
       </c>
       <c r="H333" t="n">
         <v>8500</v>
@@ -10084,7 +10084,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.5105037689209</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H335" t="n">
         <v>37500</v>
@@ -10113,7 +10113,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G336" t="n">
-        <v>2.43825888633728</v>
+        <v>2.4382586479187</v>
       </c>
       <c r="H336" t="n">
         <v>29000</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H342" t="n">
         <v>3000</v>
@@ -10316,7 +10316,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G343" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H343" t="n">
         <v>26500</v>
@@ -10374,7 +10374,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H345" t="n">
         <v>3500</v>
@@ -10403,7 +10403,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H346" t="n">
         <v>18500</v>
@@ -10432,7 +10432,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H347" t="n">
         <v>13000</v>
@@ -10490,7 +10490,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.5105037689209</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H349" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147271156311</v>
+        <v>2.50147294998169</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.47438073158264</v>
+        <v>2.4743812084198</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10809,7 +10809,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H361" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H362" t="n">
         <v>500</v>
@@ -10896,7 +10896,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G363" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H368" t="n">
         <v>1000</v>
@@ -11070,7 +11070,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.38407516479492</v>
+        <v>2.3840754032135</v>
       </c>
       <c r="H369" t="n">
         <v>16500</v>
@@ -11157,7 +11157,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45631980895996</v>
+        <v>2.45631957054138</v>
       </c>
       <c r="H372" t="n">
         <v>2000</v>
@@ -11186,7 +11186,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341178894043</v>
+        <v>2.48341155052185</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698318481445</v>
+        <v>2.35698342323303</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11476,7 +11476,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30280017852783</v>
+        <v>2.30279970169067</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11650,7 +11650,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958587646484</v>
+        <v>2.23958611488342</v>
       </c>
       <c r="H389" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861669540405</v>
+        <v>2.24861645698547</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11824,7 +11824,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>2.20346331596375</v>
+        <v>2.20346355438232</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.16734147071838</v>
+        <v>2.1673412322998</v>
       </c>
       <c r="H396" t="n">
         <v>3500</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.15831065177917</v>
+        <v>2.1583104133606</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11940,7 +11940,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.18540239334106</v>
+        <v>2.18540215492249</v>
       </c>
       <c r="H399" t="n">
         <v>18500</v>
@@ -11969,7 +11969,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>2.17637181282043</v>
+        <v>2.17637205123901</v>
       </c>
       <c r="H400" t="n">
         <v>21500</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570843696594</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H403" t="n">
         <v>8500</v>
@@ -12085,7 +12085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570843696594</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12114,7 +12114,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26667737960815</v>
+        <v>2.26667761802673</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12143,7 +12143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570843696594</v>
+        <v>2.27570796012878</v>
       </c>
       <c r="H406" t="n">
         <v>1500</v>
@@ -12172,7 +12172,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861669540405</v>
+        <v>2.24861645698547</v>
       </c>
       <c r="H407" t="n">
         <v>7500</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12288,7 +12288,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G411" t="n">
-        <v>2.17637181282043</v>
+        <v>2.17637205123901</v>
       </c>
       <c r="H411" t="n">
         <v>8000</v>
@@ -12346,7 +12346,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800436973572</v>
       </c>
       <c r="H413" t="n">
         <v>15500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703495025635</v>
+        <v>2.07703518867493</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12404,7 +12404,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.0680046081543</v>
+        <v>2.06800436973572</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99575984477997</v>
+        <v>1.99576008319855</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060706138611</v>
+        <v>1.9506071805954</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12491,7 +12491,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.8512704372406</v>
+        <v>1.85127067565918</v>
       </c>
       <c r="H418" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642322063446</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12607,7 +12607,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G422" t="n">
-        <v>1.64356708526611</v>
+        <v>1.64356696605682</v>
       </c>
       <c r="H422" t="n">
         <v>46500</v>
@@ -12781,7 +12781,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G428" t="n">
-        <v>1.21912944316864</v>
+        <v>1.21912932395935</v>
       </c>
       <c r="H428" t="n">
         <v>7500</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.2100989818573</v>
+        <v>1.21009874343872</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364449501038</v>
+        <v>1.22364473342896</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12897,7 +12897,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.2326751947403</v>
+        <v>1.23267531394958</v>
       </c>
       <c r="H432" t="n">
         <v>2500</v>
@@ -12926,7 +12926,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G433" t="n">
-        <v>1.2642822265625</v>
+        <v>1.26428234577179</v>
       </c>
       <c r="H433" t="n">
         <v>6000</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846570968628</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846594810486</v>
+        <v>1.31846570968628</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13187,7 +13187,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49004685878754</v>
+        <v>1.49004697799683</v>
       </c>
       <c r="H442" t="n">
         <v>13000</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.60292947292328</v>
+        <v>1.60292935371399</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13274,7 +13274,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099039554596</v>
+        <v>1.62099051475525</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G446" t="n">
-        <v>1.62550568580627</v>
+        <v>1.62550580501556</v>
       </c>
       <c r="H446" t="n">
         <v>8500</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259754657745</v>
+        <v>1.65259766578674</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13419,7 +13419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H450" t="n">
         <v>30500</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290335178375</v>
+        <v>1.74290347099304</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13477,7 +13477,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H452" t="n">
         <v>5000</v>
@@ -13506,7 +13506,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611765384674</v>
+        <v>1.80611753463745</v>
       </c>
       <c r="H453" t="n">
         <v>9500</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160236358643</v>
+        <v>1.80160212516785</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13564,7 +13564,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902579307556</v>
+        <v>1.77902591228485</v>
       </c>
       <c r="H455" t="n">
         <v>4500</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642345905304</v>
+        <v>1.89642322063446</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>
@@ -13680,7 +13680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8512704372406</v>
+        <v>1.85127067565918</v>
       </c>
       <c r="H459" t="n">
         <v>6500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984978675842</v>
+        <v>1.75984966754913</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13738,7 +13738,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.6775711774826</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H461" t="n">
         <v>31000</v>
@@ -13796,7 +13796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>1.57243716716766</v>
+        <v>1.57243728637695</v>
       </c>
       <c r="H463" t="n">
         <v>9500</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13883,7 +13883,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H466" t="n">
         <v>7500</v>
@@ -13941,7 +13941,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H468" t="n">
         <v>1000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H473" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.6775711774826</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H475" t="n">
         <v>12000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14202,7 +14202,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G477" t="n">
-        <v>1.70956826210022</v>
+        <v>1.70956838130951</v>
       </c>
       <c r="H477" t="n">
         <v>2000</v>
@@ -14231,7 +14231,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G478" t="n">
-        <v>1.70956826210022</v>
+        <v>1.70956838130951</v>
       </c>
       <c r="H478" t="n">
         <v>1000</v>
@@ -14347,7 +14347,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G482" t="n">
-        <v>1.72785246372223</v>
+        <v>1.72785258293152</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14376,7 +14376,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G483" t="n">
-        <v>1.73699450492859</v>
+        <v>1.73699462413788</v>
       </c>
       <c r="H483" t="n">
         <v>8000</v>
@@ -14405,7 +14405,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>1.77356290817261</v>
+        <v>1.77356278896332</v>
       </c>
       <c r="H484" t="n">
         <v>46500</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897808551788</v>
+        <v>1.92897796630859</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412559986115</v>
+        <v>1.87412571907043</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.8832676410675</v>
+        <v>1.88326752185822</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14579,7 +14579,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841539382935</v>
+        <v>1.82841527462006</v>
       </c>
       <c r="H490" t="n">
         <v>500</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841539382935</v>
+        <v>1.82841527462006</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14956,7 +14956,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070762634277</v>
+        <v>1.75070750713348</v>
       </c>
       <c r="H503" t="n">
         <v>500</v>
@@ -14985,7 +14985,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070762634277</v>
+        <v>1.75070750713348</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G505" t="n">
-        <v>1.72785246372223</v>
+        <v>1.72785258293152</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H507" t="n">
         <v>500</v>
@@ -15101,7 +15101,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.74156558513641</v>
+        <v>1.74156546592712</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G512" t="n">
-        <v>1.73699450492859</v>
+        <v>1.73699462413788</v>
       </c>
       <c r="H512" t="n">
         <v>4500</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.73699450492859</v>
+        <v>1.73699462413788</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G514" t="n">
-        <v>1.73699450492859</v>
+        <v>1.73699462413788</v>
       </c>
       <c r="H514" t="n">
         <v>500</v>
@@ -15333,7 +15333,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>1.77356290817261</v>
+        <v>1.77356278896332</v>
       </c>
       <c r="H516" t="n">
         <v>500</v>
@@ -15362,7 +15362,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77356290817261</v>
+        <v>1.77356278896332</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>1.77356290817261</v>
+        <v>1.77356278896332</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75527882575989</v>
+        <v>1.7552787065506</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G523" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H524" t="n">
         <v>3500</v>
@@ -15594,7 +15594,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G525" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G526" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814773082733</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15710,7 +15710,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G531" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G532" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G533" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G534" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072124958038</v>
+        <v>1.59072136878967</v>
       </c>
       <c r="H548" t="n">
         <v>9500</v>
@@ -16290,7 +16290,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H549" t="n">
         <v>7000</v>
@@ -16319,7 +16319,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G551" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014481544495</v>
+        <v>1.65014469623566</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16406,7 +16406,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014481544495</v>
+        <v>1.65014469623566</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G554" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H554" t="n">
         <v>2000</v>
@@ -16464,7 +16464,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65471577644348</v>
+        <v>1.65471589565277</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014481544495</v>
+        <v>1.65014469623566</v>
       </c>
       <c r="H556" t="n">
         <v>1000</v>
@@ -16522,7 +16522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G557" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643169403076</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G561" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16696,7 +16696,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67299997806549</v>
+        <v>1.67300009727478</v>
       </c>
       <c r="H563" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H565" t="n">
         <v>500</v>
@@ -16783,7 +16783,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G566" t="n">
-        <v>1.51758468151093</v>
+        <v>1.51758480072021</v>
       </c>
       <c r="H566" t="n">
         <v>10000</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16928,7 +16928,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G571" t="n">
-        <v>1.69128429889679</v>
+        <v>1.6912841796875</v>
       </c>
       <c r="H571" t="n">
         <v>6500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -16986,7 +16986,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66385805606842</v>
+        <v>1.66385793685913</v>
       </c>
       <c r="H573" t="n">
         <v>1000</v>
@@ -17044,7 +17044,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H575" t="n">
         <v>16500</v>
@@ -17073,7 +17073,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.79184699058533</v>
+        <v>1.79184710979462</v>
       </c>
       <c r="H576" t="n">
         <v>17500</v>
@@ -17131,7 +17131,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242342472076</v>
+        <v>1.73242354393005</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>1.69128429889679</v>
+        <v>1.6912841796875</v>
       </c>
       <c r="H579" t="n">
         <v>10000</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17305,7 +17305,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>1.5632951259613</v>
+        <v>1.56329524517059</v>
       </c>
       <c r="H584" t="n">
         <v>500</v>
@@ -17334,7 +17334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.63287794589996</v>
+        <v>1.63287806510925</v>
       </c>
       <c r="H585" t="n">
         <v>1500</v>
@@ -17363,7 +17363,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360024452209</v>
+        <v>1.62360036373138</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154541015625</v>
+        <v>1.52154529094696</v>
       </c>
       <c r="H587" t="n">
         <v>6500</v>
@@ -17421,7 +17421,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937839508057</v>
+        <v>1.54937851428986</v>
       </c>
       <c r="H588" t="n">
         <v>11500</v>
@@ -17450,7 +17450,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937839508057</v>
+        <v>1.54937851428986</v>
       </c>
       <c r="H589" t="n">
         <v>500</v>
@@ -17624,7 +17624,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>1.44732367992401</v>
+        <v>1.44732356071472</v>
       </c>
       <c r="H595" t="n">
         <v>10500</v>
@@ -17653,7 +17653,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G596" t="n">
-        <v>1.45660150051117</v>
+        <v>1.45660138130188</v>
       </c>
       <c r="H596" t="n">
         <v>5000</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.45660150051117</v>
+        <v>1.45660138130188</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>1.52618432044983</v>
+        <v>1.52618420124054</v>
       </c>
       <c r="H598" t="n">
         <v>3500</v>
@@ -17740,7 +17740,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.57721173763275</v>
+        <v>1.57721161842346</v>
       </c>
       <c r="H599" t="n">
         <v>3500</v>
@@ -17769,7 +17769,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G600" t="n">
-        <v>1.5957670211792</v>
+        <v>1.59576714038849</v>
       </c>
       <c r="H600" t="n">
         <v>4500</v>
@@ -17798,7 +17798,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>1.57721173763275</v>
+        <v>1.57721161842346</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360024452209</v>
+        <v>1.62360036373138</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17856,7 +17856,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>1.66998875141144</v>
+        <v>1.66998887062073</v>
       </c>
       <c r="H603" t="n">
         <v>14500</v>
@@ -17885,7 +17885,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G604" t="n">
-        <v>1.77204370498657</v>
+        <v>1.77204358577728</v>
       </c>
       <c r="H604" t="n">
         <v>8500</v>
@@ -17914,7 +17914,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.80915451049805</v>
+        <v>1.80915462970734</v>
       </c>
       <c r="H605" t="n">
         <v>13000</v>
@@ -17943,7 +17943,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G606" t="n">
-        <v>1.88337635993958</v>
+        <v>1.88337624073029</v>
       </c>
       <c r="H606" t="n">
         <v>49500</v>
@@ -17972,7 +17972,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G607" t="n">
-        <v>1.88337635993958</v>
+        <v>1.88337624073029</v>
       </c>
       <c r="H607" t="n">
         <v>35500</v>
@@ -18001,7 +18001,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048716545105</v>
+        <v>1.92048692703247</v>
       </c>
       <c r="H608" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.91120934486389</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.91120934486389</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.91120934486389</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.91120934486389</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>2.05037546157837</v>
+        <v>2.05037522315979</v>
       </c>
       <c r="H623" t="n">
         <v>67500</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820844650269</v>
+        <v>2.07820820808411</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615337371826</v>
+        <v>1.97615349292755</v>
       </c>
       <c r="H625" t="n">
         <v>14000</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.91120934486389</v>
+        <v>1.9112092256546</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18581,7 +18581,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326417922974</v>
+        <v>2.01326441764832</v>
       </c>
       <c r="H628" t="n">
         <v>10500</v>
@@ -18697,7 +18697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>2.91320300102234</v>
+        <v>2.91320276260376</v>
       </c>
       <c r="H632" t="n">
         <v>262000</v>
@@ -18726,7 +18726,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.78331446647644</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H633" t="n">
         <v>86500</v>
@@ -18755,7 +18755,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H634" t="n">
         <v>177500</v>
@@ -18784,7 +18784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H635" t="n">
         <v>49500</v>
@@ -18900,7 +18900,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.78331446647644</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H639" t="n">
         <v>1000</v>
@@ -18929,7 +18929,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>2.67198204994202</v>
+        <v>2.6719822883606</v>
       </c>
       <c r="H640" t="n">
         <v>8500</v>
@@ -18987,7 +18987,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.64414882659912</v>
+        <v>2.6441490650177</v>
       </c>
       <c r="H642" t="n">
         <v>34000</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H644" t="n">
         <v>12000</v>
@@ -19074,7 +19074,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68126010894775</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H645" t="n">
         <v>22000</v>
@@ -19132,7 +19132,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H647" t="n">
         <v>12000</v>
@@ -19161,7 +19161,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G648" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19248,7 +19248,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>2.38437271118164</v>
+        <v>2.38437294960022</v>
       </c>
       <c r="H651" t="n">
         <v>63000</v>
@@ -19277,7 +19277,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.34726214408875</v>
+        <v>2.34726238250732</v>
       </c>
       <c r="H652" t="n">
         <v>52500</v>
@@ -19480,7 +19480,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.31015133857727</v>
+        <v>2.31015110015869</v>
       </c>
       <c r="H659" t="n">
         <v>10500</v>
@@ -19509,7 +19509,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G660" t="n">
-        <v>2.31015133857727</v>
+        <v>2.31015110015869</v>
       </c>
       <c r="H660" t="n">
         <v>8000</v>
@@ -19625,7 +19625,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>2.3936505317688</v>
+        <v>2.39365077018738</v>
       </c>
       <c r="H664" t="n">
         <v>5500</v>
@@ -19654,7 +19654,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.34726214408875</v>
+        <v>2.34726238250732</v>
       </c>
       <c r="H665" t="n">
         <v>5500</v>
@@ -19770,7 +19770,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>2.43076133728027</v>
+        <v>2.43076157569885</v>
       </c>
       <c r="H669" t="n">
         <v>1500</v>
@@ -20031,7 +20031,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H678" t="n">
         <v>18000</v>
@@ -20060,7 +20060,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>2.76475954055786</v>
+        <v>2.7647590637207</v>
       </c>
       <c r="H679" t="n">
         <v>15500</v>
@@ -20089,7 +20089,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764849662781</v>
+        <v>2.72764873504639</v>
       </c>
       <c r="H680" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.68126010894775</v>
+        <v>2.68125987052917</v>
       </c>
       <c r="H681" t="n">
         <v>13000</v>
@@ -20147,7 +20147,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G682" t="n">
-        <v>2.67198204994202</v>
+        <v>2.6719822883606</v>
       </c>
       <c r="H682" t="n">
         <v>23000</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.83898091316223</v>
+        <v>2.83898115158081</v>
       </c>
       <c r="H684" t="n">
         <v>17000</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.78331446647644</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20263,7 +20263,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>2.81114768981934</v>
+        <v>2.81114792823792</v>
       </c>
       <c r="H686" t="n">
         <v>1000</v>
@@ -20292,7 +20292,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G687" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H687" t="n">
         <v>18500</v>
@@ -20408,7 +20408,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.90392518043518</v>
+        <v>2.9039249420166</v>
       </c>
       <c r="H691" t="n">
         <v>110000</v>
@@ -20437,7 +20437,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>2.95031356811523</v>
+        <v>2.95031380653381</v>
       </c>
       <c r="H692" t="n">
         <v>52500</v>
@@ -20466,7 +20466,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.95031356811523</v>
+        <v>2.95031380653381</v>
       </c>
       <c r="H693" t="n">
         <v>128500</v>
@@ -20495,7 +20495,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G694" t="n">
-        <v>2.95031356811523</v>
+        <v>2.95031380653381</v>
       </c>
       <c r="H694" t="n">
         <v>12500</v>
@@ -20553,7 +20553,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H696" t="n">
         <v>8000</v>
@@ -20582,7 +20582,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>2.83898091316223</v>
+        <v>2.83898115158081</v>
       </c>
       <c r="H697" t="n">
         <v>5500</v>
@@ -20611,7 +20611,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>2.85753655433655</v>
+        <v>2.85753631591797</v>
       </c>
       <c r="H698" t="n">
         <v>500</v>
@@ -20756,7 +20756,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.82042551040649</v>
+        <v>2.82042574882507</v>
       </c>
       <c r="H703" t="n">
         <v>9500</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -20901,7 +20901,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.0430908203125</v>
+        <v>3.04309058189392</v>
       </c>
       <c r="H708" t="n">
         <v>7000</v>
@@ -20988,7 +20988,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.0430908203125</v>
+        <v>3.04309058189392</v>
       </c>
       <c r="H711" t="n">
         <v>6000</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -21104,7 +21104,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H715" t="n">
         <v>6000</v>
@@ -21133,7 +21133,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G716" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H716" t="n">
         <v>4000</v>
@@ -21220,7 +21220,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H719" t="n">
         <v>500</v>
@@ -21336,7 +21336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G723" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H723" t="n">
         <v>2000</v>
@@ -21365,7 +21365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H724" t="n">
         <v>5000</v>
@@ -21394,7 +21394,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G725" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H725" t="n">
         <v>11500</v>
@@ -21423,7 +21423,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.99626851081848</v>
+        <v>2.99626874923706</v>
       </c>
       <c r="H726" t="n">
         <v>5500</v>
@@ -21510,7 +21510,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G729" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H729" t="n">
         <v>3500</v>
@@ -21539,7 +21539,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H730" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G735" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H735" t="n">
         <v>3500</v>
@@ -21713,7 +21713,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21858,7 +21858,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H741" t="n">
         <v>7500</v>
@@ -21887,7 +21887,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H742" t="n">
         <v>2500</v>
@@ -21916,7 +21916,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H743" t="n">
         <v>10000</v>
@@ -22003,7 +22003,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G746" t="n">
-        <v>2.95858001708984</v>
+        <v>2.95857977867126</v>
       </c>
       <c r="H746" t="n">
         <v>10500</v>
@@ -22032,7 +22032,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>3.10933518409729</v>
+        <v>3.10933542251587</v>
       </c>
       <c r="H747" t="n">
         <v>72500</v>
@@ -22061,7 +22061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H748" t="n">
         <v>24500</v>
@@ -22148,7 +22148,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H751" t="n">
         <v>37000</v>
@@ -22177,7 +22177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H752" t="n">
         <v>5500</v>
@@ -22264,7 +22264,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H755" t="n">
         <v>1000</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H766" t="n">
         <v>11000</v>
@@ -22612,7 +22612,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>3.24124646186829</v>
+        <v>3.24124670028687</v>
       </c>
       <c r="H767" t="n">
         <v>9500</v>
@@ -22641,7 +22641,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H768" t="n">
         <v>7000</v>
@@ -22786,7 +22786,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24124646186829</v>
+        <v>3.24124670028687</v>
       </c>
       <c r="H773" t="n">
         <v>13000</v>
@@ -22902,7 +22902,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H777" t="n">
         <v>10000</v>
@@ -22960,7 +22960,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.10933518409729</v>
+        <v>3.10933542251587</v>
       </c>
       <c r="H779" t="n">
         <v>5000</v>
@@ -22989,7 +22989,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H780" t="n">
         <v>4000</v>
@@ -23018,7 +23018,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.10933518409729</v>
+        <v>3.10933542251587</v>
       </c>
       <c r="H781" t="n">
         <v>3500</v>
@@ -23047,7 +23047,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H782" t="n">
         <v>1500</v>
@@ -23076,7 +23076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H786" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H787" t="n">
         <v>7000</v>
@@ -23221,7 +23221,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H788" t="n">
         <v>5000</v>
@@ -23250,7 +23250,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G789" t="n">
-        <v>3.10933518409729</v>
+        <v>3.10933542251587</v>
       </c>
       <c r="H789" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23395,7 +23395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H794" t="n">
         <v>9000</v>
@@ -23511,7 +23511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H798" t="n">
         <v>7000</v>
@@ -23685,7 +23685,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H804" t="n">
         <v>29000</v>
@@ -23743,7 +23743,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29777979850769</v>
+        <v>3.29778003692627</v>
       </c>
       <c r="H806" t="n">
         <v>15000</v>
@@ -23801,7 +23801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H808" t="n">
         <v>6500</v>
@@ -23830,7 +23830,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H809" t="n">
         <v>14500</v>
@@ -23859,7 +23859,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H810" t="n">
         <v>3500</v>
@@ -23946,7 +23946,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H813" t="n">
         <v>7000</v>
@@ -24004,7 +24004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.09049105644226</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H815" t="n">
         <v>15000</v>
@@ -24033,7 +24033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H816" t="n">
         <v>44000</v>
@@ -24062,7 +24062,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.24124646186829</v>
+        <v>3.24124670028687</v>
       </c>
       <c r="H817" t="n">
         <v>19000</v>
@@ -24207,7 +24207,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>3.61813569068909</v>
+        <v>3.61813545227051</v>
       </c>
       <c r="H822" t="n">
         <v>59500</v>
@@ -24236,7 +24236,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H823" t="n">
         <v>29000</v>
@@ -24265,7 +24265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H824" t="n">
         <v>23500</v>
@@ -24497,7 +24497,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>3.78773593902588</v>
+        <v>3.7877357006073</v>
       </c>
       <c r="H832" t="n">
         <v>21500</v>
@@ -24526,7 +24526,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>4.0138692855835</v>
+        <v>4.01386976242065</v>
       </c>
       <c r="H833" t="n">
         <v>119000</v>
@@ -24613,7 +24613,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H836" t="n">
         <v>184500</v>
@@ -24816,7 +24816,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H843" t="n">
         <v>32000</v>
@@ -24874,7 +24874,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H845" t="n">
         <v>16500</v>
@@ -24961,7 +24961,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H848" t="n">
         <v>22000</v>
@@ -24990,7 +24990,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H849" t="n">
         <v>25000</v>
@@ -25106,7 +25106,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25135,7 +25135,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H854" t="n">
         <v>16000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H856" t="n">
         <v>4500</v>
@@ -25222,7 +25222,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H857" t="n">
         <v>18000</v>
@@ -25251,7 +25251,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G858" t="n">
-        <v>4.0138692855835</v>
+        <v>4.01386976242065</v>
       </c>
       <c r="H858" t="n">
         <v>39000</v>
@@ -25309,7 +25309,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502491950989</v>
+        <v>3.99502420425415</v>
       </c>
       <c r="H860" t="n">
         <v>49000</v>
@@ -25396,7 +25396,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.9761803150177</v>
+        <v>3.97618007659912</v>
       </c>
       <c r="H863" t="n">
         <v>58000</v>
@@ -25425,7 +25425,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H864" t="n">
         <v>12000</v>
@@ -25541,7 +25541,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H868" t="n">
         <v>16000</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H875" t="n">
         <v>6500</v>
@@ -25773,7 +25773,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G876" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H876" t="n">
         <v>72000</v>
@@ -26121,7 +26121,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G888" t="n">
-        <v>4.50382566452026</v>
+        <v>4.50382518768311</v>
       </c>
       <c r="H888" t="n">
         <v>46000</v>
@@ -26353,7 +26353,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H896" t="n">
         <v>22500</v>
@@ -26469,7 +26469,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>5.27644777297974</v>
+        <v>5.27644824981689</v>
       </c>
       <c r="H900" t="n">
         <v>253500</v>
@@ -26527,7 +26527,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H902" t="n">
         <v>88500</v>
@@ -26556,7 +26556,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H903" t="n">
         <v>32500</v>
@@ -26585,7 +26585,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>5.13511419296265</v>
+        <v>5.1351146697998</v>
       </c>
       <c r="H904" t="n">
         <v>67500</v>
@@ -26614,7 +26614,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>5.27644777297974</v>
+        <v>5.27644824981689</v>
       </c>
       <c r="H905" t="n">
         <v>36500</v>
@@ -26643,7 +26643,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G906" t="n">
-        <v>5.13511419296265</v>
+        <v>5.1351146697998</v>
       </c>
       <c r="H906" t="n">
         <v>35000</v>
@@ -26672,7 +26672,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H907" t="n">
         <v>170500</v>
@@ -26701,7 +26701,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H908" t="n">
         <v>23500</v>
@@ -26730,7 +26730,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -26759,7 +26759,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H910" t="n">
         <v>22500</v>
@@ -26817,7 +26817,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H912" t="n">
         <v>14000</v>
@@ -26875,7 +26875,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H914" t="n">
         <v>37000</v>
@@ -26904,7 +26904,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H915" t="n">
         <v>16000</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378108978271</v>
+        <v>4.99378156661987</v>
       </c>
       <c r="H916" t="n">
         <v>26000</v>
@@ -26962,7 +26962,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H917" t="n">
         <v>61000</v>
@@ -26991,7 +26991,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H918" t="n">
         <v>13000</v>
@@ -27049,7 +27049,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H920" t="n">
         <v>12500</v>
@@ -27107,7 +27107,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H922" t="n">
         <v>5000</v>
@@ -27281,7 +27281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G928" t="n">
-        <v>4.4472918510437</v>
+        <v>4.44729137420654</v>
       </c>
       <c r="H928" t="n">
         <v>9000</v>
@@ -27368,7 +27368,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56160235404968</v>
+        <v>3.5616021156311</v>
       </c>
       <c r="H931" t="n">
         <v>72500</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.9384913444519</v>
+        <v>3.93849110603333</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.8819580078125</v>
+        <v>3.88195776939392</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502491950989</v>
+        <v>3.99502420425415</v>
       </c>
       <c r="H936" t="n">
         <v>4500</v>
@@ -27542,7 +27542,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H937" t="n">
         <v>12000</v>
@@ -27600,7 +27600,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H939" t="n">
         <v>8000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27658,7 +27658,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H941" t="n">
         <v>3500</v>
@@ -27745,7 +27745,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H944" t="n">
         <v>3500</v>
@@ -27890,7 +27890,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H949" t="n">
         <v>30500</v>
@@ -27977,7 +27977,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880313873291</v>
+        <v>4.74880266189575</v>
       </c>
       <c r="H952" t="n">
         <v>8000</v>
@@ -28209,7 +28209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G960" t="n">
-        <v>4.10809183120728</v>
+        <v>4.10809135437012</v>
       </c>
       <c r="H960" t="n">
         <v>42500</v>
@@ -28296,7 +28296,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G963" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H963" t="n">
         <v>10500</v>
@@ -28325,7 +28325,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G964" t="n">
-        <v>4.10809183120728</v>
+        <v>4.10809135437012</v>
       </c>
       <c r="H964" t="n">
         <v>7000</v>
@@ -28354,7 +28354,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H965" t="n">
         <v>3500</v>
@@ -28383,7 +28383,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404699325562</v>
+        <v>4.17404747009277</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28586,7 +28586,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H973" t="n">
         <v>11500</v>
@@ -61495,7 +61495,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="E2108" t="n">
-        <v>3.05999994277954</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="F2108" t="n">
         <v>3.03999996185303</v>
@@ -61507,6 +61507,35 @@
         <v>2000</v>
       </c>
       <c r="I2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2109" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>500</v>
+      </c>
+      <c r="I2109" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614682197571</v>
+        <v>3.59614658355713</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709558486938</v>
+        <v>3.74709582328796</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244758605957</v>
+        <v>3.52244782447815</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -543,7 +543,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42743825912476</v>
+        <v>3.42743849754333</v>
       </c>
       <c r="H6" t="n">
         <v>110500</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.34752416610718</v>
+        <v>3.3475239276886</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274472236633</v>
+        <v>3.45274496078491</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>3.71050000190735</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29469203948975</v>
+        <v>3.29469227790833</v>
       </c>
       <c r="H10" t="n">
         <v>88500</v>
@@ -688,7 +688,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H11" t="n">
         <v>156500</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -862,7 +862,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G17" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H17" t="n">
         <v>22000</v>
@@ -949,7 +949,7 @@
         <v>3.58949995040894</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18725156784058</v>
+        <v>3.187251329422</v>
       </c>
       <c r="H20" t="n">
         <v>214000</v>
@@ -978,7 +978,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898765563965</v>
+        <v>3.01898717880249</v>
       </c>
       <c r="H21" t="n">
         <v>50500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467644691467</v>
+        <v>2.89467597007751</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1239,7 +1239,7 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H30" t="n">
         <v>45000</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1326,7 +1326,7 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1355,7 +1355,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.09890198707581</v>
+        <v>3.09890174865723</v>
       </c>
       <c r="H34" t="n">
         <v>49500</v>
@@ -1500,7 +1500,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H39" t="n">
         <v>20500</v>
@@ -1616,7 +1616,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.9168746471405</v>
+        <v>2.91687488555908</v>
       </c>
       <c r="H43" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H47" t="n">
         <v>58000</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.9168746471405</v>
+        <v>2.91687488555908</v>
       </c>
       <c r="H50" t="n">
         <v>18000</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08558225631714</v>
+        <v>3.08558249473572</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769550323486</v>
+        <v>3.18769526481628</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769550323486</v>
+        <v>3.18769526481628</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760959625244</v>
+        <v>3.26760983467102</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868721961975</v>
+        <v>3.29868745803833</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678921699524</v>
+        <v>2.99678897857666</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2225,7 +2225,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G64" t="n">
-        <v>3.09890198707581</v>
+        <v>3.09890174865723</v>
       </c>
       <c r="H64" t="n">
         <v>18500</v>
@@ -2254,7 +2254,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338405609131</v>
+        <v>3.06338453292847</v>
       </c>
       <c r="H65" t="n">
         <v>5500</v>
@@ -2370,7 +2370,7 @@
         <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H69" t="n">
         <v>15500</v>
@@ -2428,7 +2428,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>2.73484706878662</v>
+        <v>2.7348473072052</v>
       </c>
       <c r="H71" t="n">
         <v>17500</v>
@@ -2486,7 +2486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.73484706878662</v>
+        <v>2.7348473072052</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2544,7 +2544,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135695457458</v>
+        <v>2.88135671615601</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2573,7 +2573,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.95683169364929</v>
+        <v>2.95683145523071</v>
       </c>
       <c r="H76" t="n">
         <v>17000</v>
@@ -2631,7 +2631,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.85027885437012</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459053993225</v>
+        <v>2.97459006309509</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2747,7 +2747,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85027885437012</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2776,7 +2776,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122857093811</v>
+        <v>3.00122880935669</v>
       </c>
       <c r="H83" t="n">
         <v>15000</v>
@@ -2892,7 +2892,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.19657444953918</v>
+        <v>3.19657468795776</v>
       </c>
       <c r="H87" t="n">
         <v>5500</v>
@@ -2921,7 +2921,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H88" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H89" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670331001282</v>
+        <v>3.07670307159424</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3066,7 +3066,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H93" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04562520980835</v>
+        <v>3.04562544822693</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3153,7 +3153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338405609131</v>
+        <v>3.06338453292847</v>
       </c>
       <c r="H96" t="n">
         <v>4500</v>
@@ -3182,7 +3182,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666059494019</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H97" t="n">
         <v>9500</v>
@@ -3269,7 +3269,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334157943726</v>
+        <v>3.10334134101868</v>
       </c>
       <c r="H100" t="n">
         <v>4500</v>
@@ -3327,7 +3327,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23209238052368</v>
+        <v>3.2320921421051</v>
       </c>
       <c r="H102" t="n">
         <v>28000</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881608009338</v>
+        <v>3.17881631851196</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674650192261</v>
+        <v>3.03674626350403</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3472,7 +3472,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>3.10778141021729</v>
+        <v>3.10778117179871</v>
       </c>
       <c r="H107" t="n">
         <v>6000</v>
@@ -3501,7 +3501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898765563965</v>
+        <v>3.01898717880249</v>
       </c>
       <c r="H108" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.97015070915222</v>
+        <v>2.97015047073364</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023685455322</v>
+        <v>2.89023661613464</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.25</v>
       </c>
       <c r="G116" t="n">
-        <v>2.88579678535461</v>
+        <v>2.88579654693604</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915851593018</v>
+        <v>2.8591582775116</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3994,7 +3994,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040795326233</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4110,7 +4110,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808065414429</v>
+        <v>2.82808089256287</v>
       </c>
       <c r="H129" t="n">
         <v>39500</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256343841553</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4284,7 +4284,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H135" t="n">
         <v>2500</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.672691822052</v>
+        <v>2.67269158363342</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4342,7 +4342,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G137" t="n">
-        <v>2.71264863014221</v>
+        <v>2.71264910697937</v>
       </c>
       <c r="H137" t="n">
         <v>7500</v>
@@ -4400,7 +4400,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713165283203</v>
+        <v>2.67713141441345</v>
       </c>
       <c r="H139" t="n">
         <v>2500</v>
@@ -4429,7 +4429,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H140" t="n">
         <v>5500</v>
@@ -4458,7 +4458,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040795326233</v>
       </c>
       <c r="H141" t="n">
         <v>4500</v>
@@ -4574,7 +4574,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H145" t="n">
         <v>21000</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592540740967</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471868515015</v>
+        <v>2.85471892356873</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76148533821106</v>
+        <v>2.76148557662964</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592540740967</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5473,7 +5473,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040771484375</v>
+        <v>2.73040795326233</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924418449402</v>
+        <v>2.7792444229126</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5531,7 +5531,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808065414429</v>
+        <v>2.82808089256287</v>
       </c>
       <c r="H178" t="n">
         <v>9500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5589,7 +5589,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H180" t="n">
         <v>5000</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467644691467</v>
+        <v>2.89467597007751</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5763,7 +5763,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.85027885437012</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H186" t="n">
         <v>66000</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6082,7 +6082,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.85027885437012</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H197" t="n">
         <v>10500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252048492432</v>
+        <v>2.83252024650574</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.84139966964722</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588269233704</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.85027885437012</v>
+        <v>2.85027933120728</v>
       </c>
       <c r="H203" t="n">
         <v>26000</v>
@@ -6285,7 +6285,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H204" t="n">
         <v>3500</v>
@@ -6314,7 +6314,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>2.83713674545288</v>
+        <v>2.8371365070343</v>
       </c>
       <c r="H205" t="n">
         <v>2500</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6488,7 +6488,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H211" t="n">
         <v>5000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6546,7 +6546,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H213" t="n">
         <v>37000</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6662,7 +6662,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868727684021</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H217" t="n">
         <v>14000</v>
@@ -6720,7 +6720,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G219" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H219" t="n">
         <v>9000</v>
@@ -6865,7 +6865,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H224" t="n">
         <v>13000</v>
@@ -6981,7 +6981,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H228" t="n">
         <v>36000</v>
@@ -7039,7 +7039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>2.59548759460449</v>
+        <v>2.59548783302307</v>
       </c>
       <c r="H230" t="n">
         <v>18500</v>
@@ -7097,7 +7097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H232" t="n">
         <v>32000</v>
@@ -7155,7 +7155,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G234" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H234" t="n">
         <v>21000</v>
@@ -7184,7 +7184,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H235" t="n">
         <v>8000</v>
@@ -7213,7 +7213,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H236" t="n">
         <v>3500</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813732147217</v>
+        <v>2.65813779830933</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813732147217</v>
+        <v>2.65813779830933</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7416,7 +7416,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H243" t="n">
         <v>17500</v>
@@ -7445,7 +7445,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128781318665</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7503,7 +7503,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918756484985</v>
+        <v>2.64918732643127</v>
       </c>
       <c r="H246" t="n">
         <v>6000</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7619,7 +7619,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H250" t="n">
         <v>17500</v>
@@ -7648,7 +7648,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.83713674545288</v>
+        <v>2.8371365070343</v>
       </c>
       <c r="H251" t="n">
         <v>24500</v>
@@ -7677,7 +7677,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.83713674545288</v>
+        <v>2.8371365070343</v>
       </c>
       <c r="H252" t="n">
         <v>10000</v>
@@ -7706,7 +7706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818627357483</v>
+        <v>2.82818651199341</v>
       </c>
       <c r="H253" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503649711609</v>
+        <v>2.85503625869751</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7764,7 +7764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>2.8102867603302</v>
+        <v>2.81028652191162</v>
       </c>
       <c r="H255" t="n">
         <v>11000</v>
@@ -7822,7 +7822,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H257" t="n">
         <v>19000</v>
@@ -7851,7 +7851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133676528931</v>
+        <v>2.80133700370789</v>
       </c>
       <c r="H258" t="n">
         <v>14000</v>
@@ -8025,7 +8025,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G264" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8228,7 +8228,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>2.78343677520752</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923675537109</v>
+        <v>2.81923699378967</v>
       </c>
       <c r="H272" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8344,7 +8344,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76553702354431</v>
+        <v>2.76553678512573</v>
       </c>
       <c r="H275" t="n">
         <v>5500</v>
@@ -8431,7 +8431,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868727684021</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078680992126</v>
+        <v>2.72078704833984</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H292" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G294" t="n">
-        <v>2.70288729667664</v>
+        <v>2.70288705825806</v>
       </c>
       <c r="H294" t="n">
         <v>500</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238653182983</v>
+        <v>2.79238629341125</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -9127,7 +9127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78343677520752</v>
+        <v>2.7834370136261</v>
       </c>
       <c r="H302" t="n">
         <v>19000</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128781318665</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128781318665</v>
+        <v>2.63128757476807</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9533,7 +9533,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G316" t="n">
-        <v>2.59548759460449</v>
+        <v>2.59548783302307</v>
       </c>
       <c r="H316" t="n">
         <v>2500</v>
@@ -9562,7 +9562,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.55968761444092</v>
+        <v>2.55968737602234</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G320" t="n">
-        <v>2.55968761444092</v>
+        <v>2.55968737602234</v>
       </c>
       <c r="H320" t="n">
         <v>61000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G323" t="n">
-        <v>2.5507378578186</v>
+        <v>2.55073761940002</v>
       </c>
       <c r="H323" t="n">
         <v>1500</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.58653783798218</v>
+        <v>2.5865375995636</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.59548759460449</v>
+        <v>2.59548783302307</v>
       </c>
       <c r="H327" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.59548759460449</v>
+        <v>2.59548783302307</v>
       </c>
       <c r="H328" t="n">
         <v>6500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.6670868396759</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9939,7 +9939,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023733139038</v>
+        <v>2.64023756980896</v>
       </c>
       <c r="H330" t="n">
         <v>6000</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -10026,7 +10026,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56468677520752</v>
+        <v>2.5646870136261</v>
       </c>
       <c r="H333" t="n">
         <v>8500</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42019748687744</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147294998169</v>
+        <v>2.50147271156311</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.42019748687744</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.42019748687744</v>
+        <v>2.42019772529602</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310574531555</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698342323303</v>
+        <v>2.35698318481445</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11650,7 +11650,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958611488342</v>
+        <v>2.23958587646484</v>
       </c>
       <c r="H389" t="n">
         <v>9000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11824,7 +11824,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>2.20346355438232</v>
+        <v>2.20346331596375</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.1583104133606</v>
+        <v>2.15831065177917</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703518867493</v>
+        <v>2.07703542709351</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642322063446</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12636,7 +12636,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G423" t="n">
-        <v>1.47198581695557</v>
+        <v>1.47198593616486</v>
       </c>
       <c r="H423" t="n">
         <v>9500</v>
@@ -12665,7 +12665,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H424" t="n">
         <v>3000</v>
@@ -12694,7 +12694,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H425" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.3545880317688</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.21009874343872</v>
+        <v>1.21009886264801</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12955,7 +12955,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.3545880317688</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H434" t="n">
         <v>11500</v>
@@ -12984,7 +12984,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>1.37264931201935</v>
+        <v>1.37264943122864</v>
       </c>
       <c r="H435" t="n">
         <v>4000</v>
@@ -13100,7 +13100,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.3545880317688</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H439" t="n">
         <v>5000</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259766578674</v>
+        <v>1.65259754657745</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13506,7 +13506,7 @@
         <v>2</v>
       </c>
       <c r="G453" t="n">
-        <v>1.80611753463745</v>
+        <v>1.80611765384674</v>
       </c>
       <c r="H453" t="n">
         <v>9500</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160212516785</v>
+        <v>1.80160224437714</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642322063446</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614658355713</v>
+        <v>3.59614706039429</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709582328796</v>
+        <v>3.74709606170654</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -485,7 +485,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589263916016</v>
+        <v>3.62589240074158</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244782447815</v>
+        <v>3.52244806289673</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -543,7 +543,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42743849754333</v>
+        <v>3.42743825912476</v>
       </c>
       <c r="H6" t="n">
         <v>110500</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274496078491</v>
+        <v>3.45274448394775</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>3.71050000190735</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29469227790833</v>
+        <v>3.29469180107117</v>
       </c>
       <c r="H10" t="n">
         <v>88500</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881631851196</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -920,7 +920,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15173387527466</v>
+        <v>3.15173363685608</v>
       </c>
       <c r="H19" t="n">
         <v>13500</v>
@@ -1065,7 +1065,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.95860743522644</v>
+        <v>2.95860767364502</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1094,7 +1094,7 @@
         <v>3.3289999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.95594382286072</v>
+        <v>2.95594358444214</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H26" t="n">
         <v>15500</v>
@@ -1152,7 +1152,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H27" t="n">
         <v>57500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875705718994</v>
+        <v>2.8187575340271</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1297,7 +1297,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G32" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H32" t="n">
         <v>33500</v>
@@ -1355,7 +1355,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890151023865</v>
       </c>
       <c r="H34" t="n">
         <v>49500</v>
@@ -1413,7 +1413,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93907284736633</v>
+        <v>2.93907308578491</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325873374939</v>
+        <v>2.97325849533081</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1471,7 +1471,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H38" t="n">
         <v>9000</v>
@@ -1558,7 +1558,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H41" t="n">
         <v>11000</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H42" t="n">
         <v>3000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H44" t="n">
         <v>7000</v>
@@ -1703,7 +1703,7 @@
         <v>3.27900004386902</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9115469455719</v>
+        <v>2.91154670715332</v>
       </c>
       <c r="H46" t="n">
         <v>10000</v>
@@ -1790,7 +1790,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.93907284736633</v>
+        <v>2.93907308578491</v>
       </c>
       <c r="H49" t="n">
         <v>4000</v>
@@ -1848,7 +1848,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1935,7 +1935,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08114290237427</v>
+        <v>3.08114314079285</v>
       </c>
       <c r="H54" t="n">
         <v>61000</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769526481628</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760983467102</v>
+        <v>3.2676100730896</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868745803833</v>
+        <v>3.29868769645691</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2109,7 +2109,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873041152954</v>
+        <v>3.25873017311096</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881631851196</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2225,7 +2225,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G64" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890151023865</v>
       </c>
       <c r="H64" t="n">
         <v>18500</v>
@@ -2254,7 +2254,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338453292847</v>
+        <v>3.06338429450989</v>
       </c>
       <c r="H65" t="n">
         <v>5500</v>
@@ -2457,7 +2457,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820879936218</v>
+        <v>2.70820951461792</v>
       </c>
       <c r="H72" t="n">
         <v>15500</v>
@@ -2631,7 +2631,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459006309509</v>
+        <v>2.97459030151367</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.15217781066895</v>
+        <v>3.15217804908752</v>
       </c>
       <c r="H85" t="n">
         <v>19000</v>
@@ -2863,7 +2863,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.15217781066895</v>
+        <v>3.15217804908752</v>
       </c>
       <c r="H86" t="n">
         <v>7000</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670307159424</v>
+        <v>3.0767035484314</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3037,7 +3037,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.17437648773193</v>
+        <v>3.17437624931335</v>
       </c>
       <c r="H92" t="n">
         <v>19000</v>
@@ -3153,7 +3153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338453292847</v>
+        <v>3.06338429450989</v>
       </c>
       <c r="H96" t="n">
         <v>4500</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.032306432724</v>
+        <v>3.03230619430542</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.10334134101868</v>
+        <v>3.1033411026001</v>
       </c>
       <c r="H100" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.15217781066895</v>
+        <v>3.15217804908752</v>
       </c>
       <c r="H101" t="n">
         <v>14500</v>
@@ -3327,7 +3327,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G102" t="n">
-        <v>3.2320921421051</v>
+        <v>3.23209261894226</v>
       </c>
       <c r="H102" t="n">
         <v>28000</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881631851196</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545411109924</v>
+        <v>3.20545434951782</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3414,7 +3414,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.08114290237427</v>
+        <v>3.08114314079285</v>
       </c>
       <c r="H105" t="n">
         <v>22500</v>
@@ -3559,7 +3559,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H110" t="n">
         <v>14000</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023661613464</v>
+        <v>2.89023637771606</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H114" t="n">
         <v>4000</v>
@@ -3704,7 +3704,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8591582775116</v>
+        <v>2.85915851593018</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3936,7 +3936,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H123" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4110,7 +4110,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H129" t="n">
         <v>39500</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588269233704</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4284,7 +4284,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H135" t="n">
         <v>2500</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.67269158363342</v>
+        <v>2.672691822052</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4400,7 +4400,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713141441345</v>
+        <v>2.67713165283203</v>
       </c>
       <c r="H139" t="n">
         <v>2500</v>
@@ -4429,7 +4429,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H140" t="n">
         <v>5500</v>
@@ -4458,7 +4458,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H141" t="n">
         <v>4500</v>
@@ -4545,7 +4545,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H144" t="n">
         <v>72000</v>
@@ -4574,7 +4574,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>2.71708869934082</v>
+        <v>2.71708846092224</v>
       </c>
       <c r="H145" t="n">
         <v>21000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -5009,7 +5009,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H160" t="n">
         <v>1500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5154,7 +5154,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>2.78368401527405</v>
+        <v>2.78368425369263</v>
       </c>
       <c r="H165" t="n">
         <v>33000</v>
@@ -5183,7 +5183,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H166" t="n">
         <v>6000</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144286155701</v>
+        <v>2.80144262313843</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5299,7 +5299,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H170" t="n">
         <v>4500</v>
@@ -5328,7 +5328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H171" t="n">
         <v>7500</v>
@@ -5357,7 +5357,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040795326233</v>
+        <v>2.73040747642517</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.7792444229126</v>
+        <v>2.77924418449402</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5531,7 +5531,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H178" t="n">
         <v>9500</v>
@@ -5560,7 +5560,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G179" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H179" t="n">
         <v>6500</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588269233704</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5763,7 +5763,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H186" t="n">
         <v>66000</v>
@@ -5792,7 +5792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5879,7 +5879,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G190" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H191" t="n">
         <v>9500</v>
@@ -5937,7 +5937,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77036452293396</v>
+        <v>2.77036499977112</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6082,7 +6082,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H197" t="n">
         <v>10500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252024650574</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588269233704</v>
+        <v>2.80588221549988</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6256,7 +6256,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>2.85027933120728</v>
+        <v>2.8502790927887</v>
       </c>
       <c r="H203" t="n">
         <v>26000</v>
@@ -6314,7 +6314,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H205" t="n">
         <v>2500</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6546,7 +6546,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H213" t="n">
         <v>37000</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6720,7 +6720,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G219" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H219" t="n">
         <v>9000</v>
@@ -6807,7 +6807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H222" t="n">
         <v>11500</v>
@@ -6836,7 +6836,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H223" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393754005432</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973728179932</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7097,7 +7097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H232" t="n">
         <v>32000</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393754005432</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813779830933</v>
+        <v>2.65813755989075</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813779830933</v>
+        <v>2.65813755989075</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708755493164</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708755493164</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7445,7 +7445,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7503,7 +7503,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H246" t="n">
         <v>6000</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708755493164</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7619,7 +7619,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H250" t="n">
         <v>17500</v>
@@ -7648,7 +7648,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H251" t="n">
         <v>24500</v>
@@ -7677,7 +7677,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>2.8371365070343</v>
+        <v>2.83713674545288</v>
       </c>
       <c r="H252" t="n">
         <v>10000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503625869751</v>
+        <v>2.85503649711609</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7822,7 +7822,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H257" t="n">
         <v>19000</v>
@@ -7851,7 +7851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133700370789</v>
+        <v>2.80133676528931</v>
       </c>
       <c r="H258" t="n">
         <v>14000</v>
@@ -8025,7 +8025,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G264" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8228,7 +8228,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>2.7834370136261</v>
+        <v>2.78343677520752</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>2.81923699378967</v>
+        <v>2.81923651695251</v>
       </c>
       <c r="H272" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8344,7 +8344,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G275" t="n">
-        <v>2.76553678512573</v>
+        <v>2.76553702354431</v>
       </c>
       <c r="H275" t="n">
         <v>5500</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973728179932</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H282" t="n">
         <v>1500</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973728179932</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973728179932</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393754005432</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393730163574</v>
+        <v>2.69393754005432</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973728179932</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238629341125</v>
+        <v>2.79238677024841</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -9127,7 +9127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G302" t="n">
-        <v>2.7834370136261</v>
+        <v>2.78343677520752</v>
       </c>
       <c r="H302" t="n">
         <v>19000</v>
@@ -9156,7 +9156,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H303" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H308" t="n">
         <v>3500</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9388,7 +9388,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128781318665</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233757972717</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9562,7 +9562,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.55968737602234</v>
+        <v>2.5596878528595</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G320" t="n">
-        <v>2.55968737602234</v>
+        <v>2.5596878528595</v>
       </c>
       <c r="H320" t="n">
         <v>61000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708755493164</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758808135986</v>
+        <v>2.57758784294128</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -10084,7 +10084,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.51050353050232</v>
+        <v>2.51050329208374</v>
       </c>
       <c r="H335" t="n">
         <v>37500</v>
@@ -10229,7 +10229,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H340" t="n">
         <v>4000</v>
@@ -10461,7 +10461,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49244236946106</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H348" t="n">
         <v>11000</v>
@@ -10490,7 +10490,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.51050353050232</v>
+        <v>2.51050329208374</v>
       </c>
       <c r="H349" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>2.49244236946106</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.4743812084198</v>
+        <v>2.47438097000122</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -11128,7 +11128,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49244236946106</v>
+        <v>2.49244213104248</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45631957054138</v>
+        <v>2.45631980895996</v>
       </c>
       <c r="H372" t="n">
         <v>2000</v>
@@ -11186,7 +11186,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341155052185</v>
+        <v>2.48341202735901</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G374" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H374" t="n">
         <v>9500</v>
@@ -11244,7 +11244,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>2.41116714477539</v>
+        <v>2.41116690635681</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.42922830581665</v>
+        <v>2.42922806739807</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698318481445</v>
+        <v>2.35698366165161</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H381" t="n">
         <v>6000</v>
@@ -11447,7 +11447,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H382" t="n">
         <v>2500</v>
@@ -11476,7 +11476,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.30279970169067</v>
+        <v>2.30280017852783</v>
       </c>
       <c r="H383" t="n">
         <v>2500</v>
@@ -11505,7 +11505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.29376912117004</v>
+        <v>2.2937695980072</v>
       </c>
       <c r="H384" t="n">
         <v>11500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11650,7 +11650,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958587646484</v>
+        <v>2.23958563804626</v>
       </c>
       <c r="H389" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11766,7 +11766,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.19443297386169</v>
+        <v>2.19443273544312</v>
       </c>
       <c r="H393" t="n">
         <v>3000</v>
@@ -11795,7 +11795,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G394" t="n">
-        <v>2.19443297386169</v>
+        <v>2.19443273544312</v>
       </c>
       <c r="H394" t="n">
         <v>3000</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.15831065177917</v>
+        <v>2.1583104133606</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11940,7 +11940,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.18540215492249</v>
+        <v>2.18540239334106</v>
       </c>
       <c r="H399" t="n">
         <v>18500</v>
@@ -11969,7 +11969,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>2.17637205123901</v>
+        <v>2.17637157440186</v>
       </c>
       <c r="H400" t="n">
         <v>21500</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.2124936580658</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12056,7 +12056,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H403" t="n">
         <v>8500</v>
@@ -12085,7 +12085,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H404" t="n">
         <v>8000</v>
@@ -12143,7 +12143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.27570796012878</v>
+        <v>2.27570819854736</v>
       </c>
       <c r="H406" t="n">
         <v>1500</v>
@@ -12172,7 +12172,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H407" t="n">
         <v>7500</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.2576470375061</v>
+        <v>2.25764727592468</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12288,7 +12288,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G411" t="n">
-        <v>2.17637205123901</v>
+        <v>2.17637157440186</v>
       </c>
       <c r="H411" t="n">
         <v>8000</v>
@@ -12346,7 +12346,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>2.06800436973572</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H413" t="n">
         <v>15500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703542709351</v>
+        <v>2.07703518867493</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12404,7 +12404,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>2.06800436973572</v>
+        <v>2.06800484657288</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99576008319855</v>
+        <v>1.99575996398926</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.9506071805954</v>
+        <v>1.95060694217682</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12549,7 +12549,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G420" t="n">
-        <v>1.81514823436737</v>
+        <v>1.81514811515808</v>
       </c>
       <c r="H420" t="n">
         <v>9000</v>
@@ -12578,7 +12578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G421" t="n">
-        <v>1.77451062202454</v>
+        <v>1.77451050281525</v>
       </c>
       <c r="H421" t="n">
         <v>12000</v>
@@ -12665,7 +12665,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489419460297</v>
+        <v>1.44489407539368</v>
       </c>
       <c r="H424" t="n">
         <v>3000</v>
@@ -12694,7 +12694,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489419460297</v>
+        <v>1.44489407539368</v>
       </c>
       <c r="H425" t="n">
         <v>5000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364473342896</v>
+        <v>1.22364461421967</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12897,7 +12897,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.23267531394958</v>
+        <v>1.2326751947403</v>
       </c>
       <c r="H432" t="n">
         <v>2500</v>
@@ -12984,7 +12984,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>1.37264943122864</v>
+        <v>1.37264931201935</v>
       </c>
       <c r="H435" t="n">
         <v>4000</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846570968628</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846570968628</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13071,7 +13071,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>1.2958892583847</v>
+        <v>1.29588937759399</v>
       </c>
       <c r="H438" t="n">
         <v>7000</v>
@@ -13129,7 +13129,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G440" t="n">
-        <v>1.36361885070801</v>
+        <v>1.36361873149872</v>
       </c>
       <c r="H440" t="n">
         <v>6000</v>
@@ -13158,7 +13158,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.36361885070801</v>
+        <v>1.36361873149872</v>
       </c>
       <c r="H441" t="n">
         <v>5500</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.60292935371399</v>
+        <v>1.6029292345047</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13303,7 +13303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G446" t="n">
-        <v>1.62550580501556</v>
+        <v>1.62550568580627</v>
       </c>
       <c r="H446" t="n">
         <v>8500</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259754657745</v>
+        <v>1.65259766578674</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13361,7 +13361,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.670658826828</v>
+        <v>1.67065894603729</v>
       </c>
       <c r="H448" t="n">
         <v>19500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162824630737</v>
+        <v>1.66162836551666</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13419,7 +13419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193393230438</v>
       </c>
       <c r="H450" t="n">
         <v>30500</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290347099304</v>
+        <v>1.74290335178375</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13477,7 +13477,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193405151367</v>
+        <v>1.75193393230438</v>
       </c>
       <c r="H452" t="n">
         <v>5000</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160224437714</v>
+        <v>1.80160212516785</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13622,7 +13622,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030101776123</v>
+        <v>1.86030125617981</v>
       </c>
       <c r="H457" t="n">
         <v>7500</v>
@@ -13651,7 +13651,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G458" t="n">
-        <v>1.88739287853241</v>
+        <v>1.88739275932312</v>
       </c>
       <c r="H458" t="n">
         <v>500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984966754913</v>
+        <v>1.75984978675842</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13796,7 +13796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>1.57243728637695</v>
+        <v>1.57243716716766</v>
       </c>
       <c r="H463" t="n">
         <v>9500</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13912,7 +13912,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G467" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H467" t="n">
         <v>5000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -13999,7 +13999,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G470" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H470" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G471" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H471" t="n">
         <v>3500</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14260,7 +14260,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H479" t="n">
         <v>1000</v>
@@ -14289,7 +14289,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H480" t="n">
         <v>4000</v>
@@ -14318,7 +14318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G481" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G482" t="n">
-        <v>1.72785258293152</v>
+        <v>1.72785246372223</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14376,7 +14376,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G483" t="n">
-        <v>1.73699462413788</v>
+        <v>1.73699450492859</v>
       </c>
       <c r="H483" t="n">
         <v>8000</v>
@@ -14405,7 +14405,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H484" t="n">
         <v>46500</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897796630859</v>
+        <v>1.92897820472717</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14463,7 +14463,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G486" t="n">
-        <v>1.82384431362152</v>
+        <v>1.82384419441223</v>
       </c>
       <c r="H486" t="n">
         <v>9500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412571907043</v>
+        <v>1.87412559986115</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14521,7 +14521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.80098915100098</v>
+        <v>1.80098927021027</v>
       </c>
       <c r="H488" t="n">
         <v>7500</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326752185822</v>
+        <v>1.88326776027679</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14579,7 +14579,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H490" t="n">
         <v>500</v>
@@ -14608,7 +14608,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83755743503571</v>
+        <v>1.83755731582642</v>
       </c>
       <c r="H491" t="n">
         <v>2000</v>
@@ -14637,7 +14637,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.83755743503571</v>
+        <v>1.83755731582642</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G493" t="n">
-        <v>1.82384431362152</v>
+        <v>1.82384419441223</v>
       </c>
       <c r="H493" t="n">
         <v>1500</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270506858826</v>
+        <v>1.78270494937897</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14753,7 +14753,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G496" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813398838043</v>
       </c>
       <c r="H496" t="n">
         <v>7500</v>
@@ -14782,7 +14782,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.77813386917114</v>
+        <v>1.77813398838043</v>
       </c>
       <c r="H497" t="n">
         <v>2000</v>
@@ -14811,7 +14811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G498" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H498" t="n">
         <v>2000</v>
@@ -14840,7 +14840,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G499" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -14869,7 +14869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H500" t="n">
         <v>2000</v>
@@ -14898,7 +14898,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74613654613495</v>
+        <v>1.74613666534424</v>
       </c>
       <c r="H502" t="n">
         <v>5000</v>
@@ -14956,7 +14956,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H503" t="n">
         <v>500</v>
@@ -14985,7 +14985,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G504" t="n">
-        <v>1.75070750713348</v>
+        <v>1.75070762634277</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G505" t="n">
-        <v>1.72785258293152</v>
+        <v>1.72785246372223</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.74156546592712</v>
+        <v>1.7415657043457</v>
       </c>
       <c r="H506" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.74156546592712</v>
+        <v>1.7415657043457</v>
       </c>
       <c r="H507" t="n">
         <v>500</v>
@@ -15101,7 +15101,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.74156546592712</v>
+        <v>1.7415657043457</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G512" t="n">
-        <v>1.73699462413788</v>
+        <v>1.73699450492859</v>
       </c>
       <c r="H512" t="n">
         <v>4500</v>
@@ -15246,7 +15246,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G513" t="n">
-        <v>1.73699462413788</v>
+        <v>1.73699450492859</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G514" t="n">
-        <v>1.73699462413788</v>
+        <v>1.73699450492859</v>
       </c>
       <c r="H514" t="n">
         <v>500</v>
@@ -15304,7 +15304,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H515" t="n">
         <v>1000</v>
@@ -15333,7 +15333,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H516" t="n">
         <v>500</v>
@@ -15362,7 +15362,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>1.77356278896332</v>
+        <v>1.77356290817261</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.7552787065506</v>
+        <v>1.75527858734131</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15449,7 +15449,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H520" t="n">
         <v>10500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G523" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H524" t="n">
         <v>3500</v>
@@ -15594,7 +15594,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G525" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G526" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H526" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814773082733</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15768,7 +15768,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G531" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G532" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G533" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G534" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G537" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="n">
-        <v>1.60443437099457</v>
+        <v>1.60443460941315</v>
       </c>
       <c r="H538" t="n">
         <v>10000</v>
@@ -16000,7 +16000,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G539" t="n">
-        <v>1.60443437099457</v>
+        <v>1.60443460941315</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.60443437099457</v>
+        <v>1.60443460941315</v>
       </c>
       <c r="H540" t="n">
         <v>3000</v>
@@ -16058,7 +16058,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G541" t="n">
-        <v>1.60443437099457</v>
+        <v>1.60443460941315</v>
       </c>
       <c r="H541" t="n">
         <v>500</v>
@@ -16087,7 +16087,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H549" t="n">
         <v>7000</v>
@@ -16319,7 +16319,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G551" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16406,7 +16406,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G554" t="n">
-        <v>1.65471589565277</v>
+        <v>1.65471577644348</v>
       </c>
       <c r="H554" t="n">
         <v>2000</v>
@@ -16464,7 +16464,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65471589565277</v>
+        <v>1.65471577644348</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H556" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G561" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H561" t="n">
         <v>2000</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H565" t="n">
         <v>500</v>
@@ -16783,7 +16783,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G566" t="n">
-        <v>1.51758480072021</v>
+        <v>1.51758468151093</v>
       </c>
       <c r="H566" t="n">
         <v>10000</v>
@@ -16870,7 +16870,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H569" t="n">
         <v>2500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16928,7 +16928,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G571" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H571" t="n">
         <v>6500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -16986,7 +16986,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66385793685913</v>
+        <v>1.66385805606842</v>
       </c>
       <c r="H573" t="n">
         <v>1000</v>
@@ -17015,7 +17015,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H574" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.79184710979462</v>
+        <v>1.79184699058533</v>
       </c>
       <c r="H576" t="n">
         <v>17500</v>
@@ -17131,7 +17131,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G578" t="n">
-        <v>1.73242354393005</v>
+        <v>1.73242342472076</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6912841796875</v>
+        <v>1.69128429889679</v>
       </c>
       <c r="H579" t="n">
         <v>10000</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214225769043</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17247,7 +17247,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H582" t="n">
         <v>5500</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900557041168</v>
+        <v>1.60900545120239</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17305,7 +17305,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H584" t="n">
         <v>500</v>
@@ -17334,7 +17334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.63287806510925</v>
+        <v>1.63287794589996</v>
       </c>
       <c r="H585" t="n">
         <v>1500</v>
@@ -17363,7 +17363,7 @@
         <v>1.75</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G587" t="n">
-        <v>1.52154529094696</v>
+        <v>1.52154541015625</v>
       </c>
       <c r="H587" t="n">
         <v>6500</v>
@@ -17479,7 +17479,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G590" t="n">
-        <v>1.53082299232483</v>
+        <v>1.53082311153412</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17653,7 +17653,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G596" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H596" t="n">
         <v>5000</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>1.52618420124054</v>
+        <v>1.52618432044983</v>
       </c>
       <c r="H598" t="n">
         <v>3500</v>
@@ -17740,7 +17740,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H599" t="n">
         <v>3500</v>
@@ -17798,7 +17798,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>1.57721161842346</v>
+        <v>1.57721173763275</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>1.75</v>
       </c>
       <c r="G602" t="n">
-        <v>1.62360036373138</v>
+        <v>1.62360024452209</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17885,7 +17885,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G604" t="n">
-        <v>1.77204358577728</v>
+        <v>1.77204370498657</v>
       </c>
       <c r="H604" t="n">
         <v>8500</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18175,7 +18175,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>1.81843233108521</v>
+        <v>1.81843221187592</v>
       </c>
       <c r="H614" t="n">
         <v>4000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820820808411</v>
+        <v>2.07820844650269</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615349292755</v>
+        <v>1.97615361213684</v>
       </c>
       <c r="H625" t="n">
         <v>14000</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.9112092256546</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18581,7 +18581,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326441764832</v>
+        <v>2.01326417922974</v>
       </c>
       <c r="H628" t="n">
         <v>10500</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748626708984</v>
+        <v>2.08748602867126</v>
       </c>
       <c r="H629" t="n">
         <v>42500</v>
@@ -18639,7 +18639,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.00398659706116</v>
+        <v>2.00398683547974</v>
       </c>
       <c r="H630" t="n">
         <v>13000</v>
@@ -18697,7 +18697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>2.91320276260376</v>
+        <v>2.91320300102234</v>
       </c>
       <c r="H632" t="n">
         <v>262000</v>
@@ -18755,7 +18755,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H634" t="n">
         <v>177500</v>
@@ -18784,7 +18784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H635" t="n">
         <v>49500</v>
@@ -18813,7 +18813,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G636" t="n">
-        <v>2.84825849533081</v>
+        <v>2.84825873374939</v>
       </c>
       <c r="H636" t="n">
         <v>10500</v>
@@ -18842,7 +18842,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G637" t="n">
-        <v>2.84825849533081</v>
+        <v>2.84825873374939</v>
       </c>
       <c r="H637" t="n">
         <v>39500</v>
@@ -18871,7 +18871,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H638" t="n">
         <v>15500</v>
@@ -18929,7 +18929,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G640" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H640" t="n">
         <v>8500</v>
@@ -18958,7 +18958,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>2.52353858947754</v>
+        <v>2.52353882789612</v>
       </c>
       <c r="H641" t="n">
         <v>36000</v>
@@ -18987,7 +18987,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.6441490650177</v>
+        <v>2.64414882659912</v>
       </c>
       <c r="H642" t="n">
         <v>34000</v>
@@ -19074,7 +19074,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H645" t="n">
         <v>22000</v>
@@ -19219,7 +19219,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.54209423065186</v>
+        <v>2.54209399223328</v>
       </c>
       <c r="H650" t="n">
         <v>4500</v>
@@ -19277,7 +19277,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.34726238250732</v>
+        <v>2.34726214408875</v>
       </c>
       <c r="H652" t="n">
         <v>52500</v>
@@ -19306,7 +19306,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H653" t="n">
         <v>19500</v>
@@ -19335,7 +19335,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H654" t="n">
         <v>24000</v>
@@ -19364,7 +19364,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H655" t="n">
         <v>36500</v>
@@ -19422,7 +19422,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H657" t="n">
         <v>9000</v>
@@ -19451,7 +19451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.30087351799011</v>
+        <v>2.30087327957153</v>
       </c>
       <c r="H658" t="n">
         <v>16500</v>
@@ -19480,7 +19480,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.31015110015869</v>
+        <v>2.31015133857727</v>
       </c>
       <c r="H659" t="n">
         <v>10500</v>
@@ -19509,7 +19509,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G660" t="n">
-        <v>2.31015110015869</v>
+        <v>2.31015133857727</v>
       </c>
       <c r="H660" t="n">
         <v>8000</v>
@@ -19538,7 +19538,7 @@
         <v>2.5</v>
       </c>
       <c r="G661" t="n">
-        <v>2.31942892074585</v>
+        <v>2.31942915916443</v>
       </c>
       <c r="H661" t="n">
         <v>210500</v>
@@ -19596,7 +19596,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H663" t="n">
         <v>11500</v>
@@ -19625,7 +19625,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>2.39365077018738</v>
+        <v>2.3936505317688</v>
       </c>
       <c r="H664" t="n">
         <v>5500</v>
@@ -19654,7 +19654,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.34726238250732</v>
+        <v>2.34726214408875</v>
       </c>
       <c r="H665" t="n">
         <v>5500</v>
@@ -19741,7 +19741,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H668" t="n">
         <v>14000</v>
@@ -19770,7 +19770,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>2.43076157569885</v>
+        <v>2.43076133728027</v>
       </c>
       <c r="H669" t="n">
         <v>1500</v>
@@ -19799,7 +19799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H670" t="n">
         <v>4500</v>
@@ -19828,7 +19828,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H671" t="n">
         <v>8000</v>
@@ -19857,7 +19857,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37509512901306</v>
+        <v>2.37509536743164</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57920503616333</v>
+        <v>2.57920479774475</v>
       </c>
       <c r="H674" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57920503616333</v>
+        <v>2.57920479774475</v>
       </c>
       <c r="H675" t="n">
         <v>12000</v>
@@ -20060,7 +20060,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>2.7647590637207</v>
+        <v>2.76475954055786</v>
       </c>
       <c r="H679" t="n">
         <v>15500</v>
@@ -20118,7 +20118,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G681" t="n">
-        <v>2.68125987052917</v>
+        <v>2.68126010894775</v>
       </c>
       <c r="H681" t="n">
         <v>13000</v>
@@ -20147,7 +20147,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G682" t="n">
-        <v>2.6719822883606</v>
+        <v>2.67198204994202</v>
       </c>
       <c r="H682" t="n">
         <v>23000</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970333099365</v>
+        <v>2.82970309257507</v>
       </c>
       <c r="H683" t="n">
         <v>121000</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.83898115158081</v>
+        <v>2.83898091316223</v>
       </c>
       <c r="H684" t="n">
         <v>17000</v>
@@ -20321,7 +20321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G688" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>2.80187010765076</v>
+        <v>2.80187034606934</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H691" t="n">
         <v>110000</v>
@@ -20437,7 +20437,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H692" t="n">
         <v>52500</v>
@@ -20466,7 +20466,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H693" t="n">
         <v>128500</v>
@@ -20495,7 +20495,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G694" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H694" t="n">
         <v>12500</v>
@@ -20582,7 +20582,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>2.83898115158081</v>
+        <v>2.83898091316223</v>
       </c>
       <c r="H697" t="n">
         <v>5500</v>
@@ -20756,7 +20756,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.82042574882507</v>
+        <v>2.82042551040649</v>
       </c>
       <c r="H703" t="n">
         <v>9500</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -20901,7 +20901,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G708" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H708" t="n">
         <v>7000</v>
@@ -20988,7 +20988,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>3.04309058189392</v>
+        <v>3.0430908203125</v>
       </c>
       <c r="H711" t="n">
         <v>6000</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742461204529</v>
+        <v>2.98742437362671</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -21104,7 +21104,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H715" t="n">
         <v>6000</v>
@@ -21133,7 +21133,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G716" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H716" t="n">
         <v>4000</v>
@@ -21220,7 +21220,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H719" t="n">
         <v>500</v>
@@ -21336,7 +21336,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G723" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H723" t="n">
         <v>2000</v>
@@ -21365,7 +21365,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G724" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H724" t="n">
         <v>5000</v>
@@ -21394,7 +21394,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G725" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H725" t="n">
         <v>11500</v>
@@ -21423,7 +21423,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.99626874923706</v>
+        <v>2.99626851081848</v>
       </c>
       <c r="H726" t="n">
         <v>5500</v>
@@ -21510,7 +21510,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G729" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H729" t="n">
         <v>3500</v>
@@ -21539,7 +21539,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H730" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G735" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H735" t="n">
         <v>3500</v>
@@ -21713,7 +21713,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G736" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21858,7 +21858,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G741" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H741" t="n">
         <v>7500</v>
@@ -21887,7 +21887,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H742" t="n">
         <v>2500</v>
@@ -21916,7 +21916,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H743" t="n">
         <v>10000</v>
@@ -22003,7 +22003,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G746" t="n">
-        <v>2.95857977867126</v>
+        <v>2.95858001708984</v>
       </c>
       <c r="H746" t="n">
         <v>10500</v>
@@ -22032,7 +22032,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H747" t="n">
         <v>72500</v>
@@ -22061,7 +22061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H748" t="n">
         <v>24500</v>
@@ -22148,7 +22148,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H751" t="n">
         <v>37000</v>
@@ -22177,7 +22177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H752" t="n">
         <v>5500</v>
@@ -22264,7 +22264,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H755" t="n">
         <v>1000</v>
@@ -22583,7 +22583,7 @@
         <v>3.5</v>
       </c>
       <c r="G766" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H766" t="n">
         <v>11000</v>
@@ -22612,7 +22612,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G767" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H767" t="n">
         <v>9500</v>
@@ -22641,7 +22641,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H768" t="n">
         <v>7000</v>
@@ -22786,7 +22786,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H773" t="n">
         <v>13000</v>
@@ -22902,7 +22902,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H777" t="n">
         <v>10000</v>
@@ -22960,7 +22960,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H779" t="n">
         <v>5000</v>
@@ -22989,7 +22989,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H780" t="n">
         <v>4000</v>
@@ -23018,7 +23018,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G781" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H781" t="n">
         <v>3500</v>
@@ -23047,7 +23047,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H782" t="n">
         <v>1500</v>
@@ -23076,7 +23076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H786" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H787" t="n">
         <v>7000</v>
@@ -23221,7 +23221,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H788" t="n">
         <v>5000</v>
@@ -23250,7 +23250,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G789" t="n">
-        <v>3.10933542251587</v>
+        <v>3.10933518409729</v>
       </c>
       <c r="H789" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23395,7 +23395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H794" t="n">
         <v>9000</v>
@@ -23511,7 +23511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H798" t="n">
         <v>7000</v>
@@ -23685,7 +23685,7 @@
         <v>3.5</v>
       </c>
       <c r="G804" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H804" t="n">
         <v>29000</v>
@@ -23743,7 +23743,7 @@
         <v>3.5</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29778003692627</v>
+        <v>3.29777979850769</v>
       </c>
       <c r="H806" t="n">
         <v>15000</v>
@@ -23801,7 +23801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H808" t="n">
         <v>6500</v>
@@ -23830,7 +23830,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.1281795501709</v>
+        <v>3.12817978858948</v>
       </c>
       <c r="H809" t="n">
         <v>14500</v>
@@ -23859,7 +23859,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H810" t="n">
         <v>3500</v>
@@ -23946,7 +23946,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H813" t="n">
         <v>7000</v>
@@ -24004,7 +24004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.09049081802368</v>
+        <v>3.09049105644226</v>
       </c>
       <c r="H815" t="n">
         <v>15000</v>
@@ -24033,7 +24033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355749130249</v>
+        <v>3.20355772972107</v>
       </c>
       <c r="H816" t="n">
         <v>44000</v>
@@ -24062,7 +24062,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.24124670028687</v>
+        <v>3.24124646186829</v>
       </c>
       <c r="H817" t="n">
         <v>19000</v>
@@ -24207,7 +24207,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G822" t="n">
-        <v>3.61813545227051</v>
+        <v>3.61813569068909</v>
       </c>
       <c r="H822" t="n">
         <v>59500</v>
@@ -24236,7 +24236,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H823" t="n">
         <v>29000</v>
@@ -24265,7 +24265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391362190247</v>
+        <v>3.52391338348389</v>
       </c>
       <c r="H824" t="n">
         <v>23500</v>
@@ -24497,7 +24497,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>3.7877357006073</v>
+        <v>3.78773593902588</v>
       </c>
       <c r="H832" t="n">
         <v>21500</v>
@@ -24526,7 +24526,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>4.01386976242065</v>
+        <v>4.0138692855835</v>
       </c>
       <c r="H833" t="n">
         <v>119000</v>
@@ -24613,7 +24613,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H836" t="n">
         <v>184500</v>
@@ -24816,7 +24816,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H843" t="n">
         <v>32000</v>
@@ -24874,7 +24874,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H845" t="n">
         <v>16500</v>
@@ -24961,7 +24961,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H848" t="n">
         <v>22000</v>
@@ -24990,7 +24990,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H849" t="n">
         <v>25000</v>
@@ -25106,7 +25106,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25135,7 +25135,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H854" t="n">
         <v>16000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H856" t="n">
         <v>4500</v>
@@ -25222,7 +25222,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H857" t="n">
         <v>18000</v>
@@ -25251,7 +25251,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G858" t="n">
-        <v>4.01386976242065</v>
+        <v>4.0138692855835</v>
       </c>
       <c r="H858" t="n">
         <v>39000</v>
@@ -25309,7 +25309,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502420425415</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H860" t="n">
         <v>49000</v>
@@ -25396,7 +25396,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>3.97618007659912</v>
+        <v>3.9761803150177</v>
       </c>
       <c r="H863" t="n">
         <v>58000</v>
@@ -25425,7 +25425,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H864" t="n">
         <v>12000</v>
@@ -25541,7 +25541,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H868" t="n">
         <v>16000</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H875" t="n">
         <v>6500</v>
@@ -25773,7 +25773,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G876" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H876" t="n">
         <v>72000</v>
@@ -26121,7 +26121,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G888" t="n">
-        <v>4.50382518768311</v>
+        <v>4.50382566452026</v>
       </c>
       <c r="H888" t="n">
         <v>46000</v>
@@ -26353,7 +26353,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H896" t="n">
         <v>22500</v>
@@ -26469,7 +26469,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>5.27644824981689</v>
+        <v>5.27644777297974</v>
       </c>
       <c r="H900" t="n">
         <v>253500</v>
@@ -26527,7 +26527,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H902" t="n">
         <v>88500</v>
@@ -26556,7 +26556,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H903" t="n">
         <v>32500</v>
@@ -26585,7 +26585,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>5.1351146697998</v>
+        <v>5.13511419296265</v>
       </c>
       <c r="H904" t="n">
         <v>67500</v>
@@ -26614,7 +26614,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>5.27644824981689</v>
+        <v>5.27644777297974</v>
       </c>
       <c r="H905" t="n">
         <v>36500</v>
@@ -26643,7 +26643,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G906" t="n">
-        <v>5.1351146697998</v>
+        <v>5.13511419296265</v>
       </c>
       <c r="H906" t="n">
         <v>35000</v>
@@ -26672,7 +26672,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G907" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H907" t="n">
         <v>170500</v>
@@ -26701,7 +26701,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H908" t="n">
         <v>23500</v>
@@ -26730,7 +26730,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -26759,7 +26759,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H910" t="n">
         <v>22500</v>
@@ -26817,7 +26817,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H912" t="n">
         <v>14000</v>
@@ -26875,7 +26875,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089164733887</v>
+        <v>5.04089212417603</v>
       </c>
       <c r="H914" t="n">
         <v>37000</v>
@@ -26904,7 +26904,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H915" t="n">
         <v>16000</v>
@@ -26933,7 +26933,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G916" t="n">
-        <v>4.99378156661987</v>
+        <v>4.99378108978271</v>
       </c>
       <c r="H916" t="n">
         <v>26000</v>
@@ -26962,7 +26962,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H917" t="n">
         <v>61000</v>
@@ -26991,7 +26991,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H918" t="n">
         <v>13000</v>
@@ -27049,7 +27049,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H920" t="n">
         <v>12500</v>
@@ -27107,7 +27107,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244798660278</v>
+        <v>4.85244750976562</v>
       </c>
       <c r="H922" t="n">
         <v>5000</v>
@@ -27281,7 +27281,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G928" t="n">
-        <v>4.44729137420654</v>
+        <v>4.4472918510437</v>
       </c>
       <c r="H928" t="n">
         <v>9000</v>
@@ -27368,7 +27368,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5616021156311</v>
+        <v>3.56160235404968</v>
       </c>
       <c r="H931" t="n">
         <v>72500</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.93849110603333</v>
+        <v>3.9384913444519</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.88195776939392</v>
+        <v>3.8819580078125</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502420425415</v>
+        <v>3.99502491950989</v>
       </c>
       <c r="H936" t="n">
         <v>4500</v>
@@ -27542,7 +27542,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271436691284</v>
+        <v>4.03271389007568</v>
       </c>
       <c r="H937" t="n">
         <v>12000</v>
@@ -27600,7 +27600,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H939" t="n">
         <v>8000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27658,7 +27658,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H941" t="n">
         <v>3500</v>
@@ -27745,7 +27745,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H944" t="n">
         <v>3500</v>
@@ -27890,7 +27890,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955806732178</v>
+        <v>4.89955854415894</v>
       </c>
       <c r="H949" t="n">
         <v>30500</v>
@@ -27977,7 +27977,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880266189575</v>
+        <v>4.74880313873291</v>
       </c>
       <c r="H952" t="n">
         <v>8000</v>
@@ -28209,7 +28209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G960" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H960" t="n">
         <v>42500</v>
@@ -28296,7 +28296,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G963" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H963" t="n">
         <v>10500</v>
@@ -28325,7 +28325,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G964" t="n">
-        <v>4.10809135437012</v>
+        <v>4.10809183120728</v>
       </c>
       <c r="H964" t="n">
         <v>7000</v>
@@ -28354,7 +28354,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>4.18346977233887</v>
+        <v>4.18346929550171</v>
       </c>
       <c r="H965" t="n">
         <v>3500</v>
@@ -28383,7 +28383,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404747009277</v>
+        <v>4.17404699325562</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28586,7 +28586,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>4.31538105010986</v>
+        <v>4.31538057327271</v>
       </c>
       <c r="H973" t="n">
         <v>11500</v>
@@ -61536,6 +61536,64 @@
         <v>500</v>
       </c>
       <c r="I2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2110" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2111" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I2111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614682197571</v>
+        <v>3.59614706039429</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -456,7 +456,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G3" t="n">
-        <v>3.74709582328796</v>
+        <v>3.74709606170654</v>
       </c>
       <c r="H3" t="n">
         <v>657000</v>
@@ -485,7 +485,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589240074158</v>
+        <v>3.62589263916016</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244758605957</v>
+        <v>3.52244806289673</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -543,7 +543,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42743849754333</v>
+        <v>3.42743825912476</v>
       </c>
       <c r="H6" t="n">
         <v>110500</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.34752416610718</v>
+        <v>3.34752440452576</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274472236633</v>
+        <v>3.45274496078491</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -688,7 +688,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666083335876</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H11" t="n">
         <v>156500</v>
@@ -717,7 +717,7 @@
         <v>3.65750002861023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24763131141663</v>
+        <v>3.24763107299805</v>
       </c>
       <c r="H12" t="n">
         <v>215500</v>
@@ -775,7 +775,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.22321319580078</v>
+        <v>3.2232129573822</v>
       </c>
       <c r="H14" t="n">
         <v>55000</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -891,7 +891,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416525840759</v>
+        <v>3.16416501998901</v>
       </c>
       <c r="H18" t="n">
         <v>39500</v>
@@ -978,7 +978,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01898717880249</v>
+        <v>3.01898741722107</v>
       </c>
       <c r="H21" t="n">
         <v>50500</v>
@@ -1036,7 +1036,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96571087837219</v>
+        <v>2.96571111679077</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1065,7 +1065,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9586079120636</v>
+        <v>2.95860743522644</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1094,7 +1094,7 @@
         <v>3.3289999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.95594358444214</v>
+        <v>2.95594382286072</v>
       </c>
       <c r="H25" t="n">
         <v>500</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H26" t="n">
         <v>15500</v>
@@ -1152,7 +1152,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H27" t="n">
         <v>57500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467573165894</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8187575340271</v>
+        <v>2.81875777244568</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1239,7 +1239,7 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H30" t="n">
         <v>45000</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.83252048492432</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1326,7 +1326,7 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1355,7 +1355,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890151023865</v>
       </c>
       <c r="H34" t="n">
         <v>49500</v>
@@ -1384,7 +1384,7 @@
         <v>3.37450003623962</v>
       </c>
       <c r="G35" t="n">
-        <v>2.99634504318237</v>
+        <v>2.99634480476379</v>
       </c>
       <c r="H35" t="n">
         <v>78000</v>
@@ -1413,7 +1413,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325849533081</v>
+        <v>2.97325825691223</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1471,7 +1471,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H38" t="n">
         <v>9000</v>
@@ -1529,7 +1529,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243481636047</v>
+        <v>2.91243433952332</v>
       </c>
       <c r="H40" t="n">
         <v>9500</v>
@@ -1558,7 +1558,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H41" t="n">
         <v>11000</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H42" t="n">
         <v>3000</v>
@@ -1616,7 +1616,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.91687417030334</v>
+        <v>2.91687488555908</v>
       </c>
       <c r="H43" t="n">
         <v>3000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H44" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>3.25049996376038</v>
       </c>
       <c r="G45" t="n">
-        <v>2.88624095916748</v>
+        <v>2.88624048233032</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.27900004386902</v>
       </c>
       <c r="G46" t="n">
-        <v>2.91154670715332</v>
+        <v>2.9115469455719</v>
       </c>
       <c r="H46" t="n">
         <v>10000</v>
@@ -1761,7 +1761,7 @@
         <v>3.30949997901917</v>
       </c>
       <c r="G48" t="n">
-        <v>2.93862867355347</v>
+        <v>2.93862915039062</v>
       </c>
       <c r="H48" t="n">
         <v>19000</v>
@@ -1790,7 +1790,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.93907260894775</v>
+        <v>2.93907284736633</v>
       </c>
       <c r="H49" t="n">
         <v>4000</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.91687417030334</v>
+        <v>2.91687488555908</v>
       </c>
       <c r="H50" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.09446167945862</v>
+        <v>3.09446215629578</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08558249473572</v>
+        <v>3.0855827331543</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1935,7 +1935,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.08114314079285</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H54" t="n">
         <v>61000</v>
@@ -1964,7 +1964,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G55" t="n">
-        <v>3.13441920280457</v>
+        <v>3.13441944122314</v>
       </c>
       <c r="H55" t="n">
         <v>45500</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769502639771</v>
+        <v>3.18769574165344</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769502639771</v>
+        <v>3.18769574165344</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760983467102</v>
+        <v>3.26760959625244</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868769645691</v>
+        <v>3.29868793487549</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2109,7 +2109,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873017311096</v>
+        <v>3.25873064994812</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678874015808</v>
+        <v>2.99678897857666</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2225,7 +2225,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G64" t="n">
-        <v>3.09890174865723</v>
+        <v>3.09890151023865</v>
       </c>
       <c r="H64" t="n">
         <v>18500</v>
@@ -2254,7 +2254,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338429450989</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H65" t="n">
         <v>5500</v>
@@ -2341,7 +2341,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247753143311</v>
+        <v>2.87247729301453</v>
       </c>
       <c r="H68" t="n">
         <v>23500</v>
@@ -2370,7 +2370,7 @@
         <v>3.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H69" t="n">
         <v>15500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7348473072052</v>
+        <v>2.73484706878662</v>
       </c>
       <c r="H71" t="n">
         <v>17500</v>
@@ -2486,7 +2486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.7348473072052</v>
+        <v>2.73484706878662</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G74" t="n">
-        <v>2.74816656112671</v>
+        <v>2.74816608428955</v>
       </c>
       <c r="H74" t="n">
         <v>8500</v>
@@ -2602,7 +2602,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.92131423950195</v>
+        <v>2.92131447792053</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2718,7 +2718,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243481636047</v>
+        <v>2.91243433952332</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122880935669</v>
+        <v>3.00122833251953</v>
       </c>
       <c r="H83" t="n">
         <v>15000</v>
@@ -2805,7 +2805,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.0411856174469</v>
+        <v>3.04118609428406</v>
       </c>
       <c r="H84" t="n">
         <v>31500</v>
@@ -2921,7 +2921,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666083335876</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H88" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>3.0411856174469</v>
+        <v>3.04118609428406</v>
       </c>
       <c r="H90" t="n">
         <v>5500</v>
@@ -3008,7 +3008,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G91" t="n">
-        <v>3.07670307159424</v>
+        <v>3.07670331001282</v>
       </c>
       <c r="H91" t="n">
         <v>4500</v>
@@ -3066,7 +3066,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213533401489</v>
+        <v>3.19213509559631</v>
       </c>
       <c r="H93" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213533401489</v>
+        <v>3.19213509559631</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338429450989</v>
+        <v>3.06338405609131</v>
       </c>
       <c r="H96" t="n">
         <v>4500</v>
@@ -3182,7 +3182,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666083335876</v>
+        <v>3.11666035652161</v>
       </c>
       <c r="H97" t="n">
         <v>9500</v>
@@ -3211,7 +3211,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>3.03230667114258</v>
+        <v>3.03230619430542</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795250892639</v>
+        <v>2.94795227050781</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G102" t="n">
-        <v>3.2320921421051</v>
+        <v>3.23209238052368</v>
       </c>
       <c r="H102" t="n">
         <v>28000</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.1788158416748</v>
+        <v>3.17881608009338</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545387268066</v>
+        <v>3.20545411109924</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3414,7 +3414,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>3.08114314079285</v>
+        <v>3.08114290237427</v>
       </c>
       <c r="H105" t="n">
         <v>22500</v>
@@ -3443,7 +3443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>3.03674650192261</v>
+        <v>3.03674602508545</v>
       </c>
       <c r="H106" t="n">
         <v>20000</v>
@@ -3501,7 +3501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01898717880249</v>
+        <v>3.01898741722107</v>
       </c>
       <c r="H108" t="n">
         <v>6000</v>
@@ -3559,7 +3559,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H110" t="n">
         <v>14000</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.97015070915222</v>
+        <v>2.9701509475708</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023637771606</v>
+        <v>2.89023613929749</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H114" t="n">
         <v>4000</v>
@@ -3704,7 +3704,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019366264343</v>
+        <v>2.93019390106201</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3733,7 +3733,7 @@
         <v>3.25</v>
       </c>
       <c r="G116" t="n">
-        <v>2.88579654693604</v>
+        <v>2.88579678535461</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.84583926200867</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H117" t="n">
         <v>11500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924418449402</v>
+        <v>2.77924466133118</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85915851593018</v>
+        <v>2.8591582775116</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -3936,7 +3936,7 @@
         <v>3.125</v>
       </c>
       <c r="G123" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H123" t="n">
         <v>7000</v>
@@ -3965,7 +3965,7 @@
         <v>3.125</v>
       </c>
       <c r="G124" t="n">
-        <v>2.77480459213257</v>
+        <v>2.77480435371399</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928737640381</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>2.74372696876526</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H127" t="n">
         <v>13000</v>
@@ -4081,7 +4081,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G128" t="n">
-        <v>2.74372696876526</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H128" t="n">
         <v>2500</v>
@@ -4110,7 +4110,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H129" t="n">
         <v>39500</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4168,7 +4168,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G131" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588245391846</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924418449402</v>
+        <v>2.77924466133118</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256343841553</v>
+        <v>2.79256319999695</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G136" t="n">
-        <v>2.67269158363342</v>
+        <v>2.672691822052</v>
       </c>
       <c r="H136" t="n">
         <v>45000</v>
@@ -4458,7 +4458,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H141" t="n">
         <v>4500</v>
@@ -4487,7 +4487,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G142" t="n">
-        <v>2.74372696876526</v>
+        <v>2.74372673034668</v>
       </c>
       <c r="H142" t="n">
         <v>8500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G146" t="n">
-        <v>2.74816656112671</v>
+        <v>2.74816608428955</v>
       </c>
       <c r="H146" t="n">
         <v>11500</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592540740967</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471844673157</v>
+        <v>2.85471868515015</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032180786133</v>
+        <v>2.81032204627991</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928737640381</v>
+        <v>2.73928689956665</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592540740967</v>
+        <v>2.76592493057251</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.83252048492432</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5154,7 +5154,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>2.78368401527405</v>
+        <v>2.78368353843689</v>
       </c>
       <c r="H165" t="n">
         <v>33000</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924418449402</v>
+        <v>2.77924466133118</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144286155701</v>
+        <v>2.80144238471985</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596836090088</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5473,7 +5473,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73040747642517</v>
+        <v>2.73040771484375</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924418449402</v>
+        <v>2.77924466133118</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5531,7 +5531,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808089256287</v>
+        <v>2.82808065414429</v>
       </c>
       <c r="H178" t="n">
         <v>9500</v>
@@ -5618,7 +5618,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588245391846</v>
       </c>
       <c r="H181" t="n">
         <v>14000</v>
@@ -5647,7 +5647,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>2.84583926200867</v>
+        <v>2.84583950042725</v>
       </c>
       <c r="H182" t="n">
         <v>18500</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5705,7 +5705,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247753143311</v>
+        <v>2.87247729301453</v>
       </c>
       <c r="H184" t="n">
         <v>28000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467597007751</v>
+        <v>2.89467573165894</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596740722656</v>
+        <v>2.72596836090088</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260591506958</v>
+        <v>2.75260615348816</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.83252048492432</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.83252048492432</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.83252048492432</v>
+        <v>2.8325207233429</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.84140014648438</v>
+        <v>2.8413999080658</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6198,7 +6198,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G201" t="n">
-        <v>2.80588221549988</v>
+        <v>2.80588245391846</v>
       </c>
       <c r="H201" t="n">
         <v>10000</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364153862</v>
+        <v>2.82364130020142</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6343,7 +6343,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H210" t="n">
         <v>9000</v>
@@ -6517,7 +6517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H212" t="n">
         <v>17500</v>
@@ -6575,7 +6575,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H215" t="n">
         <v>4000</v>
@@ -6633,7 +6633,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6662,7 +6662,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868680000305</v>
       </c>
       <c r="H217" t="n">
         <v>14000</v>
@@ -6691,7 +6691,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G218" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H218" t="n">
         <v>27500</v>
@@ -6749,7 +6749,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H220" t="n">
         <v>7000</v>
@@ -6778,7 +6778,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G221" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H221" t="n">
         <v>31000</v>
@@ -6807,7 +6807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H222" t="n">
         <v>11500</v>
@@ -6836,7 +6836,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H223" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H225" t="n">
         <v>14500</v>
@@ -6952,7 +6952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H227" t="n">
         <v>27000</v>
@@ -6981,7 +6981,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H228" t="n">
         <v>36000</v>
@@ -7010,7 +7010,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G229" t="n">
-        <v>2.52388763427734</v>
+        <v>2.52388787269592</v>
       </c>
       <c r="H229" t="n">
         <v>28000</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7097,7 +7097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H232" t="n">
         <v>32000</v>
@@ -7242,7 +7242,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H237" t="n">
         <v>26000</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7416,7 +7416,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H243" t="n">
         <v>17500</v>
@@ -7445,7 +7445,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G244" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H244" t="n">
         <v>9000</v>
@@ -7503,7 +7503,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>2.64918732643127</v>
+        <v>2.64918756484985</v>
       </c>
       <c r="H246" t="n">
         <v>6000</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7590,7 +7590,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H249" t="n">
         <v>21000</v>
@@ -7706,7 +7706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>2.82818651199341</v>
+        <v>2.82818675041199</v>
       </c>
       <c r="H253" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503649711609</v>
+        <v>2.85503625869751</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7851,7 +7851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>2.80133676528931</v>
+        <v>2.80133652687073</v>
       </c>
       <c r="H258" t="n">
         <v>14000</v>
@@ -7880,7 +7880,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H259" t="n">
         <v>10000</v>
@@ -7909,7 +7909,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H260" t="n">
         <v>9500</v>
@@ -7938,7 +7938,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H261" t="n">
         <v>7000</v>
@@ -7967,7 +7967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -7996,7 +7996,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H263" t="n">
         <v>6500</v>
@@ -8054,7 +8054,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H266" t="n">
         <v>18500</v>
@@ -8112,7 +8112,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8199,7 +8199,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G270" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H270" t="n">
         <v>8500</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8315,7 +8315,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448654174805</v>
+        <v>2.77448701858521</v>
       </c>
       <c r="H276" t="n">
         <v>5000</v>
@@ -8431,7 +8431,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868703842163</v>
+        <v>2.73868680000305</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8460,7 +8460,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G279" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H280" t="n">
         <v>7500</v>
@@ -8518,7 +8518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H282" t="n">
         <v>1500</v>
@@ -8576,7 +8576,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H283" t="n">
         <v>2500</v>
@@ -8605,7 +8605,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H284" t="n">
         <v>2500</v>
@@ -8634,7 +8634,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>2.72078704833984</v>
+        <v>2.72078680992126</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G289" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H289" t="n">
         <v>500</v>
@@ -8779,7 +8779,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498706817627</v>
+        <v>2.68498730659485</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G291" t="n">
-        <v>2.69393706321716</v>
+        <v>2.69393730163574</v>
       </c>
       <c r="H291" t="n">
         <v>4500</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238677024841</v>
+        <v>2.79238700866699</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G297" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H297" t="n">
         <v>1000</v>
@@ -9011,7 +9011,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G298" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H298" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H300" t="n">
         <v>1000</v>
@@ -9098,7 +9098,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H303" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>2.75658679008484</v>
+        <v>2.75658655166626</v>
       </c>
       <c r="H306" t="n">
         <v>500</v>
@@ -9272,7 +9272,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H307" t="n">
         <v>3000</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H308" t="n">
         <v>3500</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G310" t="n">
-        <v>2.74763655662537</v>
+        <v>2.74763679504395</v>
       </c>
       <c r="H310" t="n">
         <v>1500</v>
@@ -9388,7 +9388,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183729171753</v>
+        <v>2.71183705329895</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233734130859</v>
+        <v>2.62233781814575</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9591,7 +9591,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>2.61338758468628</v>
+        <v>2.61338782310486</v>
       </c>
       <c r="H318" t="n">
         <v>18500</v>
@@ -9620,7 +9620,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G319" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H319" t="n">
         <v>5000</v>
@@ -9707,7 +9707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9765,7 +9765,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.60443758964539</v>
+        <v>2.60443782806396</v>
       </c>
       <c r="H324" t="n">
         <v>3000</v>
@@ -9794,7 +9794,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.5865375995636</v>
+        <v>2.58653783798218</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708707809448</v>
+        <v>2.66708731651306</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9939,7 +9939,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G330" t="n">
-        <v>2.64023756980896</v>
+        <v>2.64023733139038</v>
       </c>
       <c r="H330" t="n">
         <v>6000</v>
@@ -9968,7 +9968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.57758784294128</v>
+        <v>2.57758808135986</v>
       </c>
       <c r="H331" t="n">
         <v>2500</v>
@@ -10055,7 +10055,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>2.51953411102295</v>
+        <v>2.51953387260437</v>
       </c>
       <c r="H334" t="n">
         <v>1500</v>
@@ -10113,7 +10113,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G336" t="n">
-        <v>2.43825888633728</v>
+        <v>2.4382586479187</v>
       </c>
       <c r="H336" t="n">
         <v>29000</v>
@@ -10142,7 +10142,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H337" t="n">
         <v>69000</v>
@@ -10200,7 +10200,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H339" t="n">
         <v>66500</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10345,7 +10345,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H344" t="n">
         <v>11500</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310622215271</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.4201979637146</v>
+        <v>2.42019748687744</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310598373413</v>
+        <v>2.39310622215271</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H358" t="n">
         <v>7000</v>
@@ -10925,7 +10925,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -10954,7 +10954,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H366" t="n">
         <v>2500</v>
@@ -11012,7 +11012,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.42922830581665</v>
+        <v>2.42922806739807</v>
       </c>
       <c r="H376" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.36601400375366</v>
+        <v>2.36601424217224</v>
       </c>
       <c r="H378" t="n">
         <v>1500</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698342323303</v>
+        <v>2.35698318481445</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>2.3479528427124</v>
+        <v>2.34795260429382</v>
       </c>
       <c r="H380" t="n">
         <v>5000</v>
@@ -11505,7 +11505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>2.29376912117004</v>
+        <v>2.29376935958862</v>
       </c>
       <c r="H384" t="n">
         <v>11500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11621,7 +11621,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H388" t="n">
         <v>5000</v>
@@ -11650,7 +11650,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958587646484</v>
+        <v>2.23958563804626</v>
       </c>
       <c r="H389" t="n">
         <v>9000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11882,7 +11882,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G397" t="n">
-        <v>2.11315774917603</v>
+        <v>2.11315751075745</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249413490295</v>
+        <v>2.21249389648438</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12259,7 +12259,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.22152471542358</v>
+        <v>2.221524477005</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99575960636139</v>
+        <v>1.99575972557068</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.95060694217682</v>
+        <v>1.9506071805954</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12491,7 +12491,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>1.85127055644989</v>
+        <v>1.85127067565918</v>
       </c>
       <c r="H418" t="n">
         <v>9000</v>
@@ -12723,7 +12723,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G426" t="n">
-        <v>1.33652698993683</v>
+        <v>1.33652710914612</v>
       </c>
       <c r="H426" t="n">
         <v>7000</v>
@@ -12752,7 +12752,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G428" t="n">
-        <v>1.21912944316864</v>
+        <v>1.21912932395935</v>
       </c>
       <c r="H428" t="n">
         <v>7500</v>
@@ -12810,7 +12810,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G429" t="n">
-        <v>1.18300700187683</v>
+        <v>1.18300712108612</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.2100989818573</v>
+        <v>1.21009874343872</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364485263824</v>
+        <v>1.22364473342896</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12955,7 +12955,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H434" t="n">
         <v>11500</v>
@@ -13013,7 +13013,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>1.31846582889557</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H436" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>1.31846582889557</v>
+        <v>1.31846594810486</v>
       </c>
       <c r="H437" t="n">
         <v>11000</v>
@@ -13100,7 +13100,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458815097809</v>
+        <v>1.35458827018738</v>
       </c>
       <c r="H439" t="n">
         <v>5000</v>
@@ -13129,7 +13129,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G440" t="n">
-        <v>1.36361885070801</v>
+        <v>1.36361873149872</v>
       </c>
       <c r="H440" t="n">
         <v>6000</v>
@@ -13158,7 +13158,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>1.36361885070801</v>
+        <v>1.36361873149872</v>
       </c>
       <c r="H441" t="n">
         <v>5500</v>
@@ -13187,7 +13187,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49004697799683</v>
+        <v>1.49004709720612</v>
       </c>
       <c r="H442" t="n">
         <v>13000</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.60292935371399</v>
+        <v>1.6029292345047</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13274,7 +13274,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099039554596</v>
+        <v>1.62099051475525</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G447" t="n">
-        <v>1.65259766578674</v>
+        <v>1.65259778499603</v>
       </c>
       <c r="H447" t="n">
         <v>17500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162812709808</v>
+        <v>1.66162836551666</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290347099304</v>
+        <v>1.74290359020233</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160224437714</v>
+        <v>1.80160212516785</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13564,7 +13564,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902591228485</v>
+        <v>1.77902579307556</v>
       </c>
       <c r="H455" t="n">
         <v>4500</v>
@@ -13622,7 +13622,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030113697052</v>
+        <v>1.86030125617981</v>
       </c>
       <c r="H457" t="n">
         <v>7500</v>
@@ -13680,7 +13680,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>1.85127055644989</v>
+        <v>1.85127067565918</v>
       </c>
       <c r="H459" t="n">
         <v>6500</v>
@@ -13738,7 +13738,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67757093906403</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H461" t="n">
         <v>31000</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13883,7 +13883,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H466" t="n">
         <v>7500</v>
@@ -13912,7 +13912,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G467" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H467" t="n">
         <v>5000</v>
@@ -13941,7 +13941,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G468" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H468" t="n">
         <v>1000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -13999,7 +13999,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G470" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H470" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G471" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H471" t="n">
         <v>3500</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H473" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G474" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.67757093906403</v>
+        <v>1.67757105827332</v>
       </c>
       <c r="H475" t="n">
         <v>12000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14347,7 +14347,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G482" t="n">
-        <v>1.72785234451294</v>
+        <v>1.72785246372223</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412571907043</v>
+        <v>1.87412583827972</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326776027679</v>
+        <v>1.88326787948608</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G505" t="n">
-        <v>1.72785234451294</v>
+        <v>1.72785246372223</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15130,7 +15130,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G509" t="n">
-        <v>1.76442074775696</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H509" t="n">
         <v>3500</v>
@@ -15159,7 +15159,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G510" t="n">
-        <v>1.76442074775696</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G511" t="n">
-        <v>1.76442074775696</v>
+        <v>1.76442086696625</v>
       </c>
       <c r="H511" t="n">
         <v>500</v>
@@ -15449,7 +15449,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H520" t="n">
         <v>10500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814761161804</v>
+        <v>1.61814749240875</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15710,7 +15710,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G537" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -16087,7 +16087,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.6410026550293</v>
+        <v>1.64100277423859</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16406,7 +16406,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G553" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G556" t="n">
-        <v>1.65014469623566</v>
+        <v>1.65014481544495</v>
       </c>
       <c r="H556" t="n">
         <v>1000</v>
@@ -16522,7 +16522,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G557" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643169403076</v>
+        <v>1.63643181324005</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16870,7 +16870,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>1.6272896528244</v>
+        <v>1.62728953361511</v>
       </c>
       <c r="H569" t="n">
         <v>2500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -17015,7 +17015,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H574" t="n">
         <v>500</v>
@@ -17044,7 +17044,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.64557373523712</v>
+        <v>1.64557385444641</v>
       </c>
       <c r="H575" t="n">
         <v>16500</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214201927185</v>
+        <v>1.68214213848114</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17247,7 +17247,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357653141022</v>
+        <v>1.61357641220093</v>
       </c>
       <c r="H582" t="n">
         <v>5500</v>
@@ -17856,7 +17856,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>1.66998875141144</v>
+        <v>1.66998887062073</v>
       </c>
       <c r="H603" t="n">
         <v>14500</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120958328247</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18088,7 +18088,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G611" t="n">
-        <v>1.79059910774231</v>
+        <v>1.7905992269516</v>
       </c>
       <c r="H611" t="n">
         <v>12000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120958328247</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120958328247</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120958328247</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820820808411</v>
+        <v>2.07820844650269</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.91120946407318</v>
+        <v>1.91120958328247</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>2.08748602867126</v>
+        <v>2.08748626708984</v>
       </c>
       <c r="H629" t="n">
         <v>42500</v>
@@ -18639,7 +18639,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.00398659706116</v>
+        <v>2.00398683547974</v>
       </c>
       <c r="H630" t="n">
         <v>13000</v>
@@ -18726,7 +18726,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H633" t="n">
         <v>86500</v>
@@ -18900,7 +18900,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H639" t="n">
         <v>1000</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H644" t="n">
         <v>12000</v>
@@ -19132,7 +19132,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H647" t="n">
         <v>12000</v>
@@ -19161,7 +19161,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G648" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G656" t="n">
-        <v>2.32870650291443</v>
+        <v>2.32870626449585</v>
       </c>
       <c r="H656" t="n">
         <v>47500</v>
@@ -19596,7 +19596,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220569610596</v>
       </c>
       <c r="H663" t="n">
         <v>11500</v>
@@ -19683,7 +19683,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>2.32870650291443</v>
+        <v>2.32870626449585</v>
       </c>
       <c r="H666" t="n">
         <v>5000</v>
@@ -19741,7 +19741,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220593452454</v>
+        <v>2.41220569610596</v>
       </c>
       <c r="H668" t="n">
         <v>14000</v>
@@ -19886,7 +19886,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.60703802108765</v>
+        <v>2.60703825950623</v>
       </c>
       <c r="H673" t="n">
         <v>48500</v>
@@ -19973,7 +19973,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>2.60703802108765</v>
+        <v>2.60703825950623</v>
       </c>
       <c r="H676" t="n">
         <v>27000</v>
@@ -20031,7 +20031,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>2.61631560325623</v>
+        <v>2.6163158416748</v>
       </c>
       <c r="H678" t="n">
         <v>18000</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.78331470489502</v>
+        <v>2.7833149433136</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20524,7 +20524,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>2.87609171867371</v>
+        <v>2.87609195709229</v>
       </c>
       <c r="H695" t="n">
         <v>42500</v>
@@ -20640,7 +20640,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G699" t="n">
-        <v>2.87609171867371</v>
+        <v>2.87609195709229</v>
       </c>
       <c r="H699" t="n">
         <v>9500</v>
@@ -20669,7 +20669,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>2.87609171867371</v>
+        <v>2.87609195709229</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>2.87609171867371</v>
+        <v>2.87609195709229</v>
       </c>
       <c r="H701" t="n">
         <v>6500</v>
@@ -20727,7 +20727,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.87609171867371</v>
+        <v>2.87609195709229</v>
       </c>
       <c r="H702" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H730" t="n">
         <v>6000</v>
@@ -21771,7 +21771,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21887,7 +21887,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H742" t="n">
         <v>2500</v>
@@ -21916,7 +21916,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089056968689</v>
+        <v>2.92089080810547</v>
       </c>
       <c r="H743" t="n">
         <v>10000</v>
@@ -22090,7 +22090,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G749" t="n">
-        <v>3.18471336364746</v>
+        <v>3.18471312522888</v>
       </c>
       <c r="H749" t="n">
         <v>6500</v>
@@ -22119,7 +22119,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.18471336364746</v>
+        <v>3.18471312522888</v>
       </c>
       <c r="H750" t="n">
         <v>69500</v>
@@ -22264,7 +22264,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H755" t="n">
         <v>1000</v>
@@ -22293,7 +22293,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>3.18471336364746</v>
+        <v>3.18471312522888</v>
       </c>
       <c r="H756" t="n">
         <v>17000</v>
@@ -22351,7 +22351,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H758" t="n">
         <v>11500</v>
@@ -22409,7 +22409,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>3.3731575012207</v>
+        <v>3.37315773963928</v>
       </c>
       <c r="H760" t="n">
         <v>17000</v>
@@ -22438,7 +22438,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H761" t="n">
         <v>24000</v>
@@ -22496,7 +22496,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>3.33546900749207</v>
+        <v>3.33546876907349</v>
       </c>
       <c r="H763" t="n">
         <v>3500</v>
@@ -22525,7 +22525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>3.3731575012207</v>
+        <v>3.37315773963928</v>
       </c>
       <c r="H764" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H768" t="n">
         <v>7000</v>
@@ -23047,7 +23047,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H782" t="n">
         <v>1500</v>
@@ -23076,7 +23076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H788" t="n">
         <v>5000</v>
@@ -23279,7 +23279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586875915527</v>
+        <v>3.16586852073669</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23395,7 +23395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H794" t="n">
         <v>9000</v>
@@ -23511,7 +23511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H798" t="n">
         <v>7000</v>
@@ -23656,7 +23656,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.18471336364746</v>
+        <v>3.18471312522888</v>
       </c>
       <c r="H803" t="n">
         <v>42500</v>
@@ -23772,7 +23772,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>3.26009106636047</v>
+        <v>3.26009082794189</v>
       </c>
       <c r="H807" t="n">
         <v>8500</v>
@@ -23946,7 +23946,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H813" t="n">
         <v>7000</v>
@@ -24004,7 +24004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.09049081802368</v>
+        <v>3.0904905796051</v>
       </c>
       <c r="H815" t="n">
         <v>15000</v>
@@ -24816,7 +24816,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H843" t="n">
         <v>32000</v>
@@ -24961,7 +24961,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H848" t="n">
         <v>22000</v>
@@ -25106,7 +25106,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H856" t="n">
         <v>4500</v>
@@ -25280,7 +25280,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H859" t="n">
         <v>13000</v>
@@ -25338,7 +25338,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G861" t="n">
-        <v>4.0704026222229</v>
+        <v>4.07040309906006</v>
       </c>
       <c r="H861" t="n">
         <v>24000</v>
@@ -25483,7 +25483,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H866" t="n">
         <v>18000</v>
@@ -25512,7 +25512,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05155801773071</v>
+        <v>4.05155849456787</v>
       </c>
       <c r="H867" t="n">
         <v>13500</v>
@@ -25570,7 +25570,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>4.0704026222229</v>
+        <v>4.07040309906006</v>
       </c>
       <c r="H869" t="n">
         <v>5000</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H875" t="n">
         <v>6500</v>
@@ -26527,7 +26527,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089260101318</v>
       </c>
       <c r="H902" t="n">
         <v>88500</v>
@@ -26556,7 +26556,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H903" t="n">
         <v>32500</v>
@@ -26701,7 +26701,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089260101318</v>
       </c>
       <c r="H908" t="n">
         <v>23500</v>
@@ -26730,7 +26730,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089260101318</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -26759,7 +26759,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089260101318</v>
       </c>
       <c r="H910" t="n">
         <v>22500</v>
@@ -26817,7 +26817,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H912" t="n">
         <v>14000</v>
@@ -26875,7 +26875,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089212417603</v>
+        <v>5.04089260101318</v>
       </c>
       <c r="H914" t="n">
         <v>37000</v>
@@ -26962,7 +26962,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H917" t="n">
         <v>61000</v>
@@ -26991,7 +26991,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H918" t="n">
         <v>13000</v>
@@ -27020,7 +27020,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08800363540649</v>
+        <v>5.08800315856934</v>
       </c>
       <c r="H919" t="n">
         <v>26500</v>
@@ -27049,7 +27049,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G920" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H920" t="n">
         <v>12500</v>
@@ -27107,7 +27107,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G922" t="n">
-        <v>4.85244750976562</v>
+        <v>4.85244798660278</v>
       </c>
       <c r="H922" t="n">
         <v>5000</v>
@@ -27368,7 +27368,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.5616021156311</v>
+        <v>3.56160235404968</v>
       </c>
       <c r="H931" t="n">
         <v>72500</v>
@@ -27397,7 +27397,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>3.6369800567627</v>
+        <v>3.63698029518127</v>
       </c>
       <c r="H932" t="n">
         <v>50500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.8819580078125</v>
+        <v>3.88195824623108</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27571,7 +27571,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G938" t="n">
-        <v>4.0704026222229</v>
+        <v>4.07040309906006</v>
       </c>
       <c r="H938" t="n">
         <v>8500</v>
@@ -27600,7 +27600,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H939" t="n">
         <v>8000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000263214111</v>
+        <v>4.24000310897827</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27658,7 +27658,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H941" t="n">
         <v>3500</v>
@@ -27745,7 +27745,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115802764893</v>
+        <v>4.22115850448608</v>
       </c>
       <c r="H944" t="n">
         <v>3500</v>
@@ -27890,7 +27890,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G949" t="n">
-        <v>4.89955854415894</v>
+        <v>4.89955806732178</v>
       </c>
       <c r="H949" t="n">
         <v>30500</v>
@@ -27977,7 +27977,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>4.74880313873291</v>
+        <v>4.74880266189575</v>
       </c>
       <c r="H952" t="n">
         <v>8000</v>
@@ -28151,7 +28151,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G958" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H958" t="n">
         <v>36500</v>
@@ -28412,7 +28412,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G967" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H967" t="n">
         <v>4000</v>
@@ -28441,7 +28441,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>4.43787002563477</v>
+        <v>4.43786954879761</v>
       </c>
       <c r="H968" t="n">
         <v>7500</v>
@@ -28499,7 +28499,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>4.43787002563477</v>
+        <v>4.43786954879761</v>
       </c>
       <c r="H970" t="n">
         <v>14000</v>
@@ -28528,7 +28528,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>4.55093622207642</v>
+        <v>4.55093669891357</v>
       </c>
       <c r="H971" t="n">
         <v>9000</v>
@@ -28615,7 +28615,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G974" t="n">
-        <v>4.24942541122437</v>
+        <v>4.24942493438721</v>
       </c>
       <c r="H974" t="n">
         <v>4500</v>

--- a/data/ESAU.MI.xlsx
+++ b/data/ESAU.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59614706039429</v>
+        <v>3.59614682197571</v>
       </c>
       <c r="H2" t="n">
         <v>638000</v>
@@ -485,7 +485,7 @@
         <v>4.08349990844727</v>
       </c>
       <c r="G4" t="n">
-        <v>3.62589263916016</v>
+        <v>3.62589240074158</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -514,7 +514,7 @@
         <v>3.96700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.52244806289673</v>
+        <v>3.52244782447815</v>
       </c>
       <c r="H5" t="n">
         <v>82000</v>
@@ -572,7 +572,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>3.34752440452576</v>
+        <v>3.3475239276886</v>
       </c>
       <c r="H7" t="n">
         <v>94000</v>
@@ -601,7 +601,7 @@
         <v>3.88849997520447</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45274496078491</v>
+        <v>3.45274472236633</v>
       </c>
       <c r="H8" t="n">
         <v>39000</v>
@@ -630,7 +630,7 @@
         <v>3.83100008964539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40168881416321</v>
+        <v>3.40168857574463</v>
       </c>
       <c r="H9" t="n">
         <v>35000</v>
@@ -659,7 +659,7 @@
         <v>3.71050000190735</v>
       </c>
       <c r="G10" t="n">
-        <v>3.29469180107117</v>
+        <v>3.29469203948975</v>
       </c>
       <c r="H10" t="n">
         <v>88500</v>
@@ -688,7 +688,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H11" t="n">
         <v>156500</v>
@@ -746,7 +746,7 @@
         <v>3.57049989700317</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17038059234619</v>
+        <v>3.17038035392761</v>
       </c>
       <c r="H13" t="n">
         <v>78500</v>
@@ -775,7 +775,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2232129573822</v>
+        <v>3.22321271896362</v>
       </c>
       <c r="H14" t="n">
         <v>55000</v>
@@ -833,7 +833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G16" t="n">
-        <v>3.17881608009338</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H16" t="n">
         <v>26500</v>
@@ -891,7 +891,7 @@
         <v>3.56349992752075</v>
       </c>
       <c r="G18" t="n">
-        <v>3.16416501998901</v>
+        <v>3.16416525840759</v>
       </c>
       <c r="H18" t="n">
         <v>39500</v>
@@ -1007,7 +1007,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G22" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H22" t="n">
         <v>26500</v>
@@ -1036,7 +1036,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96571111679077</v>
+        <v>2.96571087837219</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H26" t="n">
         <v>15500</v>
@@ -1152,7 +1152,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H27" t="n">
         <v>57500</v>
@@ -1181,7 +1181,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G28" t="n">
-        <v>2.89467573165894</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H28" t="n">
         <v>21500</v>
@@ -1210,7 +1210,7 @@
         <v>3.17449998855591</v>
       </c>
       <c r="G29" t="n">
-        <v>2.81875777244568</v>
+        <v>2.81875729560852</v>
       </c>
       <c r="H29" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H31" t="n">
         <v>33000</v>
@@ -1355,7 +1355,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G34" t="n">
-        <v>3.09890151023865</v>
+        <v>3.09890174865723</v>
       </c>
       <c r="H34" t="n">
         <v>49500</v>
@@ -1413,7 +1413,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93907284736633</v>
+        <v>2.93907308578491</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.34850001335144</v>
       </c>
       <c r="G37" t="n">
-        <v>2.97325825691223</v>
+        <v>2.97325849533081</v>
       </c>
       <c r="H37" t="n">
         <v>16500</v>
@@ -1471,7 +1471,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H38" t="n">
         <v>9000</v>
@@ -1529,7 +1529,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G40" t="n">
-        <v>2.91243433952332</v>
+        <v>2.91243505477905</v>
       </c>
       <c r="H40" t="n">
         <v>9500</v>
@@ -1558,7 +1558,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G41" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H41" t="n">
         <v>11000</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H42" t="n">
         <v>3000</v>
@@ -1616,7 +1616,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G43" t="n">
-        <v>2.91687488555908</v>
+        <v>2.91687440872192</v>
       </c>
       <c r="H43" t="n">
         <v>3000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H44" t="n">
         <v>7000</v>
@@ -1790,7 +1790,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.93907284736633</v>
+        <v>2.93907308578491</v>
       </c>
       <c r="H49" t="n">
         <v>4000</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.91687488555908</v>
+        <v>2.91687440872192</v>
       </c>
       <c r="H50" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>3.09446215629578</v>
+        <v>3.09446167945862</v>
       </c>
       <c r="H52" t="n">
         <v>63500</v>
@@ -1906,7 +1906,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>3.0855827331543</v>
+        <v>3.08558249473572</v>
       </c>
       <c r="H53" t="n">
         <v>38000</v>
@@ -1964,7 +1964,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G55" t="n">
-        <v>3.13441944122314</v>
+        <v>3.13441920280457</v>
       </c>
       <c r="H55" t="n">
         <v>45500</v>
@@ -1993,7 +1993,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18769574165344</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H56" t="n">
         <v>38500</v>
@@ -2022,7 +2022,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G57" t="n">
-        <v>3.18769574165344</v>
+        <v>3.18769550323486</v>
       </c>
       <c r="H57" t="n">
         <v>113500</v>
@@ -2051,7 +2051,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G58" t="n">
-        <v>3.26760959625244</v>
+        <v>3.26760983467102</v>
       </c>
       <c r="H58" t="n">
         <v>79500</v>
@@ -2080,7 +2080,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>3.29868793487549</v>
+        <v>3.29868769645691</v>
       </c>
       <c r="H59" t="n">
         <v>241500</v>
@@ -2109,7 +2109,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25873064994812</v>
+        <v>3.25873017311096</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17881608009338</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H61" t="n">
         <v>37000</v>
@@ -2167,7 +2167,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H62" t="n">
         <v>25500</v>
@@ -2196,7 +2196,7 @@
         <v>3.375</v>
       </c>
       <c r="G63" t="n">
-        <v>2.99678897857666</v>
+        <v>2.99678874015808</v>
       </c>
       <c r="H63" t="n">
         <v>18000</v>
@@ -2225,7 +2225,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G64" t="n">
-        <v>3.09890151023865</v>
+        <v>3.09890174865723</v>
       </c>
       <c r="H64" t="n">
         <v>18500</v>
@@ -2254,7 +2254,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.06338405609131</v>
+        <v>3.06338429450989</v>
       </c>
       <c r="H65" t="n">
         <v>5500</v>
@@ -2283,7 +2283,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G66" t="n">
-        <v>3.02786707878113</v>
+        <v>3.02786684036255</v>
       </c>
       <c r="H66" t="n">
         <v>20500</v>
@@ -2312,7 +2312,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351315498352</v>
       </c>
       <c r="H67" t="n">
         <v>40000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H68" t="n">
         <v>23500</v>
@@ -2399,7 +2399,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H70" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>2.73484706878662</v>
+        <v>2.7348473072052</v>
       </c>
       <c r="H71" t="n">
         <v>17500</v>
@@ -2457,7 +2457,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.70820903778076</v>
+        <v>2.70820927619934</v>
       </c>
       <c r="H72" t="n">
         <v>15500</v>
@@ -2486,7 +2486,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>2.73484706878662</v>
+        <v>2.7348473072052</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G74" t="n">
-        <v>2.74816608428955</v>
+        <v>2.74816632270813</v>
       </c>
       <c r="H74" t="n">
         <v>8500</v>
@@ -2544,7 +2544,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G75" t="n">
-        <v>2.88135695457458</v>
+        <v>2.88135671615601</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2660,7 +2660,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.97459053993225</v>
+        <v>2.97459030151367</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H80" t="n">
         <v>14500</v>
@@ -2718,7 +2718,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G81" t="n">
-        <v>2.91243433952332</v>
+        <v>2.91243505477905</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00122833251953</v>
+        <v>3.00122857093811</v>
       </c>
       <c r="H83" t="n">
         <v>15000</v>
@@ -2805,7 +2805,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.04118609428406</v>
+        <v>3.0411856174469</v>
       </c>
       <c r="H84" t="n">
         <v>31500</v>
@@ -2834,7 +2834,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H85" t="n">
         <v>19000</v>
@@ -2863,7 +2863,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H86" t="n">
         <v>7000</v>
@@ -2921,7 +2921,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G88" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H88" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>3.04118609428406</v>
+        <v>3.0411856174469</v>
       </c>
       <c r="H90" t="n">
         <v>5500</v>
@@ -3066,7 +3066,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G93" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H93" t="n">
         <v>6500</v>
@@ -3095,7 +3095,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>3.19213509559631</v>
+        <v>3.19213533401489</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06338405609131</v>
+        <v>3.06338429450989</v>
       </c>
       <c r="H96" t="n">
         <v>4500</v>
@@ -3182,7 +3182,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11666035652161</v>
+        <v>3.11666059494019</v>
       </c>
       <c r="H97" t="n">
         <v>9500</v>
@@ -3240,7 +3240,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>2.94795227050781</v>
+        <v>2.94795250892639</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>3.1033411026001</v>
+        <v>3.10334134101868</v>
       </c>
       <c r="H100" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G101" t="n">
-        <v>3.15217804908752</v>
+        <v>3.15217781066895</v>
       </c>
       <c r="H101" t="n">
         <v>14500</v>
@@ -3356,7 +3356,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.17881608009338</v>
+        <v>3.1788158416748</v>
       </c>
       <c r="H103" t="n">
         <v>11000</v>
@@ -3385,7 +3385,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G104" t="n">
-        <v>3.20545411109924</v>
+        <v>3.2054545879364</v>
       </c>
       <c r="H104" t="n">
         <v>6500</v>
@@ -3472,7 +3472,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>3.10778117179871</v>
+        <v>3.10778141021729</v>
       </c>
       <c r="H107" t="n">
         <v>6000</v>
@@ -3530,7 +3530,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>2.94351267814636</v>
+        <v>2.94351315498352</v>
       </c>
       <c r="H109" t="n">
         <v>24500</v>
@@ -3559,7 +3559,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G110" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H110" t="n">
         <v>14000</v>
@@ -3588,7 +3588,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9701509475708</v>
+        <v>2.97015070915222</v>
       </c>
       <c r="H111" t="n">
         <v>2000</v>
@@ -3646,7 +3646,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.89023613929749</v>
+        <v>2.89023661613464</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H114" t="n">
         <v>4000</v>
@@ -3704,7 +3704,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93019390106201</v>
+        <v>2.93019366264343</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3791,7 +3791,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H118" t="n">
         <v>4500</v>
@@ -3820,7 +3820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H119" t="n">
         <v>7500</v>
@@ -3849,7 +3849,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G120" t="n">
-        <v>2.77924466133118</v>
+        <v>2.77924394607544</v>
       </c>
       <c r="H120" t="n">
         <v>30500</v>
@@ -3878,7 +3878,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8591582775116</v>
+        <v>2.85915851593018</v>
       </c>
       <c r="H121" t="n">
         <v>10500</v>
@@ -4023,7 +4023,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H126" t="n">
         <v>15000</v>
@@ -4110,7 +4110,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G129" t="n">
-        <v>2.82808065414429</v>
+        <v>2.82808041572571</v>
       </c>
       <c r="H129" t="n">
         <v>39500</v>
@@ -4139,7 +4139,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H130" t="n">
         <v>19000</v>
@@ -4197,7 +4197,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256296157837</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77924466133118</v>
+        <v>2.77924394607544</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.79256319999695</v>
+        <v>2.79256296157837</v>
       </c>
       <c r="H134" t="n">
         <v>3000</v>
@@ -4284,7 +4284,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H135" t="n">
         <v>2500</v>
@@ -4371,7 +4371,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>2.69932985305786</v>
+        <v>2.69932961463928</v>
       </c>
       <c r="H138" t="n">
         <v>5000</v>
@@ -4400,7 +4400,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>2.67713141441345</v>
+        <v>2.67713165283203</v>
       </c>
       <c r="H139" t="n">
         <v>2500</v>
@@ -4429,7 +4429,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H140" t="n">
         <v>5500</v>
@@ -4516,7 +4516,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H143" t="n">
         <v>2000</v>
@@ -4545,7 +4545,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H144" t="n">
         <v>72000</v>
@@ -4574,7 +4574,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>2.71708846092224</v>
+        <v>2.71708869934082</v>
       </c>
       <c r="H145" t="n">
         <v>21000</v>
@@ -4603,7 +4603,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G146" t="n">
-        <v>2.74816608428955</v>
+        <v>2.74816632270813</v>
       </c>
       <c r="H146" t="n">
         <v>11500</v>
@@ -4632,7 +4632,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G147" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H147" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H148" t="n">
         <v>19500</v>
@@ -4690,7 +4690,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.85471868515015</v>
+        <v>2.85471892356873</v>
       </c>
       <c r="H149" t="n">
         <v>8000</v>
@@ -4719,7 +4719,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H150" t="n">
         <v>44000</v>
@@ -4748,7 +4748,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H151" t="n">
         <v>7000</v>
@@ -4777,7 +4777,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H153" t="n">
         <v>17000</v>
@@ -4835,7 +4835,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H154" t="n">
         <v>2000</v>
@@ -4864,7 +4864,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>2.81032204627991</v>
+        <v>2.81032180786133</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H158" t="n">
         <v>11000</v>
@@ -4980,7 +4980,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73928689956665</v>
+        <v>2.73928713798523</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5009,7 +5009,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H160" t="n">
         <v>1500</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.76148557662964</v>
+        <v>2.76148533821106</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5067,7 +5067,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G162" t="n">
-        <v>2.76592493057251</v>
+        <v>2.76592516899109</v>
       </c>
       <c r="H162" t="n">
         <v>17500</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H163" t="n">
         <v>7500</v>
@@ -5125,7 +5125,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G164" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H164" t="n">
         <v>111500</v>
@@ -5154,7 +5154,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>2.78368353843689</v>
+        <v>2.78368377685547</v>
       </c>
       <c r="H165" t="n">
         <v>33000</v>
@@ -5183,7 +5183,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G166" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H166" t="n">
         <v>6000</v>
@@ -5212,7 +5212,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>2.77924466133118</v>
+        <v>2.77924394607544</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>2.80144238471985</v>
+        <v>2.80144262313843</v>
       </c>
       <c r="H169" t="n">
         <v>18000</v>
@@ -5299,7 +5299,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H170" t="n">
         <v>4500</v>
@@ -5328,7 +5328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G171" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H171" t="n">
         <v>7500</v>
@@ -5357,7 +5357,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G172" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>2.72596836090088</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H173" t="n">
         <v>4000</v>
@@ -5415,7 +5415,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5444,7 +5444,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H175" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G177" t="n">
-        <v>2.77924466133118</v>
+        <v>2.77924394607544</v>
       </c>
       <c r="H177" t="n">
         <v>31500</v>
@@ -5531,7 +5531,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.82808065414429</v>
+        <v>2.82808041572571</v>
       </c>
       <c r="H178" t="n">
         <v>9500</v>
@@ -5589,7 +5589,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H180" t="n">
         <v>5000</v>
@@ -5676,7 +5676,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H183" t="n">
         <v>15000</v>
@@ -5705,7 +5705,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G184" t="n">
-        <v>2.87247729301453</v>
+        <v>2.87247753143311</v>
       </c>
       <c r="H184" t="n">
         <v>28000</v>
@@ -5734,7 +5734,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G185" t="n">
-        <v>2.89467573165894</v>
+        <v>2.89467620849609</v>
       </c>
       <c r="H185" t="n">
         <v>35500</v>
@@ -5792,7 +5792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G187" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>2.72596836090088</v>
+        <v>2.72596788406372</v>
       </c>
       <c r="H188" t="n">
         <v>12000</v>
@@ -5850,7 +5850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.75260615348816</v>
+        <v>2.75260591506958</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5908,7 +5908,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H191" t="n">
         <v>9500</v>
@@ -5937,7 +5937,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.77036476135254</v>
+        <v>2.77036452293396</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H193" t="n">
         <v>21000</v>
@@ -5995,7 +5995,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H194" t="n">
         <v>500</v>
@@ -6111,7 +6111,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H198" t="n">
         <v>5500</v>
@@ -6140,7 +6140,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>2.8325207233429</v>
+        <v>2.83252048492432</v>
       </c>
       <c r="H199" t="n">
         <v>2500</v>
@@ -6169,7 +6169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G200" t="n">
-        <v>2.8413999080658</v>
+        <v>2.84140014648438</v>
       </c>
       <c r="H200" t="n">
         <v>76500</v>
@@ -6227,7 +6227,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G202" t="n">
-        <v>2.82364130020142</v>
+        <v>2.82364106178284</v>
       </c>
       <c r="H202" t="n">
         <v>2000</v>
@@ -6285,7 +6285,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>2.81476163864136</v>
+        <v>2.81476187705994</v>
       </c>
       <c r="H204" t="n">
         <v>3500</v>
@@ -6343,7 +6343,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G207" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H207" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H215" t="n">
         <v>4000</v>
@@ -6633,7 +6633,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6662,7 +6662,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.73868680000305</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H217" t="n">
         <v>14000</v>
@@ -6807,7 +6807,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H222" t="n">
         <v>11500</v>
@@ -6836,7 +6836,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G223" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H223" t="n">
         <v>2500</v>
@@ -6923,7 +6923,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H226" t="n">
         <v>3500</v>
@@ -7068,7 +7068,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H231" t="n">
         <v>34000</v>
@@ -7271,7 +7271,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813732147217</v>
       </c>
       <c r="H238" t="n">
         <v>51500</v>
@@ -7300,7 +7300,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G239" t="n">
-        <v>2.65813755989075</v>
+        <v>2.65813732147217</v>
       </c>
       <c r="H239" t="n">
         <v>12500</v>
@@ -7329,7 +7329,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.66708731651306</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H240" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G241" t="n">
-        <v>2.66708731651306</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H241" t="n">
         <v>21500</v>
@@ -7387,7 +7387,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H242" t="n">
         <v>10500</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H245" t="n">
         <v>5500</v>
@@ -7532,7 +7532,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>2.66708731651306</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G248" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7590,7 +7590,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H249" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G254" t="n">
-        <v>2.85503625869751</v>
+        <v>2.85503649711609</v>
       </c>
       <c r="H254" t="n">
         <v>5000</v>
@@ -7880,7 +7880,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H259" t="n">
         <v>10000</v>
@@ -7909,7 +7909,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H260" t="n">
         <v>9500</v>
@@ -7938,7 +7938,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H261" t="n">
         <v>7000</v>
@@ -7967,7 +7967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G262" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H262" t="n">
         <v>3500</v>
@@ -7996,7 +7996,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H263" t="n">
         <v>6500</v>
@@ -8054,7 +8054,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G265" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H265" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H269" t="n">
         <v>3000</v>
@@ -8286,7 +8286,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H273" t="n">
         <v>7500</v>
@@ -8315,7 +8315,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G274" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8373,7 +8373,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.77448701858521</v>
+        <v>2.77448654174805</v>
       </c>
       <c r="H276" t="n">
         <v>5000</v>
@@ -8402,7 +8402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G277" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H277" t="n">
         <v>6500</v>
@@ -8431,7 +8431,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>2.73868680000305</v>
+        <v>2.73868703842163</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8547,7 +8547,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H282" t="n">
         <v>1500</v>
@@ -8663,7 +8663,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H286" t="n">
         <v>2500</v>
@@ -8692,7 +8692,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H287" t="n">
         <v>4000</v>
@@ -8721,7 +8721,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>3</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68498730659485</v>
+        <v>2.68498706817627</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8866,7 +8866,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G293" t="n">
-        <v>2.72973680496216</v>
+        <v>2.72973704338074</v>
       </c>
       <c r="H293" t="n">
         <v>5000</v>
@@ -8924,7 +8924,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G295" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H295" t="n">
         <v>64500</v>
@@ -8953,7 +8953,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G296" t="n">
-        <v>2.79238700866699</v>
+        <v>2.79238653182983</v>
       </c>
       <c r="H296" t="n">
         <v>500</v>
@@ -9156,7 +9156,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H303" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>2.75658655166626</v>
+        <v>2.75658679008484</v>
       </c>
       <c r="H306" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H308" t="n">
         <v>3500</v>
@@ -9330,7 +9330,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9388,7 +9388,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G311" t="n">
-        <v>2.71183705329895</v>
+        <v>2.71183729171753</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9417,7 +9417,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H312" t="n">
         <v>22000</v>
@@ -9446,7 +9446,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G313" t="n">
-        <v>2.58653783798218</v>
+        <v>2.58653736114502</v>
       </c>
       <c r="H313" t="n">
         <v>3500</v>
@@ -9475,7 +9475,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>2.63128757476807</v>
+        <v>2.63128733634949</v>
       </c>
       <c r="H314" t="n">
         <v>3500</v>
@@ -9504,7 +9504,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>2.62233781814575</v>
+        <v>2.62233734130859</v>
       </c>
       <c r="H315" t="n">
         <v>5500</v>
@@ -9678,7 +9678,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>2.54178762435913</v>
+        <v>2.54178786277771</v>
       </c>
       <c r="H321" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.60443782806396</v>
+        <v>2.60443758964539</v>
       </c>
       <c r="H324" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.58653783798218</v>
+        <v>2.58653736114502</v>
       </c>
       <c r="H326" t="n">
         <v>9500</v>
@@ -9910,7 +9910,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>2.66708731651306</v>
+        <v>2.66708707809448</v>
       </c>
       <c r="H329" t="n">
         <v>6500</v>
@@ -9997,7 +9997,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.50598812103271</v>
+        <v>2.50598788261414</v>
       </c>
       <c r="H332" t="n">
         <v>30000</v>
@@ -10026,7 +10026,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56468677520752</v>
+        <v>2.5646870136261</v>
       </c>
       <c r="H333" t="n">
         <v>8500</v>
@@ -10055,7 +10055,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>2.51953387260437</v>
+        <v>2.51953411102295</v>
       </c>
       <c r="H334" t="n">
         <v>1500</v>
@@ -10084,7 +10084,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.51050329208374</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H335" t="n">
         <v>37500</v>
@@ -10142,7 +10142,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601376533508</v>
       </c>
       <c r="H337" t="n">
         <v>69000</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31183075904846</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H338" t="n">
         <v>33500</v>
@@ -10200,7 +10200,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H339" t="n">
         <v>66500</v>
@@ -10258,7 +10258,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42019748687744</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H341" t="n">
         <v>5000</v>
@@ -10345,7 +10345,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601376533508</v>
       </c>
       <c r="H344" t="n">
         <v>11500</v>
@@ -10403,7 +10403,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H346" t="n">
         <v>18500</v>
@@ -10490,7 +10490,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G349" t="n">
-        <v>2.51050329208374</v>
+        <v>2.51050353050232</v>
       </c>
       <c r="H349" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>2.50147271156311</v>
+        <v>2.50147294998169</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.4743812084198</v>
+        <v>2.47438097000122</v>
       </c>
       <c r="H352" t="n">
         <v>12500</v>
@@ -10606,7 +10606,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G353" t="n">
-        <v>2.42019748687744</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H353" t="n">
         <v>5500</v>
@@ -10635,7 +10635,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>2.39310622215271</v>
+        <v>2.39310550689697</v>
       </c>
       <c r="H354" t="n">
         <v>2500</v>
@@ -10664,7 +10664,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>2.42019748687744</v>
+        <v>2.4201979637146</v>
       </c>
       <c r="H355" t="n">
         <v>1000</v>
@@ -10693,7 +10693,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.39310622215271</v>
+        <v>2.39310550689697</v>
       </c>
       <c r="H356" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G358" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H358" t="n">
         <v>7000</v>
@@ -10780,7 +10780,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G359" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10809,7 +10809,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G360" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H361" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H362" t="n">
         <v>500</v>
@@ -10896,7 +10896,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G363" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601376533508</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -10954,7 +10954,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601376533508</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H366" t="n">
         <v>2500</v>
@@ -11012,7 +11012,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>2.32989192008972</v>
+        <v>2.32989168167114</v>
       </c>
       <c r="H368" t="n">
         <v>1000</v>
@@ -11099,7 +11099,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>2.37504482269287</v>
+        <v>2.37504458427429</v>
       </c>
       <c r="H370" t="n">
         <v>500</v>
@@ -11186,7 +11186,7 @@
         <v>2.75</v>
       </c>
       <c r="G373" t="n">
-        <v>2.48341155052185</v>
+        <v>2.48341202735901</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11302,7 +11302,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>2.37504482269287</v>
+        <v>2.37504458427429</v>
       </c>
       <c r="H377" t="n">
         <v>1000</v>
@@ -11331,7 +11331,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.36601424217224</v>
+        <v>2.36601376533508</v>
       </c>
       <c r="H378" t="n">
         <v>1500</v>
@@ -11360,7 +11360,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G379" t="n">
-        <v>2.35698318481445</v>
+        <v>2.35698342323303</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>2.34795260429382</v>
+        <v>2.3479528427124</v>
       </c>
       <c r="H380" t="n">
         <v>5000</v>
@@ -11418,7 +11418,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H381" t="n">
         <v>6000</v>
@@ -11447,7 +11447,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.33892226219177</v>
+        <v>2.33892250061035</v>
       </c>
       <c r="H382" t="n">
         <v>2500</v>
@@ -11534,7 +11534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H385" t="n">
         <v>15500</v>
@@ -11563,7 +11563,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H386" t="n">
         <v>30500</v>
@@ -11592,7 +11592,7 @@
         <v>2.5</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H387" t="n">
         <v>54000</v>
@@ -11621,7 +11621,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>2.221524477005</v>
+        <v>2.22152471542358</v>
       </c>
       <c r="H388" t="n">
         <v>5000</v>
@@ -11650,7 +11650,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>2.23958563804626</v>
+        <v>2.23958587646484</v>
       </c>
       <c r="H389" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G390" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11708,7 +11708,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G391" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H391" t="n">
         <v>1000</v>
@@ -11737,7 +11737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H392" t="n">
         <v>5000</v>
@@ -11911,7 +11911,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G398" t="n">
-        <v>2.1583104133606</v>
+        <v>2.15831089019775</v>
       </c>
       <c r="H398" t="n">
         <v>11500</v>
@@ -11969,7 +11969,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>2.17637181282043</v>
+        <v>2.17637157440186</v>
       </c>
       <c r="H400" t="n">
         <v>21500</v>
@@ -11998,7 +11998,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>2.21249389648438</v>
+        <v>2.2124936580658</v>
       </c>
       <c r="H401" t="n">
         <v>6500</v>
@@ -12027,7 +12027,7 @@
         <v>2.5</v>
       </c>
       <c r="G402" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H402" t="n">
         <v>8500</v>
@@ -12114,7 +12114,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26667737960815</v>
+        <v>2.26667761802673</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12172,7 +12172,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G407" t="n">
-        <v>2.24861645698547</v>
+        <v>2.24861621856689</v>
       </c>
       <c r="H407" t="n">
         <v>7500</v>
@@ -12201,7 +12201,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>2.31183075904846</v>
+        <v>2.3118302822113</v>
       </c>
       <c r="H408" t="n">
         <v>12000</v>
@@ -12230,7 +12230,7 @@
         <v>2.5</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25764727592468</v>
+        <v>2.2576470375061</v>
       </c>
       <c r="H409" t="n">
         <v>5500</v>
@@ -12259,7 +12259,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>2.221524477005</v>
+        <v>2.22152471542358</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12288,7 +12288,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G411" t="n">
-        <v>2.17637181282043</v>
+        <v>2.17637157440186</v>
       </c>
       <c r="H411" t="n">
         <v>8000</v>
@@ -12317,7 +12317,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.14928007125854</v>
+        <v>2.14927983283997</v>
       </c>
       <c r="H412" t="n">
         <v>6500</v>
@@ -12375,7 +12375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.07703495025635</v>
+        <v>2.07703542709351</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>1.99575972557068</v>
+        <v>1.99575984477997</v>
       </c>
       <c r="H416" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G417" t="n">
-        <v>1.9506071805954</v>
+        <v>1.95060682296753</v>
       </c>
       <c r="H417" t="n">
         <v>8500</v>
@@ -12520,7 +12520,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H419" t="n">
         <v>3500</v>
@@ -12549,7 +12549,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G420" t="n">
-        <v>1.81514811515808</v>
+        <v>1.81514823436737</v>
       </c>
       <c r="H420" t="n">
         <v>9000</v>
@@ -12636,7 +12636,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G423" t="n">
-        <v>1.47198593616486</v>
+        <v>1.47198581695557</v>
       </c>
       <c r="H423" t="n">
         <v>9500</v>
@@ -12665,7 +12665,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G424" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H424" t="n">
         <v>3000</v>
@@ -12694,7 +12694,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G425" t="n">
-        <v>1.44489407539368</v>
+        <v>1.44489419460297</v>
       </c>
       <c r="H425" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>1.5</v>
       </c>
       <c r="G427" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12810,7 +12810,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G429" t="n">
-        <v>1.18300712108612</v>
+        <v>1.18300688266754</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>1.21009874343872</v>
+        <v>1.2100989818573</v>
       </c>
       <c r="H430" t="n">
         <v>31000</v>
@@ -12868,7 +12868,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>1.22364473342896</v>
+        <v>1.22364461421967</v>
       </c>
       <c r="H431" t="n">
         <v>3500</v>
@@ -12897,7 +12897,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>1.23267531394958</v>
+        <v>1.23267507553101</v>
       </c>
       <c r="H432" t="n">
         <v>2500</v>
@@ -12926,7 +12926,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G433" t="n">
-        <v>1.26428234577179</v>
+        <v>1.2642822265625</v>
       </c>
       <c r="H433" t="n">
         <v>6000</v>
@@ -12955,7 +12955,7 @@
         <v>1.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H434" t="n">
         <v>11500</v>
@@ -13071,7 +13071,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G438" t="n">
-        <v>1.2958892583847</v>
+        <v>1.29588937759399</v>
       </c>
       <c r="H438" t="n">
         <v>7000</v>
@@ -13100,7 +13100,7 @@
         <v>1.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35458827018738</v>
+        <v>1.35458815097809</v>
       </c>
       <c r="H439" t="n">
         <v>5000</v>
@@ -13187,7 +13187,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.49004709720612</v>
+        <v>1.49004697799683</v>
       </c>
       <c r="H442" t="n">
         <v>13000</v>
@@ -13216,7 +13216,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57132244110107</v>
+        <v>1.57132232189178</v>
       </c>
       <c r="H443" t="n">
         <v>15000</v>
@@ -13245,7 +13245,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G444" t="n">
-        <v>1.6029292345047</v>
+        <v>1.60292935371399</v>
       </c>
       <c r="H444" t="n">
         <v>17000</v>
@@ -13274,7 +13274,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G445" t="n">
-        <v>1.62099051475525</v>
+        <v>1.62099063396454</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13361,7 +13361,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.670658826828</v>
+        <v>1.67065894603729</v>
       </c>
       <c r="H448" t="n">
         <v>19500</v>
@@ -13390,7 +13390,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G449" t="n">
-        <v>1.66162836551666</v>
+        <v>1.66162824630737</v>
       </c>
       <c r="H449" t="n">
         <v>7000</v>
@@ -13419,7 +13419,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H450" t="n">
         <v>30500</v>
@@ -13448,7 +13448,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74290359020233</v>
+        <v>1.74290335178375</v>
       </c>
       <c r="H451" t="n">
         <v>41500</v>
@@ -13477,7 +13477,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>1.75193417072296</v>
+        <v>1.75193405151367</v>
       </c>
       <c r="H452" t="n">
         <v>5000</v>
@@ -13535,7 +13535,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G454" t="n">
-        <v>1.80160212516785</v>
+        <v>1.80160224437714</v>
       </c>
       <c r="H454" t="n">
         <v>4500</v>
@@ -13564,7 +13564,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>1.77902579307556</v>
+        <v>1.77902591228485</v>
       </c>
       <c r="H455" t="n">
         <v>4500</v>
@@ -13593,7 +13593,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>1.89642333984375</v>
+        <v>1.89642345905304</v>
       </c>
       <c r="H456" t="n">
         <v>48500</v>
@@ -13622,7 +13622,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G457" t="n">
-        <v>1.86030125617981</v>
+        <v>1.86030113697052</v>
       </c>
       <c r="H457" t="n">
         <v>7500</v>
@@ -13709,7 +13709,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>1.75984966754913</v>
+        <v>1.75984954833984</v>
       </c>
       <c r="H460" t="n">
         <v>18500</v>
@@ -13738,7 +13738,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H461" t="n">
         <v>31000</v>
@@ -13767,7 +13767,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G462" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H462" t="n">
         <v>23000</v>
@@ -13796,7 +13796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>1.57243716716766</v>
+        <v>1.57243728637695</v>
       </c>
       <c r="H463" t="n">
         <v>9500</v>
@@ -13825,7 +13825,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H464" t="n">
         <v>7000</v>
@@ -13854,7 +13854,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H465" t="n">
         <v>9500</v>
@@ -13912,7 +13912,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G467" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H467" t="n">
         <v>5000</v>
@@ -13970,7 +13970,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H469" t="n">
         <v>4000</v>
@@ -13999,7 +13999,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G470" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H470" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G471" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H471" t="n">
         <v>3500</v>
@@ -14057,7 +14057,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H472" t="n">
         <v>1000</v>
@@ -14144,7 +14144,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>1.67757105827332</v>
+        <v>1.6775711774826</v>
       </c>
       <c r="H475" t="n">
         <v>12000</v>
@@ -14173,7 +14173,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G476" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H476" t="n">
         <v>4500</v>
@@ -14260,7 +14260,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G479" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H479" t="n">
         <v>1000</v>
@@ -14289,7 +14289,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H480" t="n">
         <v>4000</v>
@@ -14318,7 +14318,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G481" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H484" t="n">
         <v>46500</v>
@@ -14434,7 +14434,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G485" t="n">
-        <v>1.92897796630859</v>
+        <v>1.92897808551788</v>
       </c>
       <c r="H485" t="n">
         <v>15500</v>
@@ -14463,7 +14463,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G486" t="n">
-        <v>1.82384419441223</v>
+        <v>1.82384443283081</v>
       </c>
       <c r="H486" t="n">
         <v>9500</v>
@@ -14492,7 +14492,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>1.87412583827972</v>
+        <v>1.87412559986115</v>
       </c>
       <c r="H487" t="n">
         <v>13000</v>
@@ -14550,7 +14550,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G489" t="n">
-        <v>1.88326787948608</v>
+        <v>1.88326776027679</v>
       </c>
       <c r="H489" t="n">
         <v>5000</v>
@@ -14579,7 +14579,7 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H490" t="n">
         <v>500</v>
@@ -14666,7 +14666,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G493" t="n">
-        <v>1.82384419441223</v>
+        <v>1.82384443283081</v>
       </c>
       <c r="H493" t="n">
         <v>1500</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>1.82841527462006</v>
+        <v>1.82841539382935</v>
       </c>
       <c r="H494" t="n">
         <v>1000</v>
@@ -14724,7 +14724,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G495" t="n">
-        <v>1.78270483016968</v>
+        <v>1.78270494937897</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14753,7 +14753,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G496" t="n">
-        <v>1.77813398838043</v>
+        <v>1.77813386917114</v>
       </c>
       <c r="H496" t="n">
         <v>7500</v>
@@ -14782,7 +14782,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.77813398838043</v>
+        <v>1.77813386917114</v>
       </c>
       <c r="H497" t="n">
         <v>2000</v>
@@ -14811,7 +14811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G498" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H498" t="n">
         <v>2000</v>
@@ -14840,7 +14840,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G499" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -14869,7 +14869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H500" t="n">
         <v>2000</v>
@@ -14898,7 +14898,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74613666534424</v>
+        <v>1.74613654613495</v>
       </c>
       <c r="H502" t="n">
         <v>5000</v>
@@ -15130,7 +15130,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G509" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H509" t="n">
         <v>3500</v>
@@ -15159,7 +15159,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G510" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H510" t="n">
         <v>3000</v>
@@ -15188,7 +15188,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G511" t="n">
-        <v>1.76442086696625</v>
+        <v>1.76442074775696</v>
       </c>
       <c r="H511" t="n">
         <v>500</v>
@@ -15304,7 +15304,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G515" t="n">
-        <v>1.71871030330658</v>
+        <v>1.71871042251587</v>
       </c>
       <c r="H515" t="n">
         <v>1000</v>
@@ -15333,7 +15333,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G516" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H516" t="n">
         <v>500</v>
@@ -15362,7 +15362,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>1.77356290817261</v>
+        <v>1.7735630273819</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75527858734131</v>
+        <v>1.7552787065506</v>
       </c>
       <c r="H519" t="n">
         <v>1500</v>
@@ -15449,7 +15449,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H520" t="n">
         <v>10500</v>
@@ -15478,7 +15478,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G521" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H521" t="n">
         <v>2500</v>
@@ -15507,7 +15507,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G522" t="n">
-        <v>1.5952924489975</v>
+        <v>1.59529232978821</v>
       </c>
       <c r="H522" t="n">
         <v>500</v>
@@ -15652,7 +15652,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>1.61814749240875</v>
+        <v>1.61814761161804</v>
       </c>
       <c r="H527" t="n">
         <v>6500</v>
@@ -15681,7 +15681,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G528" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H528" t="n">
         <v>3000</v>
@@ -15884,7 +15884,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H535" t="n">
         <v>3500</v>
@@ -15913,7 +15913,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G537" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G538" t="n">
-        <v>1.60443460941315</v>
+        <v>1.60443449020386</v>
       </c>
       <c r="H538" t="n">
         <v>10000</v>
@@ -16000,7 +16000,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G539" t="n">
-        <v>1.60443460941315</v>
+        <v>1.60443449020386</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.60443460941315</v>
+        <v>1.60443449020386</v>
       </c>
       <c r="H540" t="n">
         <v>3000</v>
@@ -16058,7 +16058,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G541" t="n">
-        <v>1.60443460941315</v>
+        <v>1.60443449020386</v>
       </c>
       <c r="H541" t="n">
         <v>500</v>
@@ -16087,7 +16087,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G542" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16116,7 +16116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G544" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G545" t="n">
-        <v>1.64100277423859</v>
+        <v>1.6410026550293</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H546" t="n">
         <v>2500</v>
@@ -16261,7 +16261,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>1.59072148799896</v>
+        <v>1.59072124958038</v>
       </c>
       <c r="H548" t="n">
         <v>9500</v>
@@ -16290,7 +16290,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H549" t="n">
         <v>7000</v>
@@ -16551,7 +16551,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H558" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H559" t="n">
         <v>500</v>
@@ -16609,7 +16609,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.63643181324005</v>
+        <v>1.63643157482147</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G562" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H562" t="n">
         <v>9000</v>
@@ -16725,7 +16725,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16754,7 +16754,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H565" t="n">
         <v>500</v>
@@ -16812,7 +16812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H567" t="n">
         <v>4000</v>
@@ -16841,7 +16841,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G568" t="n">
-        <v>1.58157920837402</v>
+        <v>1.58157932758331</v>
       </c>
       <c r="H568" t="n">
         <v>3500</v>
@@ -16870,7 +16870,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>1.62728953361511</v>
+        <v>1.6272896528244</v>
       </c>
       <c r="H569" t="n">
         <v>2500</v>
@@ -16899,7 +16899,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H570" t="n">
         <v>11500</v>
@@ -16957,7 +16957,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G572" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H572" t="n">
         <v>4500</v>
@@ -17015,7 +17015,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G574" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H574" t="n">
         <v>500</v>
@@ -17102,7 +17102,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G577" t="n">
-        <v>1.7872759103775</v>
+        <v>1.78727602958679</v>
       </c>
       <c r="H577" t="n">
         <v>17500</v>
@@ -17218,7 +17218,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68214213848114</v>
+        <v>1.68214225769043</v>
       </c>
       <c r="H581" t="n">
         <v>4000</v>
@@ -17247,7 +17247,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G582" t="n">
-        <v>1.61357641220093</v>
+        <v>1.61357653141022</v>
       </c>
       <c r="H582" t="n">
         <v>5500</v>
@@ -17276,7 +17276,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.60900545120239</v>
+        <v>1.60900557041168</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17305,7 +17305,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>1.56329524517059</v>
+        <v>1.5632951259613</v>
       </c>
       <c r="H584" t="n">
         <v>500</v>
@@ -17334,7 +17334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>1.63287794589996</v>
+        <v>1.63287806510925</v>
       </c>
       <c r="H585" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937863349915</v>
       </c>
       <c r="H588" t="n">
         <v>11500</v>
@@ -17450,7 +17450,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.54937851428986</v>
+        <v>1.54937863349915</v>
       </c>
       <c r="H589" t="n">
         <v>500</v>
@@ -17479,7 +17479,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G590" t="n">
-        <v>1.53082311153412</v>
+        <v>1.53082299232483</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17566,7 +17566,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.44268476963043</v>
+        <v>1.44268465042114</v>
       </c>
       <c r="H593" t="n">
         <v>4500</v>
@@ -17595,7 +17595,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G594" t="n">
-        <v>1.44268476963043</v>
+        <v>1.44268465042114</v>
       </c>
       <c r="H594" t="n">
         <v>22000</v>
@@ -17624,7 +17624,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>1.44732367992401</v>
+        <v>1.44732356071472</v>
       </c>
       <c r="H595" t="n">
         <v>10500</v>
@@ -17653,7 +17653,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G596" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H596" t="n">
         <v>5000</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.45660138130188</v>
+        <v>1.45660150051117</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G604" t="n">
-        <v>1.77204370498657</v>
+        <v>1.77204358577728</v>
       </c>
       <c r="H604" t="n">
         <v>8500</v>
@@ -17914,7 +17914,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.80915451049805</v>
+        <v>1.80915462970734</v>
       </c>
       <c r="H605" t="n">
         <v>13000</v>
@@ -17943,7 +17943,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G606" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H606" t="n">
         <v>49500</v>
@@ -17972,7 +17972,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G607" t="n">
-        <v>1.88337624073029</v>
+        <v>1.88337635993958</v>
       </c>
       <c r="H607" t="n">
         <v>35500</v>
@@ -18001,7 +18001,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G608" t="n">
-        <v>1.92048704624176</v>
+        <v>1.92048692703247</v>
       </c>
       <c r="H608" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G609" t="n">
-        <v>1.91120958328247</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H609" t="n">
         <v>9500</v>
@@ -18059,7 +18059,7 @@
         <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H610" t="n">
         <v>9500</v>
@@ -18088,7 +18088,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G611" t="n">
-        <v>1.7905992269516</v>
+        <v>1.79059910774231</v>
       </c>
       <c r="H611" t="n">
         <v>12000</v>
@@ -18204,7 +18204,7 @@
         <v>2</v>
       </c>
       <c r="G615" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H615" t="n">
         <v>4000</v>
@@ -18233,7 +18233,7 @@
         <v>2</v>
       </c>
       <c r="G616" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H616" t="n">
         <v>2000</v>
@@ -18291,7 +18291,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>1.91120958328247</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H618" t="n">
         <v>2500</v>
@@ -18320,7 +18320,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G619" t="n">
-        <v>1.91120958328247</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>1.91120958328247</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2</v>
       </c>
       <c r="G621" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H621" t="n">
         <v>3500</v>
@@ -18407,7 +18407,7 @@
         <v>2</v>
       </c>
       <c r="G622" t="n">
-        <v>1.85554313659668</v>
+        <v>1.85554325580597</v>
       </c>
       <c r="H622" t="n">
         <v>500</v>
@@ -18436,7 +18436,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>2.05037498474121</v>
+        <v>2.05037522315979</v>
       </c>
       <c r="H623" t="n">
         <v>67500</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G624" t="n">
-        <v>2.07820844650269</v>
+        <v>2.07820820808411</v>
       </c>
       <c r="H624" t="n">
         <v>35500</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97615349292755</v>
+        <v>1.97615373134613</v>
       </c>
       <c r="H625" t="n">
         <v>14000</v>
@@ -18523,7 +18523,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.91120958328247</v>
+        <v>1.91120946407318</v>
       </c>
       <c r="H626" t="n">
         <v>25000</v>
@@ -18552,7 +18552,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.94832015037537</v>
+        <v>1.94832026958466</v>
       </c>
       <c r="H627" t="n">
         <v>8500</v>
@@ -18581,7 +18581,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>2.01326441764832</v>
+        <v>2.01326417922974</v>
       </c>
       <c r="H628" t="n">
         <v>10500</v>
@@ -18639,7 +18639,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.00398683547974</v>
+        <v>2.00398659706116</v>
       </c>
       <c r="H630" t="n">
         <v>13000</v>
@@ -18668,7 +18668,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>2.45859503746033</v>
+        <v>2.45859479904175</v>
       </c>
       <c r="H631" t="n">
         <v>119500</v>
@@ -18697,7 +18697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>2.91320276260376</v>
+        <v>2.91320300102234</v>
       </c>
       <c r="H632" t="n">
         <v>262000</v>
@@ -18726,7 +18726,7 @@
         <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H633" t="n">
         <v>86500</v>
@@ -18755,7 +18755,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G634" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H634" t="n">
         <v>177500</v>
@@ -18784,7 +18784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H635" t="n">
         <v>49500</v>
@@ -18813,7 +18813,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G636" t="n">
-        <v>2.84825849533081</v>
+        <v>2.84825873374939</v>
       </c>
       <c r="H636" t="n">
         <v>10500</v>
@@ -18842,7 +18842,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G637" t="n">
-        <v>2.84825849533081</v>
+        <v>2.84825873374939</v>
       </c>
       <c r="H637" t="n">
         <v>39500</v>
@@ -18900,7 +18900,7 @@
         <v>3</v>
       </c>
       <c r="G639" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H639" t="n">
         <v>1000</v>
@@ -18987,7 +18987,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G642" t="n">
-        <v>2.64414882659912</v>
+        <v>2.6441490650177</v>
       </c>
       <c r="H642" t="n">
         <v>34000</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H644" t="n">
         <v>12000</v>
@@ -19103,7 +19103,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G646" t="n">
-        <v>2.65342664718628</v>
+        <v>2.65342688560486</v>
       </c>
       <c r="H646" t="n">
         <v>31000</v>
@@ -19132,7 +19132,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H647" t="n">
         <v>12000</v>
@@ -19161,7 +19161,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G648" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>2.54209423065186</v>
+        <v>2.54209399223328</v>
       </c>
       <c r="H650" t="n">
         <v>4500</v>
@@ -19277,7 +19277,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.34726214408875</v>
+        <v>2.34726238250732</v>
       </c>
       <c r="H652" t="n">
         <v>52500</v>
@@ -19306,7 +19306,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H653" t="n">
         <v>19500</v>
@@ -19335,7 +19335,7 @@
         <v>2.5</v>
       </c>
       <c r="G654" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H654" t="n">
         <v>24000</v>
@@ -19364,7 +19364,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H655" t="n">
         <v>36500</v>
@@ -19480,7 +19480,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.31015133857727</v>
+        <v>2.31015110015869</v>
       </c>
       <c r="H659" t="n">
         <v>10500</v>
@@ -19509,7 +19509,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G660" t="n">
-        <v>2.31015133857727</v>
+        <v>2.31015110015869</v>
       </c>
       <c r="H660" t="n">
         <v>8000</v>
@@ -19538,7 +19538,7 @@
         <v>2.5</v>
       </c>
       <c r="G661" t="n">
-        <v>2.31942915916443</v>
+        <v>2.31942892074585</v>
       </c>
       <c r="H661" t="n">
         <v>210500</v>
@@ -19596,7 +19596,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>2.41220569610596</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H663" t="n">
         <v>11500</v>
@@ -19654,7 +19654,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.34726214408875</v>
+        <v>2.34726238250732</v>
       </c>
       <c r="H665" t="n">
         <v>5500</v>
@@ -19741,7 +19741,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.41220569610596</v>
+        <v>2.41220617294312</v>
       </c>
       <c r="H668" t="n">
         <v>14000</v>
@@ -19770,7 +19770,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>2.43076157569885</v>
+        <v>2.43076133728027</v>
       </c>
       <c r="H669" t="n">
         <v>1500</v>
@@ -19799,7 +19799,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H670" t="n">
         <v>4500</v>
@@ -19828,7 +19828,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H671" t="n">
         <v>8000</v>
@@ -19857,7 +19857,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37509536743164</v>
+        <v>2.37509512901306</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703802108765</v>
       </c>
       <c r="H673" t="n">
         <v>48500</v>
@@ -19915,7 +19915,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57920479774475</v>
+        <v>2.57920503616333</v>
       </c>
       <c r="H674" t="n">
         <v>30500</v>
@@ -19944,7 +19944,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G675" t="n">
-        <v>2.57920479774475</v>
+        <v>2.57920503616333</v>
       </c>
       <c r="H675" t="n">
         <v>12000</v>
@@ -19973,7 +19973,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>2.60703825950623</v>
+        <v>2.60703802108765</v>
       </c>
       <c r="H676" t="n">
         <v>27000</v>
@@ -20002,7 +20002,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.69053745269775</v>
+        <v>2.69053769111633</v>
       </c>
       <c r="H677" t="n">
         <v>14000</v>
@@ -20031,7 +20031,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6163158416748</v>
+        <v>2.61631560325623</v>
       </c>
       <c r="H678" t="n">
         <v>18000</v>
@@ -20089,7 +20089,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>2.72764849662781</v>
+        <v>2.72764873504639</v>
       </c>
       <c r="H680" t="n">
         <v>3000</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.82970309257507</v>
+        <v>2.82970333099365</v>
       </c>
       <c r="H683" t="n">
         <v>121000</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.83898091316223</v>
+        <v>2.83898115158081</v>
       </c>
       <c r="H684" t="n">
         <v>17000</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.7833149433136</v>
+        <v>2.78331470489502</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G687" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H687" t="n">
         <v>18500</v>
@@ -20408,7 +20408,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>2.9039249420166</v>
+        <v>2.90392518043518</v>
       </c>
       <c r="H691" t="n">
         <v>110000</v>
@@ -20437,7 +20437,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H692" t="n">
         <v>52500</v>
@@ -20466,7 +20466,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H693" t="n">
         <v>128500</v>
@@ -20495,7 +20495,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G694" t="n">
-        <v>2.95031380653381</v>
+        <v>2.95031356811523</v>
       </c>
       <c r="H694" t="n">
         <v>12500</v>
@@ -20524,7 +20524,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>2.87609195709229</v>
+        <v>2.87609171867371</v>
       </c>
       <c r="H695" t="n">
         <v>42500</v>
@@ -20553,7 +20553,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>2.89464735984802</v>
+        <v>2.89464712142944</v>
       </c>
       <c r="H696" t="n">
         <v>8000</v>
@@ -20582,7 +20582,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>2.83898091316223</v>
+        <v>2.83898115158081</v>
       </c>
       <c r="H697" t="n">
         <v>5500</v>
@@ -20640,7 +20640,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G699" t="n">
-        <v>2.87609195709229</v>
+        <v>2.87609171867371</v>
       </c>
       <c r="H699" t="n">
         <v>9500</v>
@@ -20669,7 +20669,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G700" t="n">
-        <v>2.87609195709229</v>
+        <v>2.87609171867371</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G701" t="n">
-        <v>2.87609195709229</v>
+        <v>2.87609171867371</v>
       </c>
       <c r="H701" t="n">
         <v>6500</v>
@@ -20727,7 +20727,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.87609195709229</v>
+        <v>2.87609171867371</v>
       </c>
       <c r="H702" t="n">
         <v>1500</v>
@@ -20756,7 +20756,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.82042551040649</v>
+        <v>2.82042574882507</v>
       </c>
       <c r="H703" t="n">
         <v>9500</v>
@@ -20843,7 +20843,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H706" t="n">
         <v>5500</v>
@@ -21017,7 +21017,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G712" t="n">
-        <v>2.98742437362671</v>
+        <v>2.98742461204529</v>
       </c>
       <c r="H712" t="n">
         <v>500</v>
@@ -21539,7 +21539,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H730" t="n">
         <v>6000</v>
@@ -21771,7 +21771,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G738" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21887,7 +21887,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H742" t="n">
         <v>2500</v>
@@ -21916,7 +21916,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>2.92089080810547</v>
+        <v>2.92089056968689</v>
       </c>
       <c r="H743" t="n">
         <v>10000</v>
@@ -22061,7 +22061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G748" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H748" t="n">
         <v>24500</v>
@@ -22090,7 +22090,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G749" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H749" t="n">
         <v>6500</v>
@@ -22119,7 +22119,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G750" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H750" t="n">
         <v>69500</v>
@@ -22148,7 +22148,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H751" t="n">
         <v>37000</v>
@@ -22177,7 +22177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G752" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H752" t="n">
         <v>5500</v>
@@ -22264,7 +22264,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H755" t="n">
         <v>1000</v>
@@ -22293,7 +22293,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H756" t="n">
         <v>17000</v>
@@ -22322,7 +22322,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H757" t="n">
         <v>24500</v>
@@ -22467,7 +22467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H762" t="n">
         <v>12000</v>
@@ -22641,7 +22641,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G768" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H768" t="n">
         <v>7000</v>
@@ -22902,7 +22902,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H777" t="n">
         <v>10000</v>
@@ -22989,7 +22989,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G780" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H780" t="n">
         <v>4000</v>
@@ -23047,7 +23047,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G782" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H782" t="n">
         <v>1500</v>
@@ -23076,7 +23076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G783" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H786" t="n">
         <v>6000</v>
@@ -23192,7 +23192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G787" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H787" t="n">
         <v>7000</v>
@@ -23221,7 +23221,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G788" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H788" t="n">
         <v>5000</v>
@@ -23279,7 +23279,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G790" t="n">
-        <v>3.16586852073669</v>
+        <v>3.16586875915527</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G791" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H791" t="n">
         <v>1500</v>
@@ -23395,7 +23395,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G794" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H794" t="n">
         <v>9000</v>
@@ -23511,7 +23511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H798" t="n">
         <v>7000</v>
@@ -23656,7 +23656,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.18471312522888</v>
+        <v>3.18471336364746</v>
       </c>
       <c r="H803" t="n">
         <v>42500</v>
@@ -23772,7 +23772,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>3.26009082794189</v>
+        <v>3.26009106636047</v>
       </c>
       <c r="H807" t="n">
         <v>8500</v>
@@ -23801,7 +23801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H808" t="n">
         <v>6500</v>
@@ -23830,7 +23830,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>3.12817978858948</v>
+        <v>3.1281795501709</v>
       </c>
       <c r="H809" t="n">
         <v>14500</v>
@@ -23859,7 +23859,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H810" t="n">
         <v>3500</v>
@@ -23946,7 +23946,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H813" t="n">
         <v>7000</v>
@@ -24004,7 +24004,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>3.0904905796051</v>
+        <v>3.09049081802368</v>
       </c>
       <c r="H815" t="n">
         <v>15000</v>
@@ -24033,7 +24033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G816" t="n">
-        <v>3.20355772972107</v>
+        <v>3.20355749130249</v>
       </c>
       <c r="H816" t="n">
         <v>44000</v>
@@ -24091,7 +24091,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H818" t="n">
         <v>30500</v>
@@ -24120,7 +24120,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>3.27893567085266</v>
+        <v>3.27893543243408</v>
       </c>
       <c r="H819" t="n">
         <v>13000</v>
@@ -24236,7 +24236,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G823" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H823" t="n">
         <v>29000</v>
@@ -24265,7 +24265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G824" t="n">
-        <v>3.52391338348389</v>
+        <v>3.52391362190247</v>
       </c>
       <c r="H824" t="n">
         <v>23500</v>
@@ -24526,7 +24526,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>4.0138692855835</v>
+        <v>4.01386976242065</v>
       </c>
       <c r="H833" t="n">
         <v>119000</v>
@@ -24613,7 +24613,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H836" t="n">
         <v>184500</v>
@@ -24816,7 +24816,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H843" t="n">
         <v>32000</v>
@@ -24874,7 +24874,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H845" t="n">
         <v>16500</v>
@@ -24961,7 +24961,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G848" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H848" t="n">
         <v>22000</v>
@@ -24990,7 +24990,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H849" t="n">
         <v>25000</v>
@@ -25106,7 +25106,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25135,7 +25135,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H854" t="n">
         <v>16000</v>
@@ -25164,7 +25164,7 @@
         <v>4.5</v>
       </c>
       <c r="G855" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H855" t="n">
         <v>16000</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H856" t="n">
         <v>4500</v>
@@ -25222,7 +25222,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H857" t="n">
         <v>18000</v>
@@ -25251,7 +25251,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G858" t="n">
-        <v>4.0138692855835</v>
+        <v>4.01386976242065</v>
       </c>
       <c r="H858" t="n">
         <v>39000</v>
@@ -25280,7 +25280,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H859" t="n">
         <v>13000</v>
@@ -25309,7 +25309,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G860" t="n">
-        <v>3.99502444267273</v>
+        <v>3.99502420425415</v>
       </c>
       <c r="H860" t="n">
         <v>49000</v>
@@ -25338,7 +25338,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G861" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H861" t="n">
         <v>24000</v>
@@ -25425,7 +25425,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G864" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H864" t="n">
         <v>12000</v>
@@ -25483,7 +25483,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G866" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H866" t="n">
         <v>18000</v>
@@ -25512,7 +25512,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G867" t="n">
-        <v>4.05155849456787</v>
+        <v>4.05155801773071</v>
       </c>
       <c r="H867" t="n">
         <v>13500</v>
@@ -25541,7 +25541,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G868" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H868" t="n">
         <v>16000</v>
@@ -25570,7 +25570,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G869" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H869" t="n">
         <v>5000</v>
@@ -25599,7 +25599,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.16462469100952</v>
+        <v>4.16462516784668</v>
       </c>
       <c r="H870" t="n">
         <v>19500</v>
@@ -25628,7 +25628,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>4.16462469100952</v>
+        <v>4.16462516784668</v>
       </c>
       <c r="H871" t="n">
         <v>14500</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H874" t="n">
         <v>25500</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H875" t="n">
         <v>6500</v>
@@ -25773,7 +25773,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G876" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H876" t="n">
         <v>72000</v>
@@ -26353,7 +26353,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H896" t="n">
         <v>22500</v>
@@ -26469,7 +26469,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>5.27644777297974</v>
+        <v>5.27644824981689</v>
       </c>
       <c r="H900" t="n">
         <v>253500</v>
@@ -26498,7 +26498,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G901" t="n">
-        <v>5.37066984176636</v>
+        <v>5.37067031860352</v>
       </c>
       <c r="H901" t="n">
         <v>172500</v>
@@ -26527,7 +26527,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H902" t="n">
         <v>88500</v>
@@ -26585,7 +26585,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>5.13511419296265</v>
+        <v>5.1351146697998</v>
       </c>
       <c r="H904" t="n">
         <v>67500</v>
@@ -26614,7 +26614,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>5.27644777297974</v>
+        <v>5.27644824981689</v>
       </c>
       <c r="H905" t="n">
         <v>36500</v>
@@ -26643,7 +26643,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G906" t="n">
-        <v>5.13511419296265</v>
+        <v>5.1351146697998</v>
       </c>
       <c r="H906" t="n">
         <v>35000</v>
@@ -26701,7 +26701,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H908" t="n">
         <v>23500</v>
@@ -26730,7 +26730,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G909" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -26759,7 +26759,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H910" t="n">
         <v>22500</v>
@@ -26875,7 +26875,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>5.04089260101318</v>
+        <v>5.04089164733887</v>
       </c>
       <c r="H914" t="n">
         <v>37000</v>
@@ -27020,7 +27020,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08800315856934</v>
+        <v>5.08800363540649</v>
       </c>
       <c r="H919" t="n">
         <v>26500</v>
@@ -27368,7 +27368,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>3.56160235404968</v>
+        <v>3.5616021156311</v>
       </c>
       <c r="H931" t="n">
         <v>72500</v>
@@ -27397,7 +27397,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>3.63698029518127</v>
+        <v>3.6369800567627</v>
       </c>
       <c r="H932" t="n">
         <v>50500</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.9384913444519</v>
+        <v>3.93849110603333</v>
       </c>
       <c r="H934" t="n">
         <v>15500</v>
@@ -27484,7 +27484,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>3.88195824623108</v>
+        <v>3.88195776939392</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G936" t="n">
-        <v>3.99502444267273</v>
+        <v>3.99502420425415</v>
       </c>
       <c r="H936" t="n">
         <v>4500</v>
@@ -27542,7 +27542,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G937" t="n">
-        <v>4.03271389007568</v>
+        <v>4.03271436691284</v>
       </c>
       <c r="H937" t="n">
         <v>12000</v>
@@ -27571,7 +27571,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G938" t="n">
-        <v>4.07040309906006</v>
+        <v>4.0704026222229</v>
       </c>
       <c r="H938" t="n">
         <v>8500</v>
@@ -27600,7 +27600,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H939" t="n">
         <v>8000</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.24000310897827</v>
+        <v>4.24000263214111</v>
       </c>
       <c r="H940" t="n">
         <v>8000</v>
@@ -27658,7 +27658,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H941" t="n">
         <v>3500</v>
@@ -27745,7 +27745,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>4.22115850448608</v>
+        <v>4.22115802764893</v>
       </c>
       <c r="H944" t="n">
         <v>3500</v>
@@ -28093,7 +28093,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G956" t="n">
-        <v>4.56978034973145</v>
+        <v>4.5697808265686</v>
       </c>
       <c r="H956" t="n">
         <v>1500</v>
@@ -28180,7 +28180,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G959" t="n">
-        <v>4.1928915977478</v>
+        <v>4.19289112091064</v>
       </c>
       <c r="H959" t="n">
         <v>3000</v>
@@ -28267,7 +28267,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G962" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635778427124</v>
       </c>
       <c r="H962" t="n">
         <v>2500</v>
@@ -28296,7 +28296,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G963" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H963" t="n">
         <v>10500</v>
@@ -28354,7 +28354,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>4.18346929550171</v>
+        <v>4.18346977233887</v>
       </c>
       <c r="H965" t="n">
         <v>3500</v>
@@ -28383,7 +28383,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>4.17404699325562</v>
+        <v>4.17404747009277</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28528,7 +28528,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>4.55093669891357</v>
+        <v>4.55093622207642</v>
       </c>
       <c r="H971" t="n">
         <v>9000</v>
@@ -28586,7 +28586,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>4.31538057327271</v>
+        <v>4.31538105010986</v>
       </c>
       <c r="H973" t="n">
         <v>11500</v>
@@ -28673,7 +28673,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G976" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H976" t="n">
         <v>20000</v>
@@ -28702,7 +28702,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G977" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H977" t="n">
         <v>5500</v>
@@ -28760,7 +28760,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G979" t="n">
-        <v>3.96998429298401</v>
+        <v>3.96998381614685</v>
       </c>
       <c r="H979" t="n">
         <v>6500</v>
@@ -28847,7 +28847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H982" t="n">
         <v>5500</v>
@@ -28876,7 +28876,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G985" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H985" t="n">
         <v>2500</v>
@@ -29021,7 +29021,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G988" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H988" t="n">
         <v>2500</v>
@@ -29050,7 +29050,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G989" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H989" t="n">
         <v>4000</v>
@@ -29137,7 +29137,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G992" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H992" t="n">
         <v>2500</v>
@@ -29166,7 +29166,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G993" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H993" t="n">
         <v>500</v>
@@ -29253,7 +29253,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G996" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H996" t="n">
         <v>2500</v>
@@ -29340,7 +29340,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G999" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1000" t="n">
         <v>12000</v>
@@ -29398,7 +29398,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1001" t="n">
         <v>16000</v>
@@ -29601,7 +29601,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1008" t="n">
         <v>2000</v>
@@ -29688,7 +29688,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.29760408401489</v>
+        <v>4.29760456085205</v>
       </c>
       <c r="H1011" t="n">
         <v>8500</v>
@@ -29804,7 +29804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1015" t="n">
         <v>2500</v>
@@ -29862,7 +29862,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1017" t="n">
         <v>2000</v>
@@ -30065,7 +30065,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1024" t="n">
         <v>6500</v>
@@ -30326,7 +30326,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1033" t="n">
         <v>19500</v>
@@ -30355,7 +30355,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1034" t="n">
         <v>2000</v>
@@ -30442,7 +30442,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.37469148635864</v>
+        <v>4.37469100952148</v>
       </c>
       <c r="H1037" t="n">
         <v>1500</v>
@@ -30500,7 +30500,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1039" t="n">
         <v>6500</v>
@@ -30819,7 +30819,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1050" t="n">
         <v>1000</v>
@@ -30848,7 +30848,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1051" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1059" t="n">
         <v>1500</v>
@@ -31254,7 +31254,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1065" t="n">
         <v>20000</v>
@@ -31312,7 +31312,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1067" t="n">
         <v>9000</v>
@@ -31370,7 +31370,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1069" t="n">
         <v>2000</v>
@@ -31399,7 +31399,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.91216897964478</v>
+        <v>3.9121687412262</v>
       </c>
       <c r="H1070" t="n">
         <v>8000</v>
@@ -31486,7 +31486,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1073" t="n">
         <v>35000</v>
@@ -31573,7 +31573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1076" t="n">
         <v>27000</v>
@@ -31602,7 +31602,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.44001054763794</v>
+        <v>3.44001078605652</v>
       </c>
       <c r="H1077" t="n">
         <v>17000</v>
@@ -31805,7 +31805,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.27620077133179</v>
+        <v>3.27620053291321</v>
       </c>
       <c r="H1084" t="n">
         <v>6000</v>
@@ -31834,7 +31834,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.49782609939575</v>
+        <v>3.49782586097717</v>
       </c>
       <c r="H1085" t="n">
         <v>14500</v>
@@ -32037,7 +32037,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1092" t="n">
         <v>13500</v>
@@ -32095,7 +32095,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1094" t="n">
         <v>15500</v>
@@ -32124,7 +32124,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1095" t="n">
         <v>19500</v>
@@ -32240,7 +32240,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1099" t="n">
         <v>3000</v>
@@ -32269,7 +32269,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1100" t="n">
         <v>4000</v>
@@ -32298,7 +32298,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1101" t="n">
         <v>7500</v>
@@ -32327,7 +32327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.0856146812439</v>
+        <v>4.08561420440674</v>
       </c>
       <c r="H1102" t="n">
         <v>12000</v>
@@ -32356,7 +32356,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1103" t="n">
         <v>10000</v>
@@ -32443,7 +32443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1106" t="n">
         <v>17000</v>
@@ -32472,7 +32472,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1107" t="n">
         <v>5500</v>
@@ -32530,7 +32530,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1109" t="n">
         <v>6000</v>
@@ -32559,7 +32559,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.07597923278809</v>
+        <v>4.07597875595093</v>
       </c>
       <c r="H1110" t="n">
         <v>8500</v>
@@ -32588,7 +32588,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1111" t="n">
         <v>9000</v>
@@ -32617,7 +32617,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1112" t="n">
         <v>6500</v>
@@ -32762,7 +32762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1117" t="n">
         <v>2000</v>
@@ -32849,7 +32849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.95071268081665</v>
+        <v>3.95071244239807</v>
       </c>
       <c r="H1120" t="n">
         <v>4500</v>
@@ -33226,7 +33226,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.94107675552368</v>
+        <v>3.9410765171051</v>
       </c>
       <c r="H1133" t="n">
         <v>1000</v>
@@ -33458,7 +33458,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1141" t="n">
         <v>4500</v>
@@ -33487,7 +33487,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.02779960632324</v>
+        <v>4.02779912948608</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33516,7 +33516,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1143" t="n">
         <v>2500</v>
@@ -33545,7 +33545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1144" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1144" t="n">
         <v>6500</v>
@@ -33574,7 +33574,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1145" t="n">
         <v>11500</v>
@@ -33632,7 +33632,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1147" t="n">
         <v>1000</v>
@@ -33748,7 +33748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1151" t="n">
         <v>2500</v>
@@ -33806,7 +33806,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.50959396362305</v>
+        <v>4.50959348678589</v>
       </c>
       <c r="H1153" t="n">
         <v>109500</v>
@@ -33922,7 +33922,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.58668088912964</v>
+        <v>4.5866813659668</v>
       </c>
       <c r="H1157" t="n">
         <v>17000</v>
@@ -33951,7 +33951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1158" t="n">
         <v>41000</v>
@@ -34067,7 +34067,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1162" t="n">
         <v>20000</v>
@@ -34125,7 +34125,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.76976203918457</v>
+        <v>4.76976251602173</v>
       </c>
       <c r="H1164" t="n">
         <v>18000</v>
@@ -34154,7 +34154,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.73121881484985</v>
+        <v>4.73121929168701</v>
       </c>
       <c r="H1165" t="n">
         <v>25000</v>
@@ -34299,7 +34299,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1170" t="n">
         <v>4500</v>
@@ -34328,7 +34328,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.64449596405029</v>
+        <v>4.64449644088745</v>
       </c>
       <c r="H1171" t="n">
         <v>9000</v>
@@ -34386,7 +34386,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.63486051559448</v>
+        <v>4.63486003875732</v>
       </c>
       <c r="H1173" t="n">
         <v>7500</v>
@@ -34502,7 +34502,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1177" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1177" t="n">
         <v>3500</v>
@@ -34618,7 +34618,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1181" t="n">
         <v>4500</v>
@@ -34966,7 +34966,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.23015308380127</v>
+        <v>4.23015260696411</v>
       </c>
       <c r="H1193" t="n">
         <v>7000</v>
@@ -34995,7 +34995,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1194" t="n">
         <v>2000</v>
@@ -35053,7 +35053,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.20124578475952</v>
+        <v>4.20124530792236</v>
       </c>
       <c r="H1196" t="n">
         <v>3000</v>
@@ -35140,7 +35140,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1199" t="n">
         <v>4500</v>
@@ -35169,7 +35169,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.12415838241577</v>
+        <v>4.12415885925293</v>
       </c>
       <c r="H1200" t="n">
         <v>2000</v>
@@ -35198,7 +35198,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.03743505477905</v>
+        <v>4.03743553161621</v>
       </c>
       <c r="H1201" t="n">
         <v>4000</v>
@@ -35227,7 +35227,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1202" t="n">
         <v>1000</v>
@@ -35285,7 +35285,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1204" t="n">
         <v>17500</v>
@@ -35517,7 +35517,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.54813718795776</v>
+        <v>4.54813671112061</v>
       </c>
       <c r="H1212" t="n">
         <v>13000</v>
@@ -35546,7 +35546,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.41323471069336</v>
+        <v>4.41323518753052</v>
       </c>
       <c r="H1213" t="n">
         <v>7000</v>
@@ -35604,7 +35604,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1215" t="n">
         <v>6500</v>
@@ -35633,7 +35633,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.47104978561401</v>
+        <v>4.47105026245117</v>
       </c>
       <c r="H1216" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.39396333694458</v>
+        <v>4.39396286010742</v>
       </c>
       <c r="H1217" t="n">
         <v>6000</v>
@@ -35691,7 +35691,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.27833223342896</v>
+        <v>4.27833271026611</v>
       </c>
       <c r="H1218" t="n">
         <v>11500</v>
@@ -35720,7 +35720,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.05670738220215</v>
+        <v>4.05670690536499</v>
       </c>
       <c r="H1219" t="n">
         <v>36500</v>
@@ -35749,7 +35749,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1220" t="n">
         <v>5000</v>
@@ -35865,7 +35865,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.14343070983887</v>
+        <v>4.14343023300171</v>
       </c>
       <c r="H1224" t="n">
         <v>6000</v>
@@ -35894,7 +35894,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.31687641143799</v>
+        <v>4.31687593460083</v>
       </c>
       <c r="H1225" t="n">
         <v>8000</v>
@@ -35952,7 +35952,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.10488653182983</v>
+        <v>4.10488700866699</v>
       </c>
       <c r="H1227" t="n">
         <v>15500</v>
@@ -61623,6 +61623,64 @@
         <v>19500</v>
       </c>
       <c r="I2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2113" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2114" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I2114" t="s">
         <v>9</v>
       </c>
     </row>
